--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  24-Jul-2026 14:59</t>
+          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  27-Jul-2026 15:45</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>477.8</v>
+        <v>486.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7375.5</v>
+        <v>7327.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7400</v>
+        <v>7350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28005</v>
+        <v>27800</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28000</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>393.85</v>
+        <v>400.45</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>56.25</v>
+        <v>57.05</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1340.9</v>
+        <v>1358.1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3026.4</v>
+        <v>3036.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1768.3</v>
+        <v>1770.4</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5633.5</v>
+        <v>5613</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>425.15</v>
+        <v>430.95</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>307.95</v>
+        <v>304.2</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8805.5</v>
+        <v>8843.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>419.65</v>
+        <v>419.95</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>151.07</v>
+        <v>155.06</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2637.9</v>
+        <v>2710.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2650</v>
+        <v>2700</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1468.1</v>
+        <v>1465.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>652.85</v>
+        <v>660.5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1532</v>
+        <v>1549.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1004</v>
+        <v>1052.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1227.3</v>
+        <v>1227.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11130</v>
+        <v>11183.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1876.7</v>
+        <v>1913</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1012.8</v>
+        <v>1048.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2013.5</v>
+        <v>2025.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>165.93</v>
+        <v>169.43</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>246.45</v>
+        <v>244</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405</v>
+        <v>407.15</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>497.95</v>
+        <v>504</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1898.2</v>
+        <v>1905.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>417.3</v>
+        <v>415.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>433.65</v>
+        <v>436.25</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41755</v>
+        <v>41250</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41800</v>
+        <v>41200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>310.15</v>
+        <v>316.25</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5379.5</v>
+        <v>5384.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>125.65</v>
+        <v>127.26</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1724.4</v>
+        <v>1785.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1725</v>
+        <v>1775</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1410.6</v>
+        <v>1409.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>427.4</v>
+        <v>427.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1484.7</v>
+        <v>1528.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2086.1</v>
+        <v>2136.6</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2075</v>
+        <v>2125</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>477.55</v>
+        <v>510.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>250.15</v>
+        <v>249.1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5600.5</v>
+        <v>5629.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5600</v>
+        <v>5650</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>423.2</v>
+        <v>427.35</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1649.6</v>
+        <v>1678.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>7248.5</v>
+        <v>7414</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7200</v>
+        <v>7400</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13846</v>
+        <v>13810</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>645.2</v>
+        <v>650.9</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1151.7</v>
+        <v>1150.8</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7628</v>
+        <v>7769.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7600</v>
+        <v>7800</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2905.1</v>
+        <v>2954.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>354.3</v>
+        <v>356.5</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>170.02</v>
+        <v>174.23</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1059.5</v>
+        <v>1073.7</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2028.7</v>
+        <v>2078.8</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>833.55</v>
+        <v>842.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3089.4</v>
+        <v>3112.4</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>263.15</v>
+        <v>265.45</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4573.4</v>
+        <v>4619</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1226.9</v>
+        <v>1237.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1271</v>
+        <v>1295.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2505.7</v>
+        <v>2552.4</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>742.8</v>
+        <v>739.55</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>555.05</v>
+        <v>552.85</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5011.1</v>
+        <v>5113.8</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>942.8</v>
+        <v>945.25</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>483.15</v>
+        <v>482.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>381.1</v>
+        <v>393.95</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2145</v>
+        <v>2174.6</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>80.79000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.26</v>
+        <v>126.77</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>149.33</v>
+        <v>150.27</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>727.45</v>
+        <v>733.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1759.9</v>
+        <v>1759.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>4985</v>
+        <v>5230</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5000</v>
+        <v>5250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>996.05</v>
+        <v>1006.65</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>394.6</v>
+        <v>387.4</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1040.9</v>
+        <v>1079.2</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.47</v>
+        <v>141.52</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>495.05</v>
+        <v>494</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>283.45</v>
+        <v>285.85</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1035.8</v>
+        <v>1065.7</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1025</v>
+        <v>1075</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>551.65</v>
+        <v>549.7</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1240.8</v>
+        <v>1244.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>418.25</v>
+        <v>427.45</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>384.75</v>
+        <v>384.65</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>583.2</v>
+        <v>585.2</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1759.2</v>
+        <v>1827.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1601.2</v>
+        <v>1713.4</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1600</v>
+        <v>1715</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>538.95</v>
+        <v>551.75</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3785.6</v>
+        <v>3806</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>302.4</v>
+        <v>312.25</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3418.1</v>
+        <v>3498.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2370.5</v>
+        <v>2410</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3161.4</v>
+        <v>3238.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3150</v>
+        <v>3250</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>352.95</v>
+        <v>359.85</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>855.6</v>
+        <v>858.65</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13442</v>
+        <v>13730</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13400</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2730</v>
+        <v>2755.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2725</v>
+        <v>2750</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>570.25</v>
+        <v>577.35</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1515.5</v>
+        <v>1511.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>145.55</v>
+        <v>148.97</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2288.1</v>
+        <v>2332.7</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130755</v>
+        <v>132020</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>131000</v>
+        <v>132000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2986.7</v>
+        <v>3025.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2975</v>
+        <v>3025</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>343.9</v>
+        <v>339.35</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1165.5</v>
+        <v>1194.3</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7520</v>
+        <v>7711</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7500</v>
+        <v>7700</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1443.5</v>
+        <v>1446.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.56</v>
+        <v>83.52</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>347.2</v>
+        <v>350.8</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1821.2</v>
+        <v>1832.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>10652</v>
+        <v>11089</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>10700</v>
+        <v>11100</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>248.76</v>
+        <v>238.56</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40275</v>
+        <v>39970</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40500</v>
+        <v>40000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5200.5</v>
+        <v>5268.2</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>274.7</v>
+        <v>272.9</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>411.9</v>
+        <v>420.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1570.9</v>
+        <v>1611.3</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2731.2</v>
+        <v>2742.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>110.38</v>
+        <v>111.62</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8907.5</v>
+        <v>9010</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>288.2</v>
+        <v>288.85</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>352.9</v>
+        <v>362.85</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>361.6</v>
+        <v>368.15</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>161.45</v>
+        <v>162.62</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>618.75</v>
+        <v>645</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1858.6</v>
+        <v>1866.8</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1015</v>
+        <v>1020.6</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26740</v>
+        <v>26860</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>26500</v>
+        <v>27000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1005.1</v>
+        <v>1038.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3689.8</v>
+        <v>3718</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2664.7</v>
+        <v>2636.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1941.1</v>
+        <v>1973.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1950</v>
+        <v>1975</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>486.9</v>
+        <v>488.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>406.65</v>
+        <v>413.85</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>685.35</v>
+        <v>698.9</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1775.3</v>
+        <v>1735.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1088</v>
+        <v>1107.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1090</v>
+        <v>1110</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>374.4</v>
+        <v>377.35</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>182.67</v>
+        <v>184.25</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2254.3</v>
+        <v>2295.6</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1559.5</v>
+        <v>1575</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4677</v>
+        <v>4740.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4700</v>
+        <v>4750</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4961.5</v>
+        <v>5019.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1434.1</v>
+        <v>1440</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2890.5</v>
+        <v>2938.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3870.2</v>
+        <v>3876.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1398.6</v>
+        <v>1428.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11846</v>
+        <v>11881</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.5</v>
+        <v>170.11</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>602.45</v>
+        <v>608.5</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1327.3</v>
+        <v>1319.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>177.12</v>
+        <v>178.53</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1108.7</v>
+        <v>1108.2</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  27-Jul-2026 15:45</t>
+          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  28-Jul-2026 15:24</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>486.1</v>
+        <v>476.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7327.5</v>
+        <v>7243.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7350</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27800</v>
+        <v>27905</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>400.45</v>
+        <v>391.35</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>57.05</v>
+        <v>56.7</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1358.1</v>
+        <v>1341.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3036.6</v>
+        <v>3002.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1770.4</v>
+        <v>1774.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5613</v>
+        <v>5651.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>430.95</v>
+        <v>426</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>304.2</v>
+        <v>302.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8843.5</v>
+        <v>8903</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>419.95</v>
+        <v>423.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>155.06</v>
+        <v>157.5</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2710.2</v>
+        <v>2736.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1465.8</v>
+        <v>1471.4</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>660.5</v>
+        <v>645.55</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1549.4</v>
+        <v>1549.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1052.2</v>
+        <v>1047.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1227.5</v>
+        <v>1223.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11183.5</v>
+        <v>11374</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11200</v>
+        <v>11400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1913</v>
+        <v>1927.9</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1048.3</v>
+        <v>1048.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2025.2</v>
+        <v>2013.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>169.43</v>
+        <v>168.84</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>244</v>
+        <v>239.2</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>407.15</v>
+        <v>389</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>504</v>
+        <v>499.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1905.3</v>
+        <v>1901.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>415.95</v>
+        <v>405.75</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>436.25</v>
+        <v>432.45</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41250</v>
+        <v>41310</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41200</v>
+        <v>41400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>316.25</v>
+        <v>320.05</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5384.5</v>
+        <v>5478.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>127.26</v>
+        <v>124.24</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1785.2</v>
+        <v>1753</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1409.4</v>
+        <v>1444.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>427.5</v>
+        <v>410.15</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1528.4</v>
+        <v>1686</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2136.6</v>
+        <v>2138.1</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2125</v>
+        <v>2150</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>510.5</v>
+        <v>522.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>249.1</v>
+        <v>247.4</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5629.5</v>
+        <v>5455.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5650</v>
+        <v>5450</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>427.35</v>
+        <v>424.6</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1678.9</v>
+        <v>1651.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>7414</v>
+        <v>7425</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13810</v>
+        <v>13903</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>650.9</v>
+        <v>663.05</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1150.8</v>
+        <v>1135.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7769.5</v>
+        <v>7836</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2954.1</v>
+        <v>3009.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>427</v>
+        <v>423.4</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>356.5</v>
+        <v>357.25</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.23</v>
+        <v>175.15</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2196</v>
+        <v>2184.6</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2200</v>
+        <v>2175</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1073.7</v>
+        <v>1066.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2078.8</v>
+        <v>2136.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>842.8</v>
+        <v>845.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3112.4</v>
+        <v>3116.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3100</v>
+        <v>3125</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>265.45</v>
+        <v>265.55</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4619</v>
+        <v>4600.1</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1237.4</v>
+        <v>1227.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1295.9</v>
+        <v>1318.6</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2552.4</v>
+        <v>2531.2</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>739.55</v>
+        <v>735.4</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>552.85</v>
+        <v>558.75</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5113.8</v>
+        <v>5154.3</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>945.25</v>
+        <v>936.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>482.4</v>
+        <v>473.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>393.95</v>
+        <v>400.05</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2174.6</v>
+        <v>2022.7</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2150</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.88</v>
+        <v>85.75</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.77</v>
+        <v>132.11</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>150.27</v>
+        <v>150.7</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>733.75</v>
+        <v>734.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1759.7</v>
+        <v>1743</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5230</v>
+        <v>5270.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1006.65</v>
+        <v>991.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>387.4</v>
+        <v>381.6</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1079.2</v>
+        <v>1105.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>141.52</v>
+        <v>141.28</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>494</v>
+        <v>485.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>285.85</v>
+        <v>284.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1065.7</v>
+        <v>1054.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>549.7</v>
+        <v>544.25</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1244.6</v>
+        <v>1246.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>427.45</v>
+        <v>432.2</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>384.65</v>
+        <v>385.3</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>585.2</v>
+        <v>602.45</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1827.2</v>
+        <v>1805.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1713.4</v>
+        <v>1758.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1715</v>
+        <v>1760</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>551.75</v>
+        <v>545.7</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3806</v>
+        <v>3832</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3800</v>
+        <v>3850</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>312.25</v>
+        <v>311</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3498.1</v>
+        <v>3599.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2410</v>
+        <v>2395.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3238.6</v>
+        <v>3271.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>359.85</v>
+        <v>361.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>858.65</v>
+        <v>883.25</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13730</v>
+        <v>13802</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13800</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2755.1</v>
+        <v>2713.4</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2750</v>
+        <v>2725</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>577.35</v>
+        <v>585.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1511.1</v>
+        <v>1506.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1098</v>
+        <v>1078.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>148.97</v>
+        <v>147.86</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2332.7</v>
+        <v>2413.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132020</v>
+        <v>133140</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>132000</v>
+        <v>133000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3025.9</v>
+        <v>3014.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>339.35</v>
+        <v>334.55</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1194.3</v>
+        <v>1236.15</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7711</v>
+        <v>7512.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7700</v>
+        <v>7500</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1446.1</v>
+        <v>1491.8</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3584,7 +3584,7 @@
         <v>100</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.52</v>
+        <v>83.92</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>350.8</v>
+        <v>343.75</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1832.6</v>
+        <v>1829.5</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11089</v>
+        <v>11334</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11100</v>
+        <v>11300</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.56</v>
+        <v>238.91</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39970</v>
+        <v>40370</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40000</v>
+        <v>40500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5268.2</v>
+        <v>5428.4</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>272.9</v>
+        <v>277.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>420.1</v>
+        <v>419.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1611.3</v>
+        <v>1619.6</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2742.6</v>
+        <v>2706.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>111.62</v>
+        <v>111.65</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9010</v>
+        <v>9121.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>288.85</v>
+        <v>285.3</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>362.85</v>
+        <v>364.9</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>368.15</v>
+        <v>368.45</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1280</v>
+        <v>1267.7</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>162.62</v>
+        <v>165.85</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>645</v>
+        <v>654.9</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1866.8</v>
+        <v>1889.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1020.6</v>
+        <v>1013.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26860</v>
+        <v>26875</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1038.2</v>
+        <v>1040.9</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3718</v>
+        <v>3681</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2636.5</v>
+        <v>2633.4</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1973.7</v>
+        <v>1976.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>488.7</v>
+        <v>490.45</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>413.85</v>
+        <v>409.15</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>698.9</v>
+        <v>674.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1735.2</v>
+        <v>1764.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1725</v>
+        <v>1775</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1107.4</v>
+        <v>1082.1</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1110</v>
+        <v>1080</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>377.35</v>
+        <v>371.35</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>184.25</v>
+        <v>182.63</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2295.6</v>
+        <v>2398</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1575</v>
+        <v>1635.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4740.1</v>
+        <v>4849.7</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4750</v>
+        <v>4850</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5019.5</v>
+        <v>4898.3</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1440</v>
+        <v>1431.8</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2938.3</v>
+        <v>2930.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3876.4</v>
+        <v>3993.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>3875</v>
+        <v>4000</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1428.7</v>
+        <v>1434.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11881</v>
+        <v>11956</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11900</v>
+        <v>12000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.11</v>
+        <v>168.24</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>608.5</v>
+        <v>599.65</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>264.65</v>
+        <v>259.35</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1319.3</v>
+        <v>1311.1</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>178.53</v>
+        <v>181.12</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1108.2</v>
+        <v>1099.2</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  28-Jul-2026 15:24</t>
+          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  29-Jul-2026 15:10</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>476.75</v>
+        <v>485.5</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7243.5</v>
+        <v>7310.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7250</v>
+        <v>7300</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27905</v>
+        <v>27745</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28000</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>391.35</v>
+        <v>397.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>56.7</v>
+        <v>58.06</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1341.8</v>
+        <v>1370.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3002.3</v>
+        <v>3024.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1774.7</v>
+        <v>1719.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5651.5</v>
+        <v>5672.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>426</v>
+        <v>435.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>302.6</v>
+        <v>302.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8903</v>
+        <v>8935</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>423.85</v>
+        <v>424.1</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>157.5</v>
+        <v>157.96</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2736.2</v>
+        <v>2758.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1471.4</v>
+        <v>1476.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>645.55</v>
+        <v>655.9</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1549.2</v>
+        <v>1590.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1047.7</v>
+        <v>1042.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1223.5</v>
+        <v>1235.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11374</v>
+        <v>11338</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1927.9</v>
+        <v>1924.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1048.4</v>
+        <v>1054.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2013.2</v>
+        <v>2081.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>168.84</v>
+        <v>173.58</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>239.2</v>
+        <v>243.35</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>389</v>
+        <v>387.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>499.35</v>
+        <v>520.05</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1901.8</v>
+        <v>1950.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>405.75</v>
+        <v>405.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>432.45</v>
+        <v>431.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41310</v>
+        <v>41065</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41400</v>
+        <v>41000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>320.05</v>
+        <v>317.4</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5478.5</v>
+        <v>5517.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.24</v>
+        <v>124.72</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1753</v>
+        <v>1802.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1444.6</v>
+        <v>1474.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>410.15</v>
+        <v>410.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1686</v>
+        <v>1714.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2138.1</v>
+        <v>2166.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2150</v>
+        <v>2175</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>522.4</v>
+        <v>525.85</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>247.4</v>
+        <v>264.25</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5455.5</v>
+        <v>5383</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>424.6</v>
+        <v>433.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1651.3</v>
+        <v>1674.6</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>7425</v>
+        <v>7784.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7400</v>
+        <v>7800</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13903</v>
+        <v>14275</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13900</v>
+        <v>14300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>663.05</v>
+        <v>670.25</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1135.6</v>
+        <v>1142.3</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7836</v>
+        <v>7779</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3009.9</v>
+        <v>3016.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>423.4</v>
+        <v>435.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>357.25</v>
+        <v>359.15</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.15</v>
+        <v>175.12</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2184.6</v>
+        <v>2261.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2175</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1066.9</v>
+        <v>1076.5</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2136.6</v>
+        <v>2156</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>845.4</v>
+        <v>841.85</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3116.2</v>
+        <v>3113</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>265.55</v>
+        <v>268.3</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4600.1</v>
+        <v>4592</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1227.1</v>
+        <v>1237</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1318.6</v>
+        <v>1344.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2531.2</v>
+        <v>2541.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>735.4</v>
+        <v>748.2</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>558.75</v>
+        <v>556.7</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5154.3</v>
+        <v>5149.1</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>936.4</v>
+        <v>962.45</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>473.15</v>
+        <v>483.45</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>400.05</v>
+        <v>392.75</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2022.7</v>
+        <v>2117.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.75</v>
+        <v>85.02</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>132.11</v>
+        <v>134.19</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>150.7</v>
+        <v>152.91</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>734.7</v>
+        <v>738.2</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1743</v>
+        <v>1751</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5270.5</v>
+        <v>5276.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>991.95</v>
+        <v>1012.3</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>381.6</v>
+        <v>386.15</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1105.7</v>
+        <v>1155.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>141.28</v>
+        <v>140.11</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>485.95</v>
+        <v>496</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>284.65</v>
+        <v>286.25</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1054.4</v>
+        <v>1088.7</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>544.25</v>
+        <v>545.7</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1246.9</v>
+        <v>1276.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>432.2</v>
+        <v>440.1</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>385.3</v>
+        <v>390.2</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>375</v>
+        <v>400</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>602.45</v>
+        <v>638.75</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1805.2</v>
+        <v>1882.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1758.9</v>
+        <v>1781.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1760</v>
+        <v>1780</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>545.7</v>
+        <v>553.45</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3832</v>
+        <v>3931.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3850</v>
+        <v>3950</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>311</v>
+        <v>309.15</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3599.3</v>
+        <v>3585</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2395.8</v>
+        <v>2447</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3271.2</v>
+        <v>3221.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3250</v>
+        <v>3200</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>361.25</v>
+        <v>370.15</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>883.25</v>
+        <v>878.7</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13802</v>
+        <v>13948</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2713.4</v>
+        <v>2717.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>585.5</v>
+        <v>591.6</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1506.7</v>
+        <v>1515.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1078.7</v>
+        <v>1105</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>147.86</v>
+        <v>146</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2413.5</v>
+        <v>2361.3</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133140</v>
+        <v>134200</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133000</v>
+        <v>134000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3014.4</v>
+        <v>3017.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>334.55</v>
+        <v>344.7</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1236.15</v>
+        <v>1247.85</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7512.5</v>
+        <v>7594.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1491.8</v>
+        <v>1503.3</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.92</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>343.75</v>
+        <v>343.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1829.5</v>
+        <v>1836.5</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11334</v>
+        <v>11427</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.91</v>
+        <v>238.31</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40370</v>
+        <v>40270</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5428.4</v>
+        <v>5483.3</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>277.8</v>
+        <v>277.1</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>419.9</v>
+        <v>427.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1619.6</v>
+        <v>1629.9</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2706.6</v>
+        <v>2753.9</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2700</v>
+        <v>2750</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>111.65</v>
+        <v>111.08</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9121.5</v>
+        <v>9047</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.3</v>
+        <v>282.85</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>364.9</v>
+        <v>371.15</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>368.45</v>
+        <v>374.25</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1267.7</v>
+        <v>1275.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>165.85</v>
+        <v>170.96</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>654.9</v>
+        <v>660.5</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1889.1</v>
+        <v>1894.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1013.2</v>
+        <v>1013.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26875</v>
+        <v>26825</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1040.9</v>
+        <v>1044.7</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3681</v>
+        <v>3650.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3700</v>
+        <v>3650</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2633.4</v>
+        <v>2643.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1976.7</v>
+        <v>1989.9</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1975</v>
+        <v>2000</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>490.45</v>
+        <v>512.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>409.15</v>
+        <v>414.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>674.3</v>
+        <v>679.05</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1764.5</v>
+        <v>1780.7</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1082.1</v>
+        <v>1096.1</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>371.35</v>
+        <v>377.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>182.63</v>
+        <v>187.27</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2398</v>
+        <v>2446.6</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1635.2</v>
+        <v>1644.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4849.7</v>
+        <v>4850.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4898.3</v>
+        <v>4878.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1431.8</v>
+        <v>1431.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2930.7</v>
+        <v>3005.2</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>3993.5</v>
+        <v>4075.6</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4000</v>
+        <v>4075</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1434.7</v>
+        <v>1440.2</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11956</v>
+        <v>11998</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>168.24</v>
+        <v>171.08</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>599.65</v>
+        <v>609.15</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>259.35</v>
+        <v>264.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1311.1</v>
+        <v>1313.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.12</v>
+        <v>183.61</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1099.2</v>
+        <v>1122.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  29-Jul-2026 15:10</t>
+          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  30-Jul-2026 15:13</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>485.5</v>
+        <v>480.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7310.5</v>
+        <v>7291.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27745</v>
+        <v>27555</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>27600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>397.6</v>
+        <v>394.05</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.06</v>
+        <v>58.94</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1370.8</v>
+        <v>1356.5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3024.5</v>
+        <v>3049.1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1719.7</v>
+        <v>1664.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1725</v>
+        <v>1675</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5672.5</v>
+        <v>5816.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>435.3</v>
+        <v>434.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>302.5</v>
+        <v>291.65</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8935</v>
+        <v>8988</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>424.1</v>
+        <v>423.2</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>157.96</v>
+        <v>158.09</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2758.4</v>
+        <v>2746.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1476.3</v>
+        <v>1471.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>655.9</v>
+        <v>650.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1590.7</v>
+        <v>1576.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1042.3</v>
+        <v>1030.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1235.4</v>
+        <v>1228.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11338</v>
+        <v>11432</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1924.4</v>
+        <v>1909.4</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1054.4</v>
+        <v>1053.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2081.7</v>
+        <v>2306.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.58</v>
+        <v>172.72</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>243.35</v>
+        <v>241.65</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>387.55</v>
+        <v>384.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>520.05</v>
+        <v>521.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1950.2</v>
+        <v>1956.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>405.15</v>
+        <v>403</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>431.1</v>
+        <v>425.35</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41065</v>
+        <v>41550</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41000</v>
+        <v>41600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>317.4</v>
+        <v>315.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5517.5</v>
+        <v>5524.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.72</v>
+        <v>124.28</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1802.9</v>
+        <v>1773.8</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1474.3</v>
+        <v>1466.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>410.05</v>
+        <v>417.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1714.9</v>
+        <v>1746.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2166.4</v>
+        <v>2084.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2175</v>
+        <v>2075</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>525.85</v>
+        <v>525.15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>264.25</v>
+        <v>260.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5383</v>
+        <v>5396</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>433.7</v>
+        <v>426.1</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1674.6</v>
+        <v>1643.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>7784.5</v>
+        <v>7835</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14275</v>
+        <v>14338</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>670.25</v>
+        <v>654.85</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1142.3</v>
+        <v>1144.8</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7779</v>
+        <v>7912.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3016.8</v>
+        <v>3013.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>435.65</v>
+        <v>452.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>359.15</v>
+        <v>354.15</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.12</v>
+        <v>173.64</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2261.7</v>
+        <v>2190.3</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1076.5</v>
+        <v>1072.1</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2156</v>
+        <v>2110.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>841.85</v>
+        <v>833.95</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3113</v>
+        <v>3104.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3125</v>
+        <v>3100</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>268.3</v>
+        <v>273.05</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4592</v>
+        <v>4581.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1237</v>
+        <v>1261.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1344.3</v>
+        <v>1352.7</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2541.9</v>
+        <v>2546.3</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>748.2</v>
+        <v>753.95</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>556.7</v>
+        <v>545.4</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5149.1</v>
+        <v>5325</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5150</v>
+        <v>5300</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>962.45</v>
+        <v>970.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>483.45</v>
+        <v>480.25</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>392.75</v>
+        <v>388.45</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2117.8</v>
+        <v>2107.9</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.02</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>134.19</v>
+        <v>131.4</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>152.91</v>
+        <v>151.74</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>738.2</v>
+        <v>749.25</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1751</v>
+        <v>1743.1</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5276.5</v>
+        <v>5230.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1012.3</v>
+        <v>1011.45</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>386.15</v>
+        <v>392.9</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1155.6</v>
+        <v>1155.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.11</v>
+        <v>139.94</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>496</v>
+        <v>493.15</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>286.25</v>
+        <v>285.05</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1088.7</v>
+        <v>1093.7</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>545.7</v>
+        <v>543.7</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1276.6</v>
+        <v>1270.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>440.1</v>
+        <v>439.8</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>390.2</v>
+        <v>389.4</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>638.75</v>
+        <v>589.75</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1882.5</v>
+        <v>1878.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>553.45</v>
+        <v>540.9</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3931.4</v>
+        <v>3937.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>309.15</v>
+        <v>306.25</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3585</v>
+        <v>3559.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2447</v>
+        <v>2421.2</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2450</v>
+        <v>2425</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3221.8</v>
+        <v>3283.7</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>370.15</v>
+        <v>368.35</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>878.7</v>
+        <v>885.35</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13948</v>
+        <v>14188</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13900</v>
+        <v>14200</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2717.5</v>
+        <v>2677</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2725</v>
+        <v>2675</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>591.6</v>
+        <v>585.2</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1515.1</v>
+        <v>1510.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1105</v>
+        <v>1118.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>146</v>
+        <v>146.72</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2361.3</v>
+        <v>2346.7</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134200</v>
+        <v>134860</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>134000</v>
+        <v>135000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3017.9</v>
+        <v>3008.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3025</v>
+        <v>3000</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>344.7</v>
+        <v>347.65</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1247.85</v>
+        <v>1244.05</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7594.5</v>
+        <v>7386.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7600</v>
+        <v>7400</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1503.3</v>
+        <v>1520.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.84999999999999</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>343.5</v>
+        <v>344.85</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1836.5</v>
+        <v>1814.4</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11427</v>
+        <v>11136</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11400</v>
+        <v>11100</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.31</v>
+        <v>241.59</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40270</v>
+        <v>41085</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40500</v>
+        <v>41000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5483.3</v>
+        <v>5514.7</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>277.1</v>
+        <v>278.9</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>427.1</v>
+        <v>426.25</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2753.9</v>
+        <v>2777.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>111.08</v>
+        <v>111.64</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9047</v>
+        <v>8896</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>282.85</v>
+        <v>285.7</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>371.15</v>
+        <v>378.05</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>374.25</v>
+        <v>374.9</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1275.9</v>
+        <v>1292.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>170.96</v>
+        <v>169.05</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>660.5</v>
+        <v>657.8</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1894.9</v>
+        <v>1877.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1013.7</v>
+        <v>1025.3</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1010</v>
+        <v>1030</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26825</v>
+        <v>26455</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>27000</v>
+        <v>26500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1044.7</v>
+        <v>1027.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3650.8</v>
+        <v>3658.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2643.8</v>
+        <v>2604.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1989.9</v>
+        <v>2001.1</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>512.85</v>
+        <v>511.5</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>414.25</v>
+        <v>399.2</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>679.05</v>
+        <v>670.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1780.7</v>
+        <v>1773.7</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1096.1</v>
+        <v>1094.2</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>377.25</v>
+        <v>375.95</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>187.27</v>
+        <v>186.92</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2446.6</v>
+        <v>2431.8</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1644.2</v>
+        <v>1669</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4850.2</v>
+        <v>4850</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4878.5</v>
+        <v>4872.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1431.1</v>
+        <v>1423.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3005.2</v>
+        <v>2999.2</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4075.6</v>
+        <v>4208.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4075</v>
+        <v>4200</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1440.2</v>
+        <v>1436.1</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11998</v>
+        <v>11847</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>171.08</v>
+        <v>170.4</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>609.15</v>
+        <v>602.55</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>264.5</v>
+        <v>267.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1313.3</v>
+        <v>1333.2</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>183.61</v>
+        <v>186.33</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1122.7</v>
+        <v>1115.1</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:30-Jul-2026  NM:27-Aug-2026  |  30-Jul-2026 15:13</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  31-Jul-2026 15:22</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>480.2</v>
+        <v>489.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7291.5</v>
+        <v>7284.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27555</v>
+        <v>27800</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27600</v>
+        <v>27800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>394.05</v>
+        <v>404.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.94</v>
+        <v>60.24</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1356.5</v>
+        <v>1357.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3049.1</v>
+        <v>3009.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1664.1</v>
+        <v>1696.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5816.5</v>
+        <v>5751.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>434.2</v>
+        <v>432.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>291.65</v>
+        <v>297.95</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8988</v>
+        <v>8957</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>423.2</v>
+        <v>428.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>158.09</v>
+        <v>166.18</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2746.2</v>
+        <v>2747.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1471.9</v>
+        <v>1448.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>650.15</v>
+        <v>651.45</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1576.3</v>
+        <v>1580.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1030.7</v>
+        <v>1047.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1228.9</v>
+        <v>1229.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11432</v>
+        <v>11520.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1909.4</v>
+        <v>2029.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1900</v>
+        <v>2025</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1053.5</v>
+        <v>1141.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2306.9</v>
+        <v>2473.5</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2300</v>
+        <v>2450</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>172.72</v>
+        <v>174.13</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>241.65</v>
+        <v>242.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>384.9</v>
+        <v>387.85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>521.35</v>
+        <v>520.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1956.8</v>
+        <v>1972</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>1975</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>425.35</v>
+        <v>425.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41550</v>
+        <v>41085</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41600</v>
+        <v>41000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>315.8</v>
+        <v>319.75</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5524.5</v>
+        <v>5416.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.28</v>
+        <v>124.98</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1773.8</v>
+        <v>1849.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1775</v>
+        <v>1850</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1466.4</v>
+        <v>1473.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>417.2</v>
+        <v>414.15</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1746.9</v>
+        <v>1721</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2084.8</v>
+        <v>2076.1</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>525.15</v>
+        <v>525.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>260.3</v>
+        <v>260.2</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5396</v>
+        <v>5519</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>426.1</v>
+        <v>421.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1643.9</v>
+        <v>1662.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>7835</v>
+        <v>8056</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14338</v>
+        <v>14049</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14300</v>
+        <v>14000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>654.85</v>
+        <v>659.3</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1144.8</v>
+        <v>1148.1</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7912.5</v>
+        <v>7833.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7900</v>
+        <v>7800</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3013.6</v>
+        <v>3086</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>452.7</v>
+        <v>449.8</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>354.15</v>
+        <v>358.85</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.64</v>
+        <v>181.44</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2190.3</v>
+        <v>2233.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2200</v>
+        <v>2225</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1072.1</v>
+        <v>1070.4</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2110.9</v>
+        <v>2105.7</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>833.95</v>
+        <v>824.65</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3104.8</v>
+        <v>3100.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>273.05</v>
+        <v>275.25</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4581.4</v>
+        <v>4646.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1261.7</v>
+        <v>1260.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1352.7</v>
+        <v>1346.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2546.3</v>
+        <v>2615.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>753.95</v>
+        <v>748.15</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>545.4</v>
+        <v>548.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5325</v>
+        <v>5386</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>970.4</v>
+        <v>974.45</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>480.25</v>
+        <v>491.6</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>388.45</v>
+        <v>389.75</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2107.9</v>
+        <v>2101.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.76000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>131.4</v>
+        <v>132.24</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.74</v>
+        <v>151.98</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>749.25</v>
+        <v>738.55</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1743.1</v>
+        <v>1799.8</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5230.5</v>
+        <v>5171</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5250</v>
+        <v>5150</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1011.45</v>
+        <v>1012.45</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>392.9</v>
+        <v>391.1</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1155.1</v>
+        <v>1130.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>139.94</v>
+        <v>140.17</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>493.15</v>
+        <v>489.8</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>285.05</v>
+        <v>281</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1093.7</v>
+        <v>1102.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>543.7</v>
+        <v>554.65</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1270.8</v>
+        <v>1270</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>439.8</v>
+        <v>438.25</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>389.4</v>
+        <v>390.3</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>589.75</v>
+        <v>598.4</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1878.8</v>
+        <v>1905.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1781.3</v>
+        <v>1816.2</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1780</v>
+        <v>1815</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>540.9</v>
+        <v>523.1</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3937.7</v>
+        <v>3938.9</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>306.25</v>
+        <v>311.25</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3559.1</v>
+        <v>3555.4</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2421.2</v>
+        <v>2415</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3283.7</v>
+        <v>3398.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>368.35</v>
+        <v>371.85</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>885.35</v>
+        <v>870.65</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>890</v>
+        <v>870</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14188</v>
+        <v>14234</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2677</v>
+        <v>2692.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2675</v>
+        <v>2700</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>585.2</v>
+        <v>582.45</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1510.8</v>
+        <v>1499</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1118.5</v>
+        <v>1120.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>146.72</v>
+        <v>150.75</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2346.7</v>
+        <v>2342.3</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134860</v>
+        <v>132770</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>135000</v>
+        <v>133000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3008.7</v>
+        <v>3119.6</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3000</v>
+        <v>3125</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>347.65</v>
+        <v>350.05</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1244.05</v>
+        <v>1226.25</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7386.5</v>
+        <v>7567.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1520.7</v>
+        <v>1509.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.01000000000001</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>344.85</v>
+        <v>347.25</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1814.4</v>
+        <v>1827.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11136</v>
+        <v>11186</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>241.59</v>
+        <v>242.53</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>41085</v>
+        <v>40375</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>41000</v>
+        <v>40500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5514.7</v>
+        <v>5549</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>278.9</v>
+        <v>280.75</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>426.25</v>
+        <v>424.35</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1629.9</v>
+        <v>1611.4</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2777.3</v>
+        <v>2751.2</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>111.64</v>
+        <v>112.71</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8896</v>
+        <v>9106.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8900</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>285.7</v>
+        <v>284.25</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>378.05</v>
+        <v>375.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>374.9</v>
+        <v>372.95</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1292.9</v>
+        <v>1307.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>169.05</v>
+        <v>169.03</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>657.8</v>
+        <v>660.15</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1877.5</v>
+        <v>1882</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1025.3</v>
+        <v>1027.4</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26455</v>
+        <v>26055</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>26500</v>
+        <v>26000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1027.2</v>
+        <v>1046.7</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3658.8</v>
+        <v>3760</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3650</v>
+        <v>3750</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2604.8</v>
+        <v>2622.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>2001.1</v>
+        <v>1990.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>511.5</v>
+        <v>508.65</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>399.2</v>
+        <v>385.9</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>670.3</v>
+        <v>673.55</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1773.7</v>
+        <v>1756.4</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1094.2</v>
+        <v>1083.1</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>375.95</v>
+        <v>380.7</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>186.92</v>
+        <v>189.69</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2431.8</v>
+        <v>2365.6</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2450</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1669</v>
+        <v>1651.3</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4850</v>
+        <v>4875.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4872.1</v>
+        <v>5122.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4850</v>
+        <v>5100</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1423.5</v>
+        <v>1413.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2999.2</v>
+        <v>3005.9</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4208.4</v>
+        <v>4313.1</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4200</v>
+        <v>4325</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1436.1</v>
+        <v>1418.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11847</v>
+        <v>11903</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>170.4</v>
+        <v>171.24</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>602.55</v>
+        <v>604.3</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>267.5</v>
+        <v>264.25</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1333.2</v>
+        <v>1328.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>186.33</v>
+        <v>183.65</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1115.1</v>
+        <v>1126.8</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  31-Jul-2026 15:22</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  03-Aug-2026 15:45</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>489.1</v>
+        <v>486.8</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7284.5</v>
+        <v>7601</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7300</v>
+        <v>7600</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27800</v>
+        <v>27895</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>404.3</v>
+        <v>424.35</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>60.24</v>
+        <v>62.41</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1357.4</v>
+        <v>1398</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3009.5</v>
+        <v>3068</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1696.5</v>
+        <v>1701</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5751.5</v>
+        <v>5707</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>432.2</v>
+        <v>444</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>297.95</v>
+        <v>302</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8957</v>
+        <v>8820</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9000</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>428.15</v>
+        <v>436.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>166.18</v>
+        <v>174.55</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2747.3</v>
+        <v>2810</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1448.6</v>
+        <v>1435.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>651.45</v>
+        <v>667.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1580.2</v>
+        <v>1554.7</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1047.3</v>
+        <v>1060</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1229.5</v>
+        <v>1272</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1225</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11520.5</v>
+        <v>11856</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11500</v>
+        <v>11900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2029.1</v>
+        <v>2096</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2025</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1141.2</v>
+        <v>1153</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2473.5</v>
+        <v>2492.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174.13</v>
+        <v>173.65</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>242.6</v>
+        <v>247.25</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>387.85</v>
+        <v>392.15</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>520.45</v>
+        <v>526.55</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1972</v>
+        <v>1970.5</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>407</v>
+        <v>411.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>425.7</v>
+        <v>427</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41085</v>
+        <v>41300</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41000</v>
+        <v>41200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>319.75</v>
+        <v>329.95</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5416.5</v>
+        <v>5531</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5550</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.98</v>
+        <v>127.1</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1849.9</v>
+        <v>1888.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1473.2</v>
+        <v>1474.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>414.15</v>
+        <v>416</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1721</v>
+        <v>1768</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2076.1</v>
+        <v>2077</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>525.5</v>
+        <v>525</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>260.2</v>
+        <v>266.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5519</v>
+        <v>5550</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>421.45</v>
+        <v>425.8</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1662.2</v>
+        <v>1713.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8056</v>
+        <v>8585</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8100</v>
+        <v>8600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14049</v>
+        <v>13892</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14000</v>
+        <v>13900</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>659.3</v>
+        <v>668.55</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1148.1</v>
+        <v>1180</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7833.5</v>
+        <v>8050</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3086</v>
+        <v>3135.5</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>449.8</v>
+        <v>444.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>358.85</v>
+        <v>371.7</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>181.44</v>
+        <v>174.3</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2233.9</v>
+        <v>2230</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1070.4</v>
+        <v>1085.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2105.7</v>
+        <v>2089.7</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>824.65</v>
+        <v>843.2</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3100.8</v>
+        <v>3260</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3100</v>
+        <v>3250</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>275.25</v>
+        <v>274.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4646.5</v>
+        <v>4690</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1260.7</v>
+        <v>1285</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1346.9</v>
+        <v>1377</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2615.8</v>
+        <v>2600.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>748.15</v>
+        <v>753</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>548.5</v>
+        <v>553.1</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5386</v>
+        <v>5460</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5400</v>
+        <v>5450</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>974.45</v>
+        <v>994.9</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>491.6</v>
+        <v>495.05</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>389.75</v>
+        <v>395</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2101.3</v>
+        <v>2138</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.68000000000001</v>
+        <v>86</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>132.24</v>
+        <v>128</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.98</v>
+        <v>156.17</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>738.55</v>
+        <v>752</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>740</v>
+        <v>750</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1799.8</v>
+        <v>1798.6</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5171</v>
+        <v>5400</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5150</v>
+        <v>5400</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1012.45</v>
+        <v>1028.9</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>391.1</v>
+        <v>395.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1130.1</v>
+        <v>1180</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.17</v>
+        <v>143.7</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>489.8</v>
+        <v>513.5</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1102.4</v>
+        <v>1105.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>554.65</v>
+        <v>569</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1270</v>
+        <v>1292.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>438.25</v>
+        <v>470</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>390.3</v>
+        <v>397.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>598.4</v>
+        <v>619.25</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1905.2</v>
+        <v>1900.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1816.2</v>
+        <v>1811.4</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>523.1</v>
+        <v>519</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3938.9</v>
+        <v>4025</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>311.25</v>
+        <v>318</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3555.4</v>
+        <v>3564.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2415</v>
+        <v>2393</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2425</v>
+        <v>2400</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3398.5</v>
+        <v>3428.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3400</v>
+        <v>3450</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>371.85</v>
+        <v>365</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>870.65</v>
+        <v>880.95</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14234</v>
+        <v>14150</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2692.2</v>
+        <v>2642.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>582.45</v>
+        <v>596.45</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1499</v>
+        <v>1542.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1120.5</v>
+        <v>1115.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>150.75</v>
+        <v>155.01</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2342.3</v>
+        <v>2429</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132770</v>
+        <v>133730</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133000</v>
+        <v>133500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3119.6</v>
+        <v>2890.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3125</v>
+        <v>2900</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>350.05</v>
+        <v>369</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1226.25</v>
+        <v>1268.8</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7567.5</v>
+        <v>7555</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1509.6</v>
+        <v>1530</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.04000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>347.25</v>
+        <v>350.9</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1827.7</v>
+        <v>1861.1</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11186</v>
+        <v>11332</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>242.53</v>
+        <v>242</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40375</v>
+        <v>40200</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40500</v>
+        <v>40000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5549</v>
+        <v>5575</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>280.75</v>
+        <v>284.85</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>424.35</v>
+        <v>421.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1611.4</v>
+        <v>1642.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2751.2</v>
+        <v>2793</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>112.71</v>
+        <v>113</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9106.5</v>
+        <v>9034</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>284.25</v>
+        <v>287</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>375.5</v>
+        <v>379.95</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>372.95</v>
+        <v>368.1</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1307.8</v>
+        <v>1319</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>169.03</v>
+        <v>165</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>660.15</v>
+        <v>665.05</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1882</v>
+        <v>1915</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1027.4</v>
+        <v>1045</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26055</v>
+        <v>27000</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1046.7</v>
+        <v>1090.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3760</v>
+        <v>3900</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3750</v>
+        <v>3900</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2622.5</v>
+        <v>2645</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1990.5</v>
+        <v>1963.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>508.65</v>
+        <v>503.8</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>385.9</v>
+        <v>402.2</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>673.55</v>
+        <v>674.65</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1756.4</v>
+        <v>1780.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1083.1</v>
+        <v>1110</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>380.7</v>
+        <v>382</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>189.69</v>
+        <v>191</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2365.6</v>
+        <v>2473.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1651.3</v>
+        <v>1649</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4875.2</v>
+        <v>5000</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5122.8</v>
+        <v>5050</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1413.3</v>
+        <v>1391.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3005.9</v>
+        <v>3050</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4313.1</v>
+        <v>4389</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4325</v>
+        <v>4400</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1418.8</v>
+        <v>1438.4</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11903</v>
+        <v>12054</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11900</v>
+        <v>12100</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>171.24</v>
+        <v>174</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>604.3</v>
+        <v>620</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>264.25</v>
+        <v>267.25</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1328.9</v>
+        <v>1324.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>183.65</v>
+        <v>188.66</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1126.8</v>
+        <v>1121</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  03-Aug-2026 15:45</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  04-Aug-2026 15:26</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>486.8</v>
+        <v>481.75</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7601</v>
+        <v>7700</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27895</v>
+        <v>27825</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>424.35</v>
+        <v>420</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.41</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1398</v>
+        <v>1384.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3068</v>
+        <v>3050</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1701</v>
+        <v>1706.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5707</v>
+        <v>5608</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>444</v>
+        <v>436.05</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>302</v>
+        <v>300.35</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8820</v>
+        <v>9050</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>436.6</v>
+        <v>438.35</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>174.55</v>
+        <v>172.08</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2810</v>
+        <v>2775</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1435.6</v>
+        <v>1448</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>667.6</v>
+        <v>666.95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1554.7</v>
+        <v>1585.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1272</v>
+        <v>1261.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11856</v>
+        <v>11600</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11900</v>
+        <v>11600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2096</v>
+        <v>2105</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2492.2</v>
+        <v>2491.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.65</v>
+        <v>173.6</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>247.25</v>
+        <v>245</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>392.15</v>
+        <v>391.5</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>526.55</v>
+        <v>533.8</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1970.5</v>
+        <v>1970.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>411.15</v>
+        <v>411.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41300</v>
+        <v>41200</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>329.95</v>
+        <v>324</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5531</v>
+        <v>5478</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5550</v>
+        <v>5500</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>127.1</v>
+        <v>128</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1888.2</v>
+        <v>1875</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1474.4</v>
+        <v>1460</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>416</v>
+        <v>417.6</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1768</v>
+        <v>1749.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2077</v>
+        <v>2010</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>266.3</v>
+        <v>263.1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>425.8</v>
+        <v>409.65</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1713.8</v>
+        <v>1717.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8585</v>
+        <v>8378</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8600</v>
+        <v>8400</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13892</v>
+        <v>13988</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>668.55</v>
+        <v>643.4</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1180</v>
+        <v>1172.6</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8050</v>
+        <v>7935</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3135.5</v>
+        <v>3101.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>444.7</v>
+        <v>458.35</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>371.7</v>
+        <v>362.45</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.3</v>
+        <v>175</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1085.9</v>
+        <v>1058.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2089.7</v>
+        <v>2033.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>843.2</v>
+        <v>825.7</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3260</v>
+        <v>3138</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3250</v>
+        <v>3150</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>274.5</v>
+        <v>277.55</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4690</v>
+        <v>4635</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1377</v>
+        <v>1369.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2600.6</v>
+        <v>2556</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>553.1</v>
+        <v>535.95</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5460</v>
+        <v>5548</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5450</v>
+        <v>5550</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>994.9</v>
+        <v>1020</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>990</v>
+        <v>1020</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>495.05</v>
+        <v>492.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>395</v>
+        <v>391.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2138</v>
+        <v>2096.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>128</v>
+        <v>129.2</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>156.17</v>
+        <v>153.93</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2558,7 +2558,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1798.6</v>
+        <v>1774.8</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5400</v>
+        <v>5358</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1028.9</v>
+        <v>1026</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>395.3</v>
+        <v>390</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1180</v>
+        <v>1167.5</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>143.7</v>
+        <v>141.6</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>513.5</v>
+        <v>510.25</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1105.1</v>
+        <v>1124</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1292.3</v>
+        <v>1300</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>397.5</v>
+        <v>398</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>619.25</v>
+        <v>625.6</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1900.4</v>
+        <v>1889.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1811.4</v>
+        <v>1850</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1810</v>
+        <v>1850</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4025</v>
+        <v>3990</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>318</v>
+        <v>317.9</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3564.8</v>
+        <v>3502</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2393</v>
+        <v>2410</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3428.6</v>
+        <v>3433</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>365</v>
+        <v>356.6</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>880.95</v>
+        <v>875</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14150</v>
+        <v>14168</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2642.1</v>
+        <v>2680</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2650</v>
+        <v>2675</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>596.45</v>
+        <v>584.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1542.5</v>
+        <v>1519.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1115.7</v>
+        <v>1111.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>155.01</v>
+        <v>151</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2429</v>
+        <v>2380</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133730</v>
+        <v>132745</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133500</v>
+        <v>132500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2890.9</v>
+        <v>2870</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2900</v>
+        <v>2875</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1268.8</v>
+        <v>1260</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7555</v>
+        <v>7629</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1530</v>
+        <v>1520</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>350.9</v>
+        <v>343.65</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1861.1</v>
+        <v>1778.8</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1850</v>
+        <v>1775</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11332</v>
+        <v>11600</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11300</v>
+        <v>11600</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40200</v>
+        <v>39750</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5575</v>
+        <v>5499</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>284.85</v>
+        <v>285</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>421.5</v>
+        <v>420</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1642.5</v>
+        <v>1620</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2793</v>
+        <v>2785.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>113</v>
+        <v>113.99</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9034</v>
+        <v>9176</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>287</v>
+        <v>283.4</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>379.95</v>
+        <v>380.55</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>368.1</v>
+        <v>368</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1319</v>
+        <v>1290.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>165</v>
+        <v>173.55</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>665.05</v>
+        <v>658</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1915</v>
+        <v>1899</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1045</v>
+        <v>1042.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>27000</v>
+        <v>26900</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1090.2</v>
+        <v>1087.3</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3900</v>
+        <v>4000.5</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2645</v>
+        <v>2642.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1963.5</v>
+        <v>1964</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>503.8</v>
+        <v>502.35</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>402.2</v>
+        <v>410.2</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>674.65</v>
+        <v>668.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1780.1</v>
+        <v>1778.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1110</v>
+        <v>1092</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1110</v>
+        <v>1090</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>191</v>
+        <v>190.95</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2473.7</v>
+        <v>2460</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1649</v>
+        <v>1648.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5000</v>
+        <v>4935</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1391.7</v>
+        <v>1341</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3050</v>
+        <v>3107.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4389</v>
+        <v>4360</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4400</v>
+        <v>4350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1438.4</v>
+        <v>1434.1</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12054</v>
+        <v>12050</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>620</v>
+        <v>581.9</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>625</v>
+        <v>575</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>267.25</v>
+        <v>269</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1324.8</v>
+        <v>1327.7</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>188.66</v>
+        <v>186.3</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  04-Aug-2026 15:26</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  05-Aug-2026 15:17</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>481.75</v>
+        <v>485.95</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7700</v>
+        <v>7690.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27825</v>
+        <v>27785</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>420</v>
+        <v>424.7</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61</v>
+        <v>62.1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1384.7</v>
+        <v>1394</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1706.7</v>
+        <v>1700</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5608</v>
+        <v>5696.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>436.05</v>
+        <v>445</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>300.35</v>
+        <v>299.2</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>9050</v>
+        <v>8910</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>438.35</v>
+        <v>444.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>172.08</v>
+        <v>177</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2775</v>
+        <v>2760</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1448</v>
+        <v>1434.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>666.95</v>
+        <v>660.35</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1585.9</v>
+        <v>1613.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1059</v>
+        <v>1051.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1261.8</v>
+        <v>1253.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2105</v>
+        <v>2086</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1149</v>
+        <v>1158.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2491.9</v>
+        <v>2501.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.6</v>
+        <v>170.46</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>245</v>
+        <v>245.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>391.5</v>
+        <v>390</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>533.8</v>
+        <v>545.2</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1970.1</v>
+        <v>1978</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>411.95</v>
+        <v>412.4</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>422</v>
+        <v>425.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>41200</v>
+        <v>42920</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>41200</v>
+        <v>43000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>324</v>
+        <v>326.25</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5478</v>
+        <v>5440</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5500</v>
+        <v>5450</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>128</v>
+        <v>128.91</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1875</v>
+        <v>1880</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1460</v>
+        <v>1458.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>417.6</v>
+        <v>415.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1749.9</v>
+        <v>1777</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2010</v>
+        <v>2040</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>515</v>
+        <v>516.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>263.1</v>
+        <v>266.1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5550</v>
+        <v>5440</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5550</v>
+        <v>5450</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>409.65</v>
+        <v>414</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1717.7</v>
+        <v>1736.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8378</v>
+        <v>8388</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13988</v>
+        <v>14310</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14000</v>
+        <v>14300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>643.4</v>
+        <v>649.1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1172.6</v>
+        <v>1176</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7935</v>
+        <v>7986.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7900</v>
+        <v>8000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3101.2</v>
+        <v>3089.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>458.35</v>
+        <v>467</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>362.45</v>
+        <v>356.45</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175</v>
+        <v>176.96</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2225</v>
+        <v>2259</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2225</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1058.2</v>
+        <v>1069</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2033.6</v>
+        <v>2099</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>825.7</v>
+        <v>845.1</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3138</v>
+        <v>3224</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3150</v>
+        <v>3225</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>277.55</v>
+        <v>278.85</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4635</v>
+        <v>4645</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1369.9</v>
+        <v>1350</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2556</v>
+        <v>2562</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2315,7 +2315,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>535.95</v>
+        <v>545</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5548</v>
+        <v>5690</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5550</v>
+        <v>5700</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>492.35</v>
+        <v>533.8</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>490</v>
+        <v>535</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>391.5</v>
+        <v>394.95</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2096.5</v>
+        <v>2085.3</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>86</v>
+        <v>85.3</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>129.2</v>
+        <v>129.59</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>153.93</v>
+        <v>154.08</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>750</v>
+        <v>741.05</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1774.8</v>
+        <v>1775.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5358</v>
+        <v>5400</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>390</v>
+        <v>385.85</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1167.5</v>
+        <v>1174</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>141.6</v>
+        <v>144</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>289</v>
+        <v>286.95</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1124</v>
+        <v>1113.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1300</v>
+        <v>1330</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>625.6</v>
+        <v>623</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1889.4</v>
+        <v>1887.1</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1850</v>
+        <v>1835</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1850</v>
+        <v>1835</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>512</v>
+        <v>512.05</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3990</v>
+        <v>4057</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>317.9</v>
+        <v>318.4</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3502</v>
+        <v>3575.3</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2410</v>
+        <v>2388</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3433</v>
+        <v>3455.4</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>356.6</v>
+        <v>363.6</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>875</v>
+        <v>852</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>880</v>
+        <v>850</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14168</v>
+        <v>14190</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2680</v>
+        <v>2598.6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2675</v>
+        <v>2600</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>584.5</v>
+        <v>576.75</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1519.3</v>
+        <v>1523</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1111.6</v>
+        <v>1115.1</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>151</v>
+        <v>154.35</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2380</v>
+        <v>2460</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132745</v>
+        <v>134405</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>132500</v>
+        <v>134500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2870</v>
+        <v>2892</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2875</v>
+        <v>2900</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1260</v>
+        <v>1242</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7629</v>
+        <v>7609.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>84.2</v>
+        <v>85.8</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>343.65</v>
+        <v>349.9</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1778.8</v>
+        <v>1806.5</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11600</v>
+        <v>11759</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>242</v>
+        <v>240.2</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39750</v>
+        <v>40355</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40000</v>
+        <v>40500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5499</v>
+        <v>5520</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>285</v>
+        <v>280.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1620</v>
+        <v>1665</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2785.5</v>
+        <v>2810</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>113.99</v>
+        <v>113.55</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9176</v>
+        <v>9200</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>283.4</v>
+        <v>281.75</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>380.55</v>
+        <v>389.8</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1290.9</v>
+        <v>1280</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>173.55</v>
+        <v>175.5</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>658</v>
+        <v>665.7</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1899</v>
+        <v>1879.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1042.7</v>
+        <v>1055</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1040</v>
+        <v>1060</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1087.3</v>
+        <v>1122.4</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4000.5</v>
+        <v>3980</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2642.3</v>
+        <v>2639.7</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1964</v>
+        <v>1940</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1975</v>
+        <v>1950</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>502.35</v>
+        <v>493.35</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>410.2</v>
+        <v>406.95</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>668.3</v>
+        <v>666.15</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1778.5</v>
+        <v>1747.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1092</v>
+        <v>1096.3</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1090</v>
+        <v>1100</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>190.95</v>
+        <v>192.99</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2460</v>
+        <v>2413</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1648.5</v>
+        <v>1650</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4935</v>
+        <v>4912.4</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5030</v>
+        <v>5000</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1341</v>
+        <v>1323.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3107.7</v>
+        <v>3129</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4360</v>
+        <v>4455.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4350</v>
+        <v>4450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1434.1</v>
+        <v>1412.6</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12050</v>
+        <v>12190</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>174</v>
+        <v>175.8</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>581.9</v>
+        <v>577.25</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1327.7</v>
+        <v>1300.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>186.3</v>
+        <v>186.99</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1130</v>
+        <v>1121.1</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  05-Aug-2026 15:17</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  06-Aug-2026 15:16</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>485.95</v>
+        <v>501.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7690.5</v>
+        <v>7735</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7700</v>
+        <v>7750</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27785</v>
+        <v>27855</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>424.7</v>
+        <v>421.5</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>62.1</v>
+        <v>63.26</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1394</v>
+        <v>1378.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3050</v>
+        <v>3026</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5696.5</v>
+        <v>5597.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>445</v>
+        <v>436.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>299.2</v>
+        <v>297.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8910</v>
+        <v>8974.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>9000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>444.9</v>
+        <v>449.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>177</v>
+        <v>177.5</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2760</v>
+        <v>2755</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1434.7</v>
+        <v>1442</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>660.35</v>
+        <v>660.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1613.4</v>
+        <v>1588.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1051.3</v>
+        <v>1087.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1253.9</v>
+        <v>1256</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11800</v>
+        <v>11620</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1158.8</v>
+        <v>1144.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2501.6</v>
+        <v>2465.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>170.46</v>
+        <v>174.66</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>245.6</v>
+        <v>251</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>390</v>
+        <v>399.2</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>545.2</v>
+        <v>537.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1978</v>
+        <v>1948</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1975</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>412.4</v>
+        <v>408.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>425.2</v>
+        <v>436.6</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>42920</v>
+        <v>42000</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>43000</v>
+        <v>42000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>326.25</v>
+        <v>323.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5440</v>
+        <v>5404</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>128.91</v>
+        <v>131.7</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1880</v>
+        <v>1940</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1875</v>
+        <v>1950</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1458.8</v>
+        <v>1477</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1450</v>
+        <v>1475</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>415.5</v>
+        <v>415.6</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1777</v>
+        <v>1772.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2040</v>
+        <v>2028.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2050</v>
+        <v>2025</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>516.35</v>
+        <v>512</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>266.1</v>
+        <v>270</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5440</v>
+        <v>5402</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>414</v>
+        <v>411.3</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1736.7</v>
+        <v>1750.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8388</v>
+        <v>8349</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14310</v>
+        <v>14200</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14300</v>
+        <v>14200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>649.1</v>
+        <v>642</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7986.5</v>
+        <v>7967.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3089.2</v>
+        <v>3081</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>467</v>
+        <v>474.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>356.45</v>
+        <v>353.55</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>176.96</v>
+        <v>176.4</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2259</v>
+        <v>2270</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1069</v>
+        <v>1077.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2099</v>
+        <v>2081.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>845.1</v>
+        <v>838.65</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>278.85</v>
+        <v>272.55</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4645</v>
+        <v>4920</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1290</v>
+        <v>1285.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1350</v>
+        <v>1335</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2562</v>
+        <v>2538.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>735</v>
+        <v>734.3</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>545</v>
+        <v>542.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5690</v>
+        <v>5550.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5700</v>
+        <v>5550</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1040</v>
+        <v>1027</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>533.8</v>
+        <v>545.95</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>394.95</v>
+        <v>395</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2085.3</v>
+        <v>2079.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.3</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>129.59</v>
+        <v>128.83</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>154.08</v>
+        <v>154.33</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>741.05</v>
+        <v>736</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1775.7</v>
+        <v>1763.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5400</v>
+        <v>5318.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1019</v>
+        <v>1016.2</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>385.85</v>
+        <v>383.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1174</v>
+        <v>1165</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>144</v>
+        <v>142.66</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>510.25</v>
+        <v>520.45</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>286.95</v>
+        <v>285.9</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1113.4</v>
+        <v>1101</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>566</v>
+        <v>561.5</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1330</v>
+        <v>1307.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1887.1</v>
+        <v>1928</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>512.05</v>
+        <v>505</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4057</v>
+        <v>4061.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>318.4</v>
+        <v>316.65</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3575.3</v>
+        <v>3555.4</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2388</v>
+        <v>2385</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2400</v>
+        <v>2375</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3455.4</v>
+        <v>3406</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>363.6</v>
+        <v>364</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14190</v>
+        <v>14080</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2598.6</v>
+        <v>2640</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>576.75</v>
+        <v>564.6</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3314,7 +3314,7 @@
         <v>50</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1523</v>
+        <v>1518.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1115.1</v>
+        <v>1123.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>154.35</v>
+        <v>155</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2460</v>
+        <v>2421.9</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134405</v>
+        <v>133930</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>134500</v>
+        <v>134000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2892</v>
+        <v>2894.2</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>7609.5</v>
+        <v>8650</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>7600</v>
+        <v>8600</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>349.9</v>
+        <v>345</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1806.5</v>
+        <v>1777</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11759</v>
+        <v>11735</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>240.2</v>
+        <v>237.8</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40355</v>
+        <v>40050</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40500</v>
+        <v>40000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5520</v>
+        <v>5459.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>280.8</v>
+        <v>276.95</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1665</v>
+        <v>1686</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2810</v>
+        <v>2796</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>113.55</v>
+        <v>114.3</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9200</v>
+        <v>9315</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>281.75</v>
+        <v>270.75</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>389.8</v>
+        <v>392</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>366</v>
+        <v>361.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1280</v>
+        <v>1325</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>175.5</v>
+        <v>176.74</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>665.7</v>
+        <v>660</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1879.9</v>
+        <v>1861.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1055</v>
+        <v>1085</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26900</v>
+        <v>26245</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1122.4</v>
+        <v>1141</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3980</v>
+        <v>3952</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2639.7</v>
+        <v>2624.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1940</v>
+        <v>1951</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>493.35</v>
+        <v>489.2</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>406.95</v>
+        <v>399.75</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>666.15</v>
+        <v>663.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1747.8</v>
+        <v>1735.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1096.3</v>
+        <v>1090</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>383</v>
+        <v>378.6</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>192.99</v>
+        <v>189.3</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2413</v>
+        <v>2373</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1650</v>
+        <v>1632.2</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4912.4</v>
+        <v>4998</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5000</v>
+        <v>4956</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1323.5</v>
+        <v>1325.2</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3129</v>
+        <v>3107.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4455.2</v>
+        <v>4375</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4450</v>
+        <v>4375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1412.6</v>
+        <v>1415.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12190</v>
+        <v>12075</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12200</v>
+        <v>12100</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>175.8</v>
+        <v>182.5</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>577.25</v>
+        <v>572.75</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1300.5</v>
+        <v>1275</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>186.99</v>
+        <v>186.12</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1121.1</v>
+        <v>1108</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  06-Aug-2026 15:16</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  07-Aug-2026 14:14</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>501.2</v>
+        <v>502.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7735</v>
+        <v>7600</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7750</v>
+        <v>7600</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27855</v>
+        <v>27835</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>421.5</v>
+        <v>408.05</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.26</v>
+        <v>63.33</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1378.4</v>
+        <v>1362.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3026</v>
+        <v>3020</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1695</v>
+        <v>1693.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5597.5</v>
+        <v>5620</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>436.5</v>
+        <v>434</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>297.1</v>
+        <v>292</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8974.5</v>
+        <v>8945</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>449.7</v>
+        <v>445</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2755</v>
+        <v>2735</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>660.25</v>
+        <v>657.55</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1588.9</v>
+        <v>1658</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1087.6</v>
+        <v>1067</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1256</v>
+        <v>1238</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11620</v>
+        <v>11662</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2086</v>
+        <v>2008.9</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1144.8</v>
+        <v>1078</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2465.7</v>
+        <v>2466.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174.66</v>
+        <v>176.02</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>251</v>
+        <v>250.7</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>399.2</v>
+        <v>401</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>537.6</v>
+        <v>530.55</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1948</v>
+        <v>1959.9</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>408.15</v>
+        <v>405.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>436.6</v>
+        <v>426.35</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>42000</v>
+        <v>42950</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>323.7</v>
+        <v>321</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5404</v>
+        <v>5510</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.7</v>
+        <v>131.95</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1940</v>
+        <v>1866.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1950</v>
+        <v>1875</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1477</v>
+        <v>1463.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>415.6</v>
+        <v>415.25</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1772.8</v>
+        <v>1776</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2028.4</v>
+        <v>2030</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>512</v>
+        <v>505.2</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>270</v>
+        <v>249.95</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5402</v>
+        <v>5426</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5450</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>411.3</v>
+        <v>410</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1750.4</v>
+        <v>1796.5</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8349</v>
+        <v>8275</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7967.5</v>
+        <v>8020</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>474.25</v>
+        <v>490</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>353.55</v>
+        <v>356.25</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>176.4</v>
+        <v>173.63</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2270</v>
+        <v>2279.1</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1077.3</v>
+        <v>1050</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2081.9</v>
+        <v>2070</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>838.65</v>
+        <v>873.85</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3220</v>
+        <v>3323</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3225</v>
+        <v>3325</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>272.55</v>
+        <v>275.6</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4920</v>
+        <v>4910</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1285.5</v>
+        <v>1288</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1335</v>
+        <v>1356.6</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2538.1</v>
+        <v>2545</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>734.3</v>
+        <v>731</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>542.5</v>
+        <v>540</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5550.5</v>
+        <v>5725</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5550</v>
+        <v>5700</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1027</v>
+        <v>1059.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>545.95</v>
+        <v>536.1</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>395</v>
+        <v>393.05</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2079.5</v>
+        <v>2096</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.34999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>128.83</v>
+        <v>127.1</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>154.33</v>
+        <v>151.94</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1763.5</v>
+        <v>1755</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5318.5</v>
+        <v>5333</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5300</v>
+        <v>5350</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1016.2</v>
+        <v>1022</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>383.3</v>
+        <v>386</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1165</v>
+        <v>1175.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142.66</v>
+        <v>143.38</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>520.45</v>
+        <v>519.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>285.9</v>
+        <v>286.1</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>561.5</v>
+        <v>564.4</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1307.9</v>
+        <v>1299.5</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>473</v>
+        <v>486.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>394</v>
+        <v>390.75</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>623</v>
+        <v>629.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1928</v>
+        <v>1931.6</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1830</v>
+        <v>1844.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1830</v>
+        <v>1845</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>505</v>
+        <v>504.25</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4061.8</v>
+        <v>4056</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>316.65</v>
+        <v>308</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3555.4</v>
+        <v>3598.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2385</v>
+        <v>2363.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3406</v>
+        <v>3502</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>364</v>
+        <v>366.75</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14080</v>
+        <v>14037</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>564.6</v>
+        <v>563.2</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1518.8</v>
+        <v>1497.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1123.7</v>
+        <v>1139.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>155</v>
+        <v>168.5</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2421.9</v>
+        <v>2475</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133930</v>
+        <v>134190</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2894.2</v>
+        <v>2890</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1240</v>
+        <v>1225.3</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8650</v>
+        <v>8271</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8600</v>
+        <v>8300</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1535</v>
+        <v>1540</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>86.2</v>
+        <v>84.92</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>345</v>
+        <v>342.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11735</v>
+        <v>11805</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>237.8</v>
+        <v>238.85</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>40050</v>
+        <v>39900</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5459.5</v>
+        <v>5475</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>276.95</v>
+        <v>280.6</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1686</v>
+        <v>1660</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2796</v>
+        <v>2774.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>114.3</v>
+        <v>114.81</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9315</v>
+        <v>9218</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>270.75</v>
+        <v>271.6</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>392</v>
+        <v>389.8</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>361.5</v>
+        <v>367</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1325</v>
+        <v>1334.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>176.74</v>
+        <v>176.58</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1861.5</v>
+        <v>1855.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1085</v>
+        <v>1097.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26245</v>
+        <v>26010</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1141</v>
+        <v>1115</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3952</v>
+        <v>3940.1</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2624.9</v>
+        <v>2615</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1951</v>
+        <v>1945</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>489.2</v>
+        <v>486.65</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>399.75</v>
+        <v>403.7</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>663.3</v>
+        <v>673.55</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1735.5</v>
+        <v>1755.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1090</v>
+        <v>1082.3</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>378.6</v>
+        <v>380.55</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>189.3</v>
+        <v>187.55</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2373</v>
+        <v>2452.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>2450</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1632.2</v>
+        <v>1635</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4998</v>
+        <v>4941</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4956</v>
+        <v>4924</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1325.2</v>
+        <v>1350.8</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3107.1</v>
+        <v>2997</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4375</v>
+        <v>4440.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4375</v>
+        <v>4450</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1415.3</v>
+        <v>1400.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12075</v>
+        <v>12105</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>182.5</v>
+        <v>183.6</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>572.75</v>
+        <v>573</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>275</v>
+        <v>278.85</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>186.12</v>
+        <v>187.53</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1108</v>
+        <v>1114.2</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  07-Aug-2026 14:14</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  10-Aug-2026 14:21</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>502.1</v>
+        <v>500.55</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7600</v>
+        <v>7649.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7600</v>
+        <v>7650</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27835</v>
+        <v>27535</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27800</v>
+        <v>27600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>408.05</v>
+        <v>407.75</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>63.33</v>
+        <v>61.04</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1362.8</v>
+        <v>1357.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1693.5</v>
+        <v>1681</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5620</v>
+        <v>5598.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>434</v>
+        <v>430.85</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>292</v>
+        <v>294.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8945</v>
+        <v>8912</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>445</v>
+        <v>445.95</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>177.5</v>
+        <v>174</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2735</v>
+        <v>2750</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1444</v>
+        <v>1437</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>657.55</v>
+        <v>660.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1658</v>
+        <v>1648</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1238</v>
+        <v>1247.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11662</v>
+        <v>11677</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2008.9</v>
+        <v>2021.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1078</v>
+        <v>1102.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2466.3</v>
+        <v>2524.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>176.02</v>
+        <v>172.62</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>250.7</v>
+        <v>247.81</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>401</v>
+        <v>404.35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>530.55</v>
+        <v>542.1</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1959.9</v>
+        <v>1943</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>405.2</v>
+        <v>409</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>426.35</v>
+        <v>426.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>42950</v>
+        <v>43505</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>43000</v>
+        <v>43600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>321</v>
+        <v>318.5</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5510</v>
+        <v>5623.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.95</v>
+        <v>129</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1866.2</v>
+        <v>1920</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1875</v>
+        <v>1925</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1463.8</v>
+        <v>1467.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>415.25</v>
+        <v>411</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1776</v>
+        <v>1810</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2030</v>
+        <v>2019.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>505.2</v>
+        <v>501.9</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>249.95</v>
+        <v>247.55</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5426</v>
+        <v>5448</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>410</v>
+        <v>414.2</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1796.5</v>
+        <v>1779.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8275</v>
+        <v>8300</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14200</v>
+        <v>14115</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1172</v>
+        <v>1158.8</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8020</v>
+        <v>7975</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3080</v>
+        <v>3082.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>490</v>
+        <v>485.4</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>356.25</v>
+        <v>358.35</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.63</v>
+        <v>172.5</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2279.1</v>
+        <v>2251.3</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2275</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1050</v>
+        <v>1033</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2070</v>
+        <v>2108.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>873.85</v>
+        <v>855.15</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>875</v>
+        <v>855</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3323</v>
+        <v>3380.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3325</v>
+        <v>3375</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>275.6</v>
+        <v>265.3</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4910</v>
+        <v>4928</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1356.6</v>
+        <v>1357.2</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2545</v>
+        <v>2560</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5725</v>
+        <v>5860</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5700</v>
+        <v>5850</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1059.6</v>
+        <v>1054.05</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>536.1</v>
+        <v>526.25</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>393.05</v>
+        <v>393.15</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2096</v>
+        <v>2087.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.62</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>127.1</v>
+        <v>126.3</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.94</v>
+        <v>152.15</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>731</v>
+        <v>728.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1755</v>
+        <v>1782.7</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5333</v>
+        <v>5333.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1022</v>
+        <v>1027.3</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1175.1</v>
+        <v>1183</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>143.38</v>
+        <v>142</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>519.95</v>
+        <v>522.25</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>286.1</v>
+        <v>282.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1103</v>
+        <v>1125</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>564.4</v>
+        <v>578</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1299.5</v>
+        <v>1302</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>486.5</v>
+        <v>495</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>390.75</v>
+        <v>393.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>629.9</v>
+        <v>627.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1931.6</v>
+        <v>1954</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1844.3</v>
+        <v>1854</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>504.25</v>
+        <v>500</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4056</v>
+        <v>4080</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>308</v>
+        <v>312.85</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3598.7</v>
+        <v>3583.4</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2363.5</v>
+        <v>2300</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2375</v>
+        <v>2300</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3502</v>
+        <v>3517</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>366.75</v>
+        <v>369.3</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>862</v>
+        <v>863.5</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14037</v>
+        <v>14097</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>14000</v>
+        <v>14100</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2638</v>
+        <v>2759.3</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2650</v>
+        <v>2750</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>563.2</v>
+        <v>572.65</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1497.4</v>
+        <v>1514.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1139.6</v>
+        <v>1123.6</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>168.5</v>
+        <v>167.99</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2475</v>
+        <v>2508</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134190</v>
+        <v>133850</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2890</v>
+        <v>2906</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>381</v>
+        <v>382.7</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1225.3</v>
+        <v>1282</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8271</v>
+        <v>8196.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1540</v>
+        <v>1528.6</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>84.92</v>
+        <v>85.48</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>342.5</v>
+        <v>340.45</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1775</v>
+        <v>1793</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11805</v>
+        <v>11890</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.85</v>
+        <v>239.84</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>39900</v>
+        <v>38660</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>40000</v>
+        <v>38500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5475</v>
+        <v>5474</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>280.6</v>
+        <v>280</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>420</v>
+        <v>385.15</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1660</v>
+        <v>1685</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2774.6</v>
+        <v>2751.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>114.81</v>
+        <v>113.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9218</v>
+        <v>9275</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>271.6</v>
+        <v>270.1</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>389.8</v>
+        <v>391</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>367</v>
+        <v>343.75</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1334.8</v>
+        <v>1327.3</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>176.58</v>
+        <v>172.45</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1855.5</v>
+        <v>1855</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1097.2</v>
+        <v>1071</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1100</v>
+        <v>1070</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26010</v>
+        <v>26100</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1115</v>
+        <v>1137.8</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3940.1</v>
+        <v>3914.3</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2615</v>
+        <v>2610</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1945</v>
+        <v>1944.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>486.65</v>
+        <v>487.8</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>403.7</v>
+        <v>402.6</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>673.55</v>
+        <v>668.9</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1755.2</v>
+        <v>1739.4</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1082.3</v>
+        <v>1108.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1080</v>
+        <v>1110</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>380.55</v>
+        <v>382</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>187.55</v>
+        <v>190.24</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2452.7</v>
+        <v>2425.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4941</v>
+        <v>5090</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4950</v>
+        <v>5100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1350.8</v>
+        <v>1342.9</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2997</v>
+        <v>3025</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4440.9</v>
+        <v>4466.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4450</v>
+        <v>4475</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1400.3</v>
+        <v>1382.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12105</v>
+        <v>12038</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12100</v>
+        <v>12000</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>183.6</v>
+        <v>181.14</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>278.85</v>
+        <v>283.65</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1285</v>
+        <v>1267.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>187.53</v>
+        <v>185.5</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1114.2</v>
+        <v>1119</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  10-Aug-2026 14:21</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  11-Aug-2026 14:21</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>500.55</v>
+        <v>505.3</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7649.5</v>
+        <v>7611.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7650</v>
+        <v>7600</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27535</v>
+        <v>28020</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>407.75</v>
+        <v>407.15</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>61.04</v>
+        <v>58.63</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1357.6</v>
+        <v>1339.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3010</v>
+        <v>2995.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1681</v>
+        <v>1668.2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5598.5</v>
+        <v>5527.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>430.85</v>
+        <v>424</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>294.8</v>
+        <v>291.4</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8912</v>
+        <v>8750.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>445.95</v>
+        <v>443</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>174</v>
+        <v>174.83</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2750</v>
+        <v>2735.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1437</v>
+        <v>1424.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>660.1</v>
+        <v>666.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1648</v>
+        <v>1658</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1068</v>
+        <v>1070.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1247.3</v>
+        <v>1229.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11677</v>
+        <v>11717</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2021.3</v>
+        <v>2032</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1102.2</v>
+        <v>1093.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2524.6</v>
+        <v>2498.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>172.62</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>247.81</v>
+        <v>246.2</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>404.35</v>
+        <v>405.85</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>542.1</v>
+        <v>534.95</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1943</v>
+        <v>1915.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>426.1</v>
+        <v>426</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>43505</v>
+        <v>45185</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>43600</v>
+        <v>45200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>318.5</v>
+        <v>317.8</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5623.5</v>
+        <v>5598</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129</v>
+        <v>130.3</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1920</v>
+        <v>1914.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1467.7</v>
+        <v>1463</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>411</v>
+        <v>412.6</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2019.5</v>
+        <v>2008</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>501.9</v>
+        <v>512</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>247.55</v>
+        <v>245.4</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5448</v>
+        <v>5378.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>414.2</v>
+        <v>412.65</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1779.2</v>
+        <v>1784.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8300</v>
+        <v>8578.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8300</v>
+        <v>8600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14115</v>
+        <v>14023</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>660</v>
+        <v>650.1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1158.8</v>
+        <v>1205</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7975</v>
+        <v>8000</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3082.1</v>
+        <v>3107</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>485.4</v>
+        <v>483.35</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>358.35</v>
+        <v>354.55</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172.5</v>
+        <v>175.34</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2251.3</v>
+        <v>2276</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2108.4</v>
+        <v>2037.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>855.15</v>
+        <v>861</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3380.5</v>
+        <v>3322.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3375</v>
+        <v>3325</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>265.3</v>
+        <v>265.45</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4928</v>
+        <v>4909</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1285</v>
+        <v>1274.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1357.2</v>
+        <v>1365.4</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2560</v>
+        <v>2515</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5860</v>
+        <v>5865.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1054.05</v>
+        <v>1049.1</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>526.25</v>
+        <v>533.3</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>393.15</v>
+        <v>390.85</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2087.2</v>
+        <v>2064.9</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.09999999999999</v>
+        <v>84.27</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126.3</v>
+        <v>126</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>152.15</v>
+        <v>153.07</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>728.7</v>
+        <v>724</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1782.7</v>
+        <v>1784.3</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5333.5</v>
+        <v>5284</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1027.3</v>
+        <v>1008.9</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>368</v>
+        <v>369.35</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1183</v>
+        <v>1190.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>522.25</v>
+        <v>515.05</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>282.65</v>
+        <v>279</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1125</v>
+        <v>1095</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1302</v>
+        <v>1283.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>495</v>
+        <v>488.2</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>393.5</v>
+        <v>392.9</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>627.9</v>
+        <v>627</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1954</v>
+        <v>1949.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1854</v>
+        <v>1858</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1855</v>
+        <v>1860</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4080</v>
+        <v>4037.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>312.85</v>
+        <v>315.4</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3583.4</v>
+        <v>3652.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2300</v>
+        <v>2278.9</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2300</v>
+        <v>2275</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3517</v>
+        <v>3460.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>369.3</v>
+        <v>360</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>863.5</v>
+        <v>855</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>14097</v>
+        <v>13990</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2759.3</v>
+        <v>2895</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2750</v>
+        <v>2900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>572.65</v>
+        <v>566.25</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1514.5</v>
+        <v>1499</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1123.6</v>
+        <v>1134.3</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>167.99</v>
+        <v>169.26</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2508</v>
+        <v>2530</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2500</v>
+        <v>2550</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133850</v>
+        <v>131125</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>134000</v>
+        <v>131000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2906</v>
+        <v>2915.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2900</v>
+        <v>2925</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>382.7</v>
+        <v>388</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1282</v>
+        <v>1360</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8196.5</v>
+        <v>8156</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1528.6</v>
+        <v>1493.2</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.48</v>
+        <v>85.45</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>340.45</v>
+        <v>338.45</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1793</v>
+        <v>1793.6</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11890</v>
+        <v>11896</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>239.84</v>
+        <v>239.45</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38660</v>
+        <v>38440</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5474</v>
+        <v>5536</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>385.15</v>
+        <v>381</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1685</v>
+        <v>1685.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2751.6</v>
+        <v>2730</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>113.5</v>
+        <v>114.03</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9275</v>
+        <v>9125</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9300</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>270.1</v>
+        <v>267.95</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>391</v>
+        <v>389.7</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>343.75</v>
+        <v>344.7</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1327.3</v>
+        <v>1323.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>172.45</v>
+        <v>173</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>655</v>
+        <v>650.05</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1855</v>
+        <v>1837.6</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>26100</v>
+        <v>25510</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>26000</v>
+        <v>25500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1137.8</v>
+        <v>1129.9</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3914.3</v>
+        <v>4011</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2610</v>
+        <v>2570</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1944.4</v>
+        <v>1942</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>487.8</v>
+        <v>483.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>402.6</v>
+        <v>407.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>668.9</v>
+        <v>668.75</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1739.4</v>
+        <v>1746.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1108.7</v>
+        <v>1078</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1110</v>
+        <v>1080</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>190.24</v>
+        <v>188.25</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2425.7</v>
+        <v>2445.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5090</v>
+        <v>5128</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5100</v>
+        <v>5150</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4924</v>
+        <v>4886</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1342.9</v>
+        <v>1330.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3025</v>
+        <v>3000</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4466.2</v>
+        <v>4400</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4475</v>
+        <v>4400</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1382.8</v>
+        <v>1400</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>12038</v>
+        <v>11780</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>12000</v>
+        <v>11800</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>181.14</v>
+        <v>182.5</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>283.65</v>
+        <v>275</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1267.9</v>
+        <v>1280</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>185.5</v>
+        <v>184.6</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1119</v>
+        <v>1191</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1125</v>
+        <v>1200</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  11-Aug-2026 14:21</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  12-Aug-2026 14:22</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>505.3</v>
+        <v>530.9</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7611.5</v>
+        <v>7710</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28020</v>
+        <v>28140</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28000</v>
+        <v>28200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>407.15</v>
+        <v>410.95</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58.63</v>
+        <v>57.16</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1339.8</v>
+        <v>1332.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2995.5</v>
+        <v>2985.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1668.2</v>
+        <v>1665</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5527.5</v>
+        <v>5480</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>291.4</v>
+        <v>291</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8750.5</v>
+        <v>8597</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8600</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>443</v>
+        <v>445.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>174.83</v>
+        <v>176.7</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2735.5</v>
+        <v>2740</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1424.9</v>
+        <v>1464</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1425</v>
+        <v>1475</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>666.15</v>
+        <v>660.35</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1070.9</v>
+        <v>1091.4</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1229.8</v>
+        <v>1230</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11717</v>
+        <v>11700</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2032</v>
+        <v>2020.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1093.3</v>
+        <v>1094.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2498.9</v>
+        <v>2496.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>246.2</v>
+        <v>251</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405.85</v>
+        <v>405.7</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>534.95</v>
+        <v>559.8</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1915.2</v>
+        <v>1945</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>426</v>
+        <v>427.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>45185</v>
+        <v>46480</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>45200</v>
+        <v>46400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>317.8</v>
+        <v>317</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5598</v>
+        <v>5645.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5600</v>
+        <v>5650</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>130.3</v>
+        <v>132</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1914.4</v>
+        <v>1917.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>412.6</v>
+        <v>409.3</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1819</v>
+        <v>1801.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>512</v>
+        <v>512.05</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>245.4</v>
+        <v>247.85</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5378.5</v>
+        <v>5365</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>412.65</v>
+        <v>411.25</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1784.8</v>
+        <v>1718.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8578.5</v>
+        <v>8600</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14023</v>
+        <v>13800</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14000</v>
+        <v>13800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>650.1</v>
+        <v>661.75</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8000</v>
+        <v>8049</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3107</v>
+        <v>3126</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>483.35</v>
+        <v>490.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>354.55</v>
+        <v>356.85</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.34</v>
+        <v>177.95</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2276</v>
+        <v>2290</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2275</v>
+        <v>2300</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1025</v>
+        <v>910</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>1025</v>
+        <v>900</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2037.9</v>
+        <v>2015</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>861</v>
+        <v>864.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3322.2</v>
+        <v>3307.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3325</v>
+        <v>3300</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>265.45</v>
+        <v>274.4</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4909</v>
+        <v>4995</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1274.4</v>
+        <v>1265</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2515</v>
+        <v>2490</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5865.5</v>
+        <v>5895</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5850</v>
+        <v>5900</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1049.1</v>
+        <v>1078.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>533.3</v>
+        <v>547.7</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>390.85</v>
+        <v>390</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2064.9</v>
+        <v>2063</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.27</v>
+        <v>85.8</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>126</v>
+        <v>125.95</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>153.07</v>
+        <v>154.54</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1784.3</v>
+        <v>1784.6</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5284</v>
+        <v>5333</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5300</v>
+        <v>5350</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1008.9</v>
+        <v>1017.5</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>369.35</v>
+        <v>383.4</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1190.7</v>
+        <v>1176.1</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140</v>
+        <v>140.6</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>515.05</v>
+        <v>513.55</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>279</v>
+        <v>276.15</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>563</v>
+        <v>558.75</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1283.4</v>
+        <v>1269.1</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>488.2</v>
+        <v>484.7</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>392.9</v>
+        <v>390.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>627</v>
+        <v>609.2</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1949.9</v>
+        <v>1953.3</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1858</v>
+        <v>1850</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4037.4</v>
+        <v>4020</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4000</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>315.4</v>
+        <v>317.2</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3652.7</v>
+        <v>3578.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2278.9</v>
+        <v>2281</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3460.1</v>
+        <v>3403.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>360</v>
+        <v>352.6</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13990</v>
+        <v>13875</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>14000</v>
+        <v>13900</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2895</v>
+        <v>2970.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2900</v>
+        <v>2975</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>566.25</v>
+        <v>552.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1499</v>
+        <v>1516</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1134.3</v>
+        <v>1118.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>169.26</v>
+        <v>169.5</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2530</v>
+        <v>2537.6</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>131125</v>
+        <v>130785</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2915.9</v>
+        <v>2876.3</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2925</v>
+        <v>2875</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1360</v>
+        <v>1339</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8156</v>
+        <v>8356.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1493.2</v>
+        <v>1507</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.45</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>338.45</v>
+        <v>339.45</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1793.6</v>
+        <v>1799.9</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11896</v>
+        <v>11679</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>239.45</v>
+        <v>239.05</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38440</v>
+        <v>38295</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5536</v>
+        <v>5474</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>277</v>
+        <v>279.85</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>381</v>
+        <v>376.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1685.8</v>
+        <v>1701.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2730</v>
+        <v>2483</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2750</v>
+        <v>2500</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>114.03</v>
+        <v>118.98</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9125</v>
+        <v>9289</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>267.95</v>
+        <v>269.45</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>389.7</v>
+        <v>389.8</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>344.7</v>
+        <v>346</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1323.9</v>
+        <v>1329</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>650.05</v>
+        <v>656.6</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1837.6</v>
+        <v>1830</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1066</v>
+        <v>1082</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25510</v>
+        <v>25570</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1129.9</v>
+        <v>1117.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2570</v>
+        <v>2585</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>483.7</v>
+        <v>478.2</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>407.25</v>
+        <v>408.65</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>668.75</v>
+        <v>673.15</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1746.1</v>
+        <v>1736.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1078</v>
+        <v>1061.9</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>380</v>
+        <v>379.45</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>188.25</v>
+        <v>186.2</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2445.7</v>
+        <v>2349.7</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2450</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1643</v>
+        <v>1625</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5128</v>
+        <v>5099</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5150</v>
+        <v>5100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4886</v>
+        <v>4893</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1330.4</v>
+        <v>1319</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3000</v>
+        <v>2987</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4400</v>
+        <v>4375</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4400</v>
+        <v>4375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1400</v>
+        <v>1388.3</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11780</v>
+        <v>11891</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>182.5</v>
+        <v>187</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>568</v>
+        <v>570.5</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>275</v>
+        <v>275.8</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1280</v>
+        <v>1290</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>184.6</v>
+        <v>183.94</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1191</v>
+        <v>1205</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📊 Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📋 Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📊 Summary'!$A$2:$G$2</definedName>
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  12-Aug-2026 14:22</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  13-Aug-2026 14:23</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>530.9</v>
+        <v>538.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>28140</v>
+        <v>27620</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>28200</v>
+        <v>27600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>410.95</v>
+        <v>407.7</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>57.16</v>
+        <v>56.73</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1332.8</v>
+        <v>1324.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2985.7</v>
+        <v>2964.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5480</v>
+        <v>5449.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>421</v>
+        <v>419.4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8597</v>
+        <v>8600</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>445.15</v>
+        <v>443.05</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>176.7</v>
+        <v>176.23</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2740</v>
+        <v>2755.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1464</v>
+        <v>1592</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1475</v>
+        <v>1600</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>660.35</v>
+        <v>655.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1667</v>
+        <v>1663.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1091.4</v>
+        <v>1098</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1230</v>
+        <v>1221.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11700</v>
+        <v>11661</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2020.5</v>
+        <v>2025</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1094.2</v>
+        <v>1090.8</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2496.9</v>
+        <v>2410</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>176</v>
+        <v>175.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405.7</v>
+        <v>410.5</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>559.8</v>
+        <v>546.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1945</v>
+        <v>1939.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>427.4</v>
+        <v>420</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46480</v>
+        <v>46750</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>46400</v>
+        <v>46800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5645.5</v>
+        <v>5615</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>132</v>
+        <v>131.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1917.6</v>
+        <v>1927.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1463</v>
+        <v>1458.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>409.3</v>
+        <v>410.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1801.5</v>
+        <v>1829</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>2005</v>
+        <v>1995.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>512.05</v>
+        <v>533.65</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>247.85</v>
+        <v>248.15</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5365</v>
+        <v>5315</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>411.25</v>
+        <v>410</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1718.4</v>
+        <v>1701.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13800</v>
+        <v>14035</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13800</v>
+        <v>14000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>661.75</v>
+        <v>664</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8049</v>
+        <v>8100</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3126</v>
+        <v>3093.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>490.65</v>
+        <v>485.5</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>356.85</v>
+        <v>352.45</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>177.95</v>
+        <v>175.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2290</v>
+        <v>2320</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2300</v>
+        <v>2325</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>910</v>
+        <v>936.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>864.8</v>
+        <v>857.55</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3307.8</v>
+        <v>3257</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3300</v>
+        <v>3250</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>274.4</v>
+        <v>274.35</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4995</v>
+        <v>4945</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1365.4</v>
+        <v>1370</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2490</v>
+        <v>2499.5</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>537</v>
+        <v>538.05</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5895</v>
+        <v>5850</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5900</v>
+        <v>5850</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1078.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>547.7</v>
+        <v>544.45</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>390</v>
+        <v>392.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2063</v>
+        <v>2092</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.8</v>
+        <v>86.55</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.95</v>
+        <v>125.5</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>154.54</v>
+        <v>151.77</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>724</v>
+        <v>721.75</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1784.6</v>
+        <v>1803.6</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5333</v>
+        <v>5370</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1017.5</v>
+        <v>1024.7</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>383.4</v>
+        <v>383.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1176.1</v>
+        <v>1175</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>140.6</v>
+        <v>141.5</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>513.55</v>
+        <v>504.45</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>276.15</v>
+        <v>278.5</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1112</v>
+        <v>1099.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>558.75</v>
+        <v>558.6</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1269.1</v>
+        <v>1275</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>484.7</v>
+        <v>491.55</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>390.5</v>
+        <v>392.4</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>609.2</v>
+        <v>620.5</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1953.3</v>
+        <v>1968.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1850</v>
+        <v>1851.7</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4020</v>
+        <v>4070.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>317.2</v>
+        <v>315.35</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3578.9</v>
+        <v>3604.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2281</v>
+        <v>2250.3</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2275</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3403.6</v>
+        <v>3428.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3400</v>
+        <v>3450</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>352.6</v>
+        <v>348.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>855</v>
+        <v>864.45</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13875</v>
+        <v>13905</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2970.1</v>
+        <v>2970</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>552.4</v>
+        <v>558.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1516</v>
+        <v>1512.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1118.5</v>
+        <v>1125.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>169.5</v>
+        <v>167.4</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2537.6</v>
+        <v>2541</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130785</v>
+        <v>130985</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2876.3</v>
+        <v>2875.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>420</v>
+        <v>400.5</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1339</v>
+        <v>1357.3</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8356.5</v>
+        <v>8294</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1507</v>
+        <v>1506.9</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>339.45</v>
+        <v>344.25</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1799.9</v>
+        <v>1846</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1800</v>
+        <v>1850</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11679</v>
+        <v>11420</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11700</v>
+        <v>11400</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>239.05</v>
+        <v>239.9</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>38295</v>
+        <v>36520</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>38500</v>
+        <v>36500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5474</v>
+        <v>5523</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>279.85</v>
+        <v>279.3</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>376.5</v>
+        <v>378.95</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1701.5</v>
+        <v>1696.1</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2483</v>
+        <v>2494.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>118.98</v>
+        <v>117.59</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9289</v>
+        <v>9297</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>269.45</v>
+        <v>266.6</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>389.8</v>
+        <v>387.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>346</v>
+        <v>346.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1329</v>
+        <v>1317</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4043,7 +4043,7 @@
         <v>50</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1350</v>
+        <v>1300</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>174</v>
+        <v>168.68</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>656.6</v>
+        <v>641</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1830</v>
+        <v>1812</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25570</v>
+        <v>25245</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1117.2</v>
+        <v>1132.3</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4019</v>
+        <v>3987</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2585</v>
+        <v>2608.7</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1944</v>
+        <v>1932</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>478.2</v>
+        <v>487.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>408.65</v>
+        <v>401.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>673.15</v>
+        <v>672.05</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1736.2</v>
+        <v>1758.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1061.9</v>
+        <v>1090.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>379.45</v>
+        <v>382.8</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>186.2</v>
+        <v>184.85</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2349.7</v>
+        <v>2375</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5099</v>
+        <v>5063.7</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4893</v>
+        <v>4914.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2987</v>
+        <v>2990</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4375</v>
+        <v>4342.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4375</v>
+        <v>4350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1388.3</v>
+        <v>1389.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11891</v>
+        <v>11706</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>187</v>
+        <v>186.5</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>570.5</v>
+        <v>568.15</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>275.8</v>
+        <v>271.1</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1290</v>
+        <v>1289.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>183.94</v>
+        <v>183.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1205</v>
+        <v>1167.3</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1200</v>
+        <v>1175</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  13-Aug-2026 14:23</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  14-Aug-2026 14:17</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>538.2</v>
+        <v>534.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7710</v>
+        <v>7649</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7700</v>
+        <v>7650</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27620</v>
+        <v>27060</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27600</v>
+        <v>27000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>407.7</v>
+        <v>401</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>56.73</v>
+        <v>55.98</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1324.7</v>
+        <v>1321.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2964.9</v>
+        <v>3035.1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1658</v>
+        <v>1700</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5449.5</v>
+        <v>5368</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>419.4</v>
+        <v>417.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>292</v>
+        <v>287.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8600</v>
+        <v>8920.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8600</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>443.05</v>
+        <v>444.1</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>176.23</v>
+        <v>171.64</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2755.5</v>
+        <v>2696.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1592</v>
+        <v>1556.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>655.05</v>
+        <v>654.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1663.4</v>
+        <v>1622.1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1675</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1098</v>
+        <v>1081.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1221.8</v>
+        <v>1217.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11661</v>
+        <v>11700</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2025</v>
+        <v>2008.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1090.8</v>
+        <v>1087</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2410</v>
+        <v>2363.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>175.9</v>
+        <v>174.55</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>248</v>
+        <v>248.22</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>410.5</v>
+        <v>410.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>546.35</v>
+        <v>545.1</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1939.1</v>
+        <v>1992.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>420</v>
+        <v>421.7</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46750</v>
+        <v>47100</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>46800</v>
+        <v>47200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>315</v>
+        <v>319.45</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5615</v>
+        <v>5558</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5600</v>
+        <v>5550</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.8</v>
+        <v>131.25</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1927.9</v>
+        <v>1894.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1458.8</v>
+        <v>1450</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>410.5</v>
+        <v>407.1</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1829</v>
+        <v>1812</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1995.5</v>
+        <v>1981</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>533.65</v>
+        <v>527</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>248.15</v>
+        <v>248.3</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5315</v>
+        <v>5400</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>410</v>
+        <v>405.25</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1701.8</v>
+        <v>1723.2</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8500</v>
+        <v>8477</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14035</v>
+        <v>14130</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14000</v>
+        <v>14100</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8100</v>
+        <v>8066.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3093.4</v>
+        <v>3113.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>485.5</v>
+        <v>476.1</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>352.45</v>
+        <v>351.3</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.9</v>
+        <v>174.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2320</v>
+        <v>2318.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>936.9</v>
+        <v>934.3</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2028</v>
+        <v>1990</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>857.55</v>
+        <v>858.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3257</v>
+        <v>3248.7</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>274.35</v>
+        <v>284.4</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4945</v>
+        <v>5029.9</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1270</v>
+        <v>1298</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2499.5</v>
+        <v>2485</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>538.05</v>
+        <v>535.85</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5850</v>
+        <v>5790</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5850</v>
+        <v>5800</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1046.25</v>
+        <v>1029.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>544.45</v>
+        <v>529.05</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>392.9</v>
+        <v>373.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2092</v>
+        <v>2077</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>86.55</v>
+        <v>85.69</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.5</v>
+        <v>124.75</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.77</v>
+        <v>151.7</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>721.75</v>
+        <v>720</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1803.6</v>
+        <v>1789.9</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5370</v>
+        <v>5310</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1024.7</v>
+        <v>1020.8</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>383.2</v>
+        <v>384.35</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1175</v>
+        <v>1169.2</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>141.5</v>
+        <v>139.4</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>504.45</v>
+        <v>497.5</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>278.5</v>
+        <v>278.2</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1099.9</v>
+        <v>1091.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>558.6</v>
+        <v>560</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>491.55</v>
+        <v>504.1</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>392.4</v>
+        <v>391.15</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>620.5</v>
+        <v>614</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1968.4</v>
+        <v>1916.3</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -2990,7 +2990,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1851.7</v>
+        <v>1787.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1850</v>
+        <v>1785</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4070.7</v>
+        <v>4057</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>315.35</v>
+        <v>306.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3604.7</v>
+        <v>3476.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2250.3</v>
+        <v>2235</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2225</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3428.2</v>
+        <v>3428.3</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>348.4</v>
+        <v>349</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>864.45</v>
+        <v>865.2</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13905</v>
+        <v>13834</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13900</v>
+        <v>13800</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2970</v>
+        <v>2911.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2975</v>
+        <v>2900</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>558.5</v>
+        <v>545.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1512.4</v>
+        <v>1538.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1125.8</v>
+        <v>1138.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>167.4</v>
+        <v>168.3</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2541</v>
+        <v>2545</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>130985</v>
+        <v>133490</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>131000</v>
+        <v>133500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2875.7</v>
+        <v>2842</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2875</v>
+        <v>2850</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>400.5</v>
+        <v>376</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1357.3</v>
+        <v>1343</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8294</v>
+        <v>8235</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1506.9</v>
+        <v>1499.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>344.25</v>
+        <v>340</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11420</v>
+        <v>11828</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11400</v>
+        <v>11800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>239.9</v>
+        <v>236.4</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36520</v>
+        <v>36750</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>36500</v>
+        <v>37000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5523</v>
+        <v>5580</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>279.3</v>
+        <v>282.6</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>378.95</v>
+        <v>376</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1696.1</v>
+        <v>1693</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2494.3</v>
+        <v>2490.1</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>117.59</v>
+        <v>118</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9297</v>
+        <v>9240</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>266.6</v>
+        <v>266.05</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>387.25</v>
+        <v>385</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>346.5</v>
+        <v>335</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1317</v>
+        <v>1310</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>168.68</v>
+        <v>169.51</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1812</v>
+        <v>1795</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1083</v>
+        <v>1067.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>25245</v>
+        <v>24795</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1132.3</v>
+        <v>1122</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3987</v>
+        <v>3940</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2608.7</v>
+        <v>2606</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>487.9</v>
+        <v>484.6</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>401.3</v>
+        <v>401.45</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>672.05</v>
+        <v>670.65</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1758.2</v>
+        <v>1718.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1090.5</v>
+        <v>1079.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>382.8</v>
+        <v>382.05</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>184.85</v>
+        <v>183.5</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2375</v>
+        <v>2361</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1639</v>
+        <v>1632.8</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5063.7</v>
+        <v>5056.2</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4914.5</v>
+        <v>4833</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1318</v>
+        <v>1309.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2990</v>
+        <v>2978</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4342.2</v>
+        <v>4307</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4350</v>
+        <v>4300</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1389.7</v>
+        <v>1376.6</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11706</v>
+        <v>11619</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>186.5</v>
+        <v>187.38</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>568.15</v>
+        <v>563</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>271.1</v>
+        <v>267.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1289.5</v>
+        <v>1320.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>183.1</v>
+        <v>184</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1167.3</v>
+        <v>1135.2</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  14-Aug-2026 14:17</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  17-Aug-2026 13:42</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>534.1</v>
+        <v>526.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7649</v>
+        <v>7660</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27060</v>
+        <v>26905</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>401</v>
+        <v>398.7</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>55.98</v>
+        <v>55.29</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1321.4</v>
+        <v>1316.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3035.1</v>
+        <v>3007.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1700</v>
+        <v>1691</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5368</v>
+        <v>5374</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>417.5</v>
+        <v>415.25</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>287.3</v>
+        <v>293.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8920.5</v>
+        <v>8825.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>444.1</v>
+        <v>436.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>171.64</v>
+        <v>177.1</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2696.3</v>
+        <v>2687.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1556.3</v>
+        <v>1538.3</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>654.05</v>
+        <v>646.9</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1622.1</v>
+        <v>1627.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1081.9</v>
+        <v>1072.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1217.4</v>
+        <v>1227.3</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11700</v>
+        <v>11663</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2008.3</v>
+        <v>2005</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1087</v>
+        <v>1089.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2363.6</v>
+        <v>2407.2</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174.55</v>
+        <v>173.25</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>248.22</v>
+        <v>246.55</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>410.8</v>
+        <v>412.45</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>545.1</v>
+        <v>549.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1992.1</v>
+        <v>1969.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>421.7</v>
+        <v>435.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47100</v>
+        <v>46970</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47200</v>
+        <v>47000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>319.45</v>
+        <v>316.65</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5558</v>
+        <v>5521</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5550</v>
+        <v>5500</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.25</v>
+        <v>131.1</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1894.4</v>
+        <v>1884.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1450</v>
+        <v>1431.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>407.1</v>
+        <v>408.45</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1812</v>
+        <v>1806</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1981</v>
+        <v>1964</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>527</v>
+        <v>524.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>248.3</v>
+        <v>246.5</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5400</v>
+        <v>5450</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5400</v>
+        <v>5450</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>405.25</v>
+        <v>406.8</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1723.2</v>
+        <v>1780.5</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8477</v>
+        <v>8481.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14130</v>
+        <v>14025</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1200</v>
+        <v>1192</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8066.5</v>
+        <v>8050</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3113.7</v>
+        <v>3133.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3100</v>
+        <v>3150</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>476.1</v>
+        <v>475.7</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>351.3</v>
+        <v>354.1</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.9</v>
+        <v>172.1</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2318.4</v>
+        <v>2329</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>934.3</v>
+        <v>928</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1990</v>
+        <v>2054</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>858.4</v>
+        <v>861.55</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3248.7</v>
+        <v>3250.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>284.4</v>
+        <v>282.95</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5029.9</v>
+        <v>5059</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1360</v>
+        <v>1325</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1350</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2485</v>
+        <v>2523</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>535.85</v>
+        <v>543</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5790</v>
+        <v>5745</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5800</v>
+        <v>5750</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1029.5</v>
+        <v>1049.9</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1030</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>529.05</v>
+        <v>572.65</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>373.5</v>
+        <v>371</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2077</v>
+        <v>2055</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2100</v>
+        <v>2050</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.69</v>
+        <v>85.05</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.75</v>
+        <v>125.3</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151.7</v>
+        <v>151</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1789.9</v>
+        <v>1770</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5310</v>
+        <v>5275.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1020.8</v>
+        <v>1010.6</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>384.35</v>
+        <v>380</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1169.2</v>
+        <v>1139.9</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>139.4</v>
+        <v>138.61</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>497.5</v>
+        <v>499.95</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>278.2</v>
+        <v>273.05</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2801,7 +2801,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1091.5</v>
+        <v>1116.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>560</v>
+        <v>555.5</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1270</v>
+        <v>1277.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>504.1</v>
+        <v>511.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>391.15</v>
+        <v>392.7</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1916.3</v>
+        <v>1877.3</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1787.3</v>
+        <v>1809.7</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1785</v>
+        <v>1810</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>500</v>
+        <v>498.25</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4057</v>
+        <v>4086.7</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>306.3</v>
+        <v>315</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3476.8</v>
+        <v>3528.5</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2225</v>
+        <v>2250</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3428.3</v>
+        <v>3390.4</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>349</v>
+        <v>348.6</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>865.2</v>
+        <v>852.05</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13834</v>
+        <v>13760</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2911.5</v>
+        <v>2933.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2900</v>
+        <v>2925</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>545.5</v>
+        <v>550.75</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1538.1</v>
+        <v>1571.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1138.7</v>
+        <v>1129.1</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>168.3</v>
+        <v>168.06</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2545</v>
+        <v>2510</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133490</v>
+        <v>133015</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133500</v>
+        <v>133000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2842</v>
+        <v>2888.5</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>376</v>
+        <v>387.55</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1343</v>
+        <v>1355.8</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8235</v>
+        <v>8151</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1499.1</v>
+        <v>1470</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>84.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1846</v>
+        <v>1931</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1850</v>
+        <v>1925</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11828</v>
+        <v>11789</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>236.4</v>
+        <v>238.49</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36750</v>
+        <v>37360</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37000</v>
+        <v>37500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5580</v>
+        <v>5570</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>282.6</v>
+        <v>281.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>376</v>
+        <v>374.4</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1693</v>
+        <v>1669</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2490.1</v>
+        <v>2472</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>118</v>
+        <v>117.32</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9240</v>
+        <v>9370</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>266.05</v>
+        <v>266.15</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>385</v>
+        <v>381.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>169.51</v>
+        <v>173.6</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>633</v>
+        <v>641.75</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1795</v>
+        <v>1790.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1067.7</v>
+        <v>1061.2</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24795</v>
+        <v>24535</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>25000</v>
+        <v>24500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3940</v>
+        <v>3943</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2606</v>
+        <v>2616</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1930</v>
+        <v>1882</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1925</v>
+        <v>1875</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>484.6</v>
+        <v>488.25</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>401.45</v>
+        <v>403</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>670.65</v>
+        <v>662.9</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1718.1</v>
+        <v>1711.9</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1079.5</v>
+        <v>1072.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>382.05</v>
+        <v>381.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>183.5</v>
+        <v>186</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2361</v>
+        <v>2313.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1632.8</v>
+        <v>1610</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5056.2</v>
+        <v>5068.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4833</v>
+        <v>4900</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1309.1</v>
+        <v>1312.8</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2978</v>
+        <v>2946</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4307</v>
+        <v>4385.9</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4300</v>
+        <v>4375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1376.6</v>
+        <v>1367.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11619</v>
+        <v>11681</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>187.38</v>
+        <v>188.9</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>563</v>
+        <v>567.1</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>267.5</v>
+        <v>269.7</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1320.5</v>
+        <v>1267</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1325</v>
+        <v>1275</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>184</v>
+        <v>181.9</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1135.2</v>
+        <v>1131.5</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  17-Aug-2026 13:42</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  18-Aug-2026 13:44</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>526.7</v>
+        <v>530.1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7660</v>
+        <v>7546</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7650</v>
+        <v>7550</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26905</v>
+        <v>26580</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27000</v>
+        <v>26600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>398.7</v>
+        <v>402</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>55.29</v>
+        <v>54.97</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1316.6</v>
+        <v>1303.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3007.3</v>
+        <v>3002.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1691</v>
+        <v>1682.4</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5374</v>
+        <v>5475</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>415.25</v>
+        <v>412.4</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>293.5</v>
+        <v>291.75</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8825.5</v>
+        <v>8817</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>436.7</v>
+        <v>436</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>177.1</v>
+        <v>176.35</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2687.5</v>
+        <v>2628.4</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1538.3</v>
+        <v>1520</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>646.9</v>
+        <v>647.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1627.2</v>
+        <v>1645</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1072.2</v>
+        <v>1075.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1227.3</v>
+        <v>1243</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11663</v>
+        <v>11607</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11700</v>
+        <v>11600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2005</v>
+        <v>2011.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1089.3</v>
+        <v>1094.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2407.2</v>
+        <v>2376.7</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.25</v>
+        <v>170.5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>246.55</v>
+        <v>244</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>412.45</v>
+        <v>412</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>549.35</v>
+        <v>541.2</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1969.3</v>
+        <v>1934.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>435.95</v>
+        <v>425</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>412</v>
+        <v>417.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46970</v>
+        <v>48730</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47000</v>
+        <v>48800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>316.65</v>
+        <v>310.3</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5521</v>
+        <v>5495</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>131.1</v>
+        <v>129.1</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1884.7</v>
+        <v>1868</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1431.5</v>
+        <v>1431.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>408.45</v>
+        <v>406.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1806</v>
+        <v>1773</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1964</v>
+        <v>1903</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1975</v>
+        <v>1900</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>524.5</v>
+        <v>518.25</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>246.5</v>
+        <v>244.8</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5450</v>
+        <v>5350</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5450</v>
+        <v>5350</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>406.8</v>
+        <v>403.5</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1780.5</v>
+        <v>1771</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8481.5</v>
+        <v>8588</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14025</v>
+        <v>14150</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14000</v>
+        <v>14200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>671</v>
+        <v>665.75</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1192</v>
+        <v>1178.8</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8050</v>
+        <v>8018.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3133.6</v>
+        <v>3062.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3150</v>
+        <v>3050</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>475.7</v>
+        <v>465.25</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>354.1</v>
+        <v>357.8</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172.1</v>
+        <v>173.5</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2329</v>
+        <v>2305</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2300</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2054</v>
+        <v>1997.4</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>861.55</v>
+        <v>851.2</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3250.5</v>
+        <v>3278.7</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3250</v>
+        <v>3275</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>282.95</v>
+        <v>276.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5059</v>
+        <v>5099</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1299</v>
+        <v>1299.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1325</v>
+        <v>1298</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>543</v>
+        <v>538.25</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5745</v>
+        <v>5745.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1049.9</v>
+        <v>1041.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>572.65</v>
+        <v>566.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2055</v>
+        <v>2035</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.05</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125.3</v>
+        <v>124.4</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>151</v>
+        <v>149.39</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1770</v>
+        <v>1753.1</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5275.5</v>
+        <v>5220</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1010.6</v>
+        <v>1015</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>380</v>
+        <v>372.4</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1139.9</v>
+        <v>1115</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.61</v>
+        <v>137.8</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>499.95</v>
+        <v>493.05</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>273.05</v>
+        <v>270</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1116.1</v>
+        <v>1101.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>555.5</v>
+        <v>548.1</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1277.8</v>
+        <v>1267.6</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>511.5</v>
+        <v>500.55</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>392.7</v>
+        <v>387.65</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>609</v>
+        <v>596.65</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1877.3</v>
+        <v>1901.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1809.7</v>
+        <v>1814</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>498.25</v>
+        <v>498.8</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4086.7</v>
+        <v>4064.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>315</v>
+        <v>325.1</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3528.5</v>
+        <v>3509.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2259</v>
+        <v>2232</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2250</v>
+        <v>2225</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3390.4</v>
+        <v>3421.5</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>348.6</v>
+        <v>346.6</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>852.05</v>
+        <v>841.55</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13760</v>
+        <v>13691</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13800</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2933.1</v>
+        <v>3040</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2925</v>
+        <v>3050</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>550.75</v>
+        <v>551.95</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1571.7</v>
+        <v>1584.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1129.1</v>
+        <v>1111.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>168.06</v>
+        <v>170.4</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2510</v>
+        <v>2432</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133015</v>
+        <v>133505</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133000</v>
+        <v>133500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2888.5</v>
+        <v>2894.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>387.55</v>
+        <v>388</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1355.8</v>
+        <v>1354.9</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8151</v>
+        <v>8255</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1470</v>
+        <v>1462.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.5</v>
+        <v>84.19</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>337</v>
+        <v>337.1</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1931</v>
+        <v>1858</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1925</v>
+        <v>1850</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11789</v>
+        <v>11623</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.49</v>
+        <v>239.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>37360</v>
+        <v>36425</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>37500</v>
+        <v>36500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5570</v>
+        <v>5442.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5600</v>
+        <v>5400</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>281.8</v>
+        <v>286.25</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>374.4</v>
+        <v>374.45</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1669</v>
+        <v>1674</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2472</v>
+        <v>2515</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3881,7 +3881,7 @@
         <v>50</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>117.32</v>
+        <v>116.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9370</v>
+        <v>9139</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9400</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>266.15</v>
+        <v>268</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>381.5</v>
+        <v>383</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>340</v>
+        <v>338.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>173.6</v>
+        <v>170.2</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>641.75</v>
+        <v>615</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1790.4</v>
+        <v>1778</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1061.2</v>
+        <v>1053</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24535</v>
+        <v>24725</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1122</v>
+        <v>1108.4</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3943</v>
+        <v>3957</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2616</v>
+        <v>2630</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>2650</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1882</v>
+        <v>1875.1</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>488.25</v>
+        <v>482.8</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>403</v>
+        <v>404.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>662.9</v>
+        <v>653</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1711.9</v>
+        <v>1689.8</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1072.6</v>
+        <v>1061.6</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>381.5</v>
+        <v>381</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>186</v>
+        <v>185.5</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2313.2</v>
+        <v>2280</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1610</v>
+        <v>1592</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5068.5</v>
+        <v>5048.6</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4900</v>
+        <v>4971</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1312.8</v>
+        <v>1264.1</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1325</v>
+        <v>1275</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2946</v>
+        <v>2942.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4385.9</v>
+        <v>4356.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4375</v>
+        <v>4350</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1367.9</v>
+        <v>1355.5</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11681</v>
+        <v>11499</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>188.9</v>
+        <v>185.5</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>567.1</v>
+        <v>560.05</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>269.7</v>
+        <v>264</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1267</v>
+        <v>1252.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.9</v>
+        <v>178.06</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1131.5</v>
+        <v>1115.6</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  18-Aug-2026 13:44</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  19-Aug-2026 13:47</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>530.1</v>
+        <v>527.05</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7546</v>
+        <v>7430</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7550</v>
+        <v>7450</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26580</v>
+        <v>26405</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26600</v>
+        <v>26400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.97</v>
+        <v>54.47</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1303.8</v>
+        <v>1288.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3002.5</v>
+        <v>2990.3</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1682.4</v>
+        <v>1681.9</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5475</v>
+        <v>5382.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>412.4</v>
+        <v>407.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>291.75</v>
+        <v>289.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8817</v>
+        <v>8750</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>436</v>
+        <v>427.35</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>176.35</v>
+        <v>173.1</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2628.4</v>
+        <v>2630.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1520</v>
+        <v>1544.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>647.3</v>
+        <v>664.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1645</v>
+        <v>1624.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1075.7</v>
+        <v>1075</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11607</v>
+        <v>11645</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2011.2</v>
+        <v>2012</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1094.3</v>
+        <v>1080.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2376.7</v>
+        <v>2366.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>170.5</v>
+        <v>169.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>412</v>
+        <v>409.2</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>541.2</v>
+        <v>535.9</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1934.2</v>
+        <v>1922</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>425</v>
+        <v>419.8</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>417.5</v>
+        <v>412.75</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48730</v>
+        <v>48460</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48800</v>
+        <v>48400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>310.3</v>
+        <v>307</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5495</v>
+        <v>5453</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5500</v>
+        <v>5450</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.1</v>
+        <v>129.08</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1868</v>
+        <v>1873.5</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1431.1</v>
+        <v>1422</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>406.9</v>
+        <v>400</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1773</v>
+        <v>1813.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1903</v>
+        <v>1879.6</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>518.25</v>
+        <v>514.35</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>244.8</v>
+        <v>245.5</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5350</v>
+        <v>5220</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5350</v>
+        <v>5200</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>403.5</v>
+        <v>399.75</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1771</v>
+        <v>1768.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8588</v>
+        <v>8560</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14150</v>
+        <v>14462</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14200</v>
+        <v>14500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>665.75</v>
+        <v>669.9</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1178.8</v>
+        <v>1170</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8018.5</v>
+        <v>7990.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3062.1</v>
+        <v>3054.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>465.25</v>
+        <v>459.5</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>357.8</v>
+        <v>358.8</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.5</v>
+        <v>172.5</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2305</v>
+        <v>2246.5</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1997.4</v>
+        <v>2007.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>851.2</v>
+        <v>841.15</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3278.7</v>
+        <v>3270</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>276.5</v>
+        <v>269.4</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5099</v>
+        <v>5017</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1299.7</v>
+        <v>1287</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1298</v>
+        <v>1324.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2525</v>
+        <v>2551.7</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>538.25</v>
+        <v>536.3</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5745.5</v>
+        <v>5709.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5750</v>
+        <v>5700</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1041.6</v>
+        <v>1038.95</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>566.35</v>
+        <v>554.85</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>366</v>
+        <v>366.45</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2035</v>
+        <v>2020.7</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.76000000000001</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.4</v>
+        <v>123</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>149.39</v>
+        <v>152.64</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>719</v>
+        <v>723.35</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1753.1</v>
+        <v>1734.3</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5220</v>
+        <v>5193</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1015</v>
+        <v>1016.7</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1115</v>
+        <v>1119.8</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>137.8</v>
+        <v>136.3</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>493.05</v>
+        <v>488.35</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>270</v>
+        <v>267.05</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1101.5</v>
+        <v>1115</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>548.1</v>
+        <v>543.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1267.6</v>
+        <v>1285.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>500.55</v>
+        <v>498.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>387.65</v>
+        <v>390.25</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>596.65</v>
+        <v>589.1</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1901.4</v>
+        <v>1887.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1814</v>
+        <v>1801.8</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1815</v>
+        <v>1800</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>498.8</v>
+        <v>497</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4064.3</v>
+        <v>4041.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>325.1</v>
+        <v>315.4</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3509.9</v>
+        <v>3540.9</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2232</v>
+        <v>2225</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3421.5</v>
+        <v>3415</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>346.6</v>
+        <v>340</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>841.55</v>
+        <v>850</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13691</v>
+        <v>13690</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3040</v>
+        <v>2973</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3050</v>
+        <v>2975</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>551.95</v>
+        <v>555</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1584.5</v>
+        <v>1546.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1111.4</v>
+        <v>1128</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>170.4</v>
+        <v>170.29</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2432</v>
+        <v>2424.5</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133505</v>
+        <v>133630</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2894.1</v>
+        <v>2859</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2900</v>
+        <v>2850</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>388</v>
+        <v>386.55</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1354.9</v>
+        <v>1378.4</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8255</v>
+        <v>8277.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1462.5</v>
+        <v>1465</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>84.19</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>337.1</v>
+        <v>336.55</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1858</v>
+        <v>1869.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11623</v>
+        <v>11774</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>239.5</v>
+        <v>238</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>36425</v>
+        <v>35240</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>36500</v>
+        <v>35000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5442.5</v>
+        <v>5510</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>286.25</v>
+        <v>288.15</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1674</v>
+        <v>1650</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2515</v>
+        <v>2505</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>116.5</v>
+        <v>117.48</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9139</v>
+        <v>9140</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>268</v>
+        <v>263.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>383</v>
+        <v>381.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>338.5</v>
+        <v>337</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>170.2</v>
+        <v>172.75</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>615</v>
+        <v>623.65</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1778</v>
+        <v>1780.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1053</v>
+        <v>1048.6</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24725</v>
+        <v>24340</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1108.4</v>
+        <v>1106</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3957</v>
+        <v>3898.9</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2630</v>
+        <v>2578.6</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2650</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1875.1</v>
+        <v>1900</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>482.8</v>
+        <v>480.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>404.1</v>
+        <v>396.85</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>653</v>
+        <v>636.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1689.8</v>
+        <v>1660</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1061.6</v>
+        <v>1068</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>381</v>
+        <v>378.9</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>185.5</v>
+        <v>184</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2280</v>
+        <v>2289</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1592</v>
+        <v>1589.8</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5048.6</v>
+        <v>5068</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4971</v>
+        <v>5013</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1264.1</v>
+        <v>1243.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4610,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2942.1</v>
+        <v>2953</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4356.8</v>
+        <v>4361.1</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1355.5</v>
+        <v>1354.8</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11499</v>
+        <v>11450</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>185.5</v>
+        <v>186.9</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>560.05</v>
+        <v>568</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>264</v>
+        <v>262.6</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1252.9</v>
+        <v>1223</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>178.06</v>
+        <v>179.55</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1115.6</v>
+        <v>1104.5</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  19-Aug-2026 13:47</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  20-Aug-2026 13:50</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>527.05</v>
+        <v>520.05</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7430</v>
+        <v>7479</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7450</v>
+        <v>7500</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26405</v>
+        <v>26120</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26400</v>
+        <v>26200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.47</v>
+        <v>54.75</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1288.7</v>
+        <v>1301.1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2990.3</v>
+        <v>2994.9</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1681.9</v>
+        <v>1696</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5382.5</v>
+        <v>5400</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>407.5</v>
+        <v>411</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8750</v>
+        <v>8735</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>427.35</v>
+        <v>429.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>173.1</v>
+        <v>173.8</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2630.8</v>
+        <v>2625.2</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1544.9</v>
+        <v>1532</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>664.25</v>
+        <v>657.65</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1624.5</v>
+        <v>1608</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1075</v>
+        <v>1088</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1235</v>
+        <v>1251</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11645</v>
+        <v>11793</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2000</v>
+        <v>2025</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1080.2</v>
+        <v>1095</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2366.4</v>
+        <v>2378</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>169.2</v>
+        <v>174.16</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>245</v>
+        <v>244.5</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>409.2</v>
+        <v>409.4</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>535.9</v>
+        <v>528.55</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1922</v>
+        <v>1941.7</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>419.8</v>
+        <v>413.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>412.75</v>
+        <v>412.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48460</v>
+        <v>48750</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48400</v>
+        <v>48800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307</v>
+        <v>308.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5453</v>
+        <v>5548</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5450</v>
+        <v>5550</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.08</v>
+        <v>129.6</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1873.5</v>
+        <v>1888.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1422</v>
+        <v>1438</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>400</v>
+        <v>402.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1813.1</v>
+        <v>1882</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1879.6</v>
+        <v>1910</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>514.35</v>
+        <v>519</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>245.5</v>
+        <v>252</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5220</v>
+        <v>5205</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>399.75</v>
+        <v>400</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1768.3</v>
+        <v>1750.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8560</v>
+        <v>8570</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14462</v>
+        <v>14850</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14500</v>
+        <v>14800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>669.9</v>
+        <v>676.15</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7990.5</v>
+        <v>8042</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3054.9</v>
+        <v>3092.1</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>459.5</v>
+        <v>464.1</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>358.8</v>
+        <v>355.3</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2246.5</v>
+        <v>2332.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2250</v>
+        <v>2325</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2007.3</v>
+        <v>2020</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>841.15</v>
+        <v>841.6</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3270</v>
+        <v>3300</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3275</v>
+        <v>3300</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>269.4</v>
+        <v>266.1</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5017</v>
+        <v>4998</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1287</v>
+        <v>1278</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1324.8</v>
+        <v>1318.4</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2551.7</v>
+        <v>2624</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>720</v>
+        <v>725.05</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>536.3</v>
+        <v>542</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5709.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5700</v>
+        <v>5750</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1038.95</v>
+        <v>1029.85</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>554.85</v>
+        <v>560.1</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>366.45</v>
+        <v>363.2</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2020.7</v>
+        <v>2028</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.48999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123</v>
+        <v>123.35</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>152.64</v>
+        <v>150.55</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>723.35</v>
+        <v>735.85</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1734.3</v>
+        <v>1749.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5193</v>
+        <v>5165</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1016.7</v>
+        <v>1008</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>372.4</v>
+        <v>368.8</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1119.8</v>
+        <v>1130</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>136.3</v>
+        <v>135.9</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>488.35</v>
+        <v>485.9</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>267.05</v>
+        <v>271.65</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1115</v>
+        <v>1118.9</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>543.95</v>
+        <v>542</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1285.8</v>
+        <v>1299.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>498.3</v>
+        <v>507.3</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>390.25</v>
+        <v>397.35</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>589.1</v>
+        <v>592.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1887.2</v>
+        <v>1889.4</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1801.8</v>
+        <v>1825</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>497</v>
+        <v>508.05</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4041.3</v>
+        <v>4081</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4050</v>
+        <v>4100</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>315.4</v>
+        <v>314.75</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3540.9</v>
+        <v>3579.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2225</v>
+        <v>2201.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3415</v>
+        <v>3424.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>340</v>
+        <v>349.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>850</v>
+        <v>858.35</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13690</v>
+        <v>13809</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13800</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>2973</v>
+        <v>3126</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>2975</v>
+        <v>3125</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>555</v>
+        <v>540.8</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1546.1</v>
+        <v>1575</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1128</v>
+        <v>1137.8</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>170.29</v>
+        <v>169.58</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2424.5</v>
+        <v>2430</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>133630</v>
+        <v>134000</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>133500</v>
+        <v>134000</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2859</v>
+        <v>2970</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2850</v>
+        <v>2975</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>386.55</v>
+        <v>385.6</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1378.4</v>
+        <v>1360.9</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8277.5</v>
+        <v>8256</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.34999999999999</v>
+        <v>83.95</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>336.55</v>
+        <v>337.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1869.7</v>
+        <v>1904.7</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11774</v>
+        <v>11826</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238</v>
+        <v>238.5</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35240</v>
+        <v>35505</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>35000</v>
+        <v>35500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5510</v>
+        <v>5674</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>288.15</v>
+        <v>291.4</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>374.45</v>
+        <v>363.8</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3827,7 +3827,7 @@
         <v>5</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2505</v>
+        <v>2482.5</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>117.48</v>
+        <v>118</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9140</v>
+        <v>9125</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>263.5</v>
+        <v>264.8</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>381.5</v>
+        <v>392.3</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>337</v>
+        <v>328.1</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1311</v>
+        <v>1313.2</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>172.75</v>
+        <v>174.9</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>623.65</v>
+        <v>647.05</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1780.4</v>
+        <v>1782</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1048.6</v>
+        <v>1048</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24340</v>
+        <v>24300</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1106</v>
+        <v>1128.2</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3898.9</v>
+        <v>3880</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2578.6</v>
+        <v>2574.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>480.9</v>
+        <v>477.55</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>396.85</v>
+        <v>395.5</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>636.3</v>
+        <v>634.5</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1660</v>
+        <v>1677.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1068</v>
+        <v>1056.3</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>378.9</v>
+        <v>375.25</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>184</v>
+        <v>183.5</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2289</v>
+        <v>2298</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1589.8</v>
+        <v>1592.1</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5013</v>
+        <v>5005</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1243.7</v>
+        <v>1248.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2953</v>
+        <v>2970</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4361.1</v>
+        <v>4390</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1354.8</v>
+        <v>1338.5</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11450</v>
+        <v>11575</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>186.9</v>
+        <v>184.68</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>568</v>
+        <v>571.9</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>262.6</v>
+        <v>268</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1223</v>
+        <v>1219.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>179.55</v>
+        <v>181</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1104.5</v>
+        <v>1107.7</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  20-Aug-2026 13:50</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  21-Aug-2026 13:49</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>520.05</v>
+        <v>527.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7479</v>
+        <v>7424</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26120</v>
+        <v>26230</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.75</v>
+        <v>54.35</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1301.1</v>
+        <v>1307.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2994.9</v>
+        <v>2997</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>411</v>
+        <v>414.5</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>289.5</v>
+        <v>287.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8735</v>
+        <v>8693</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>429.3</v>
+        <v>439.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>173.8</v>
+        <v>173</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2625.2</v>
+        <v>2640</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1532</v>
+        <v>1528.5</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>657.65</v>
+        <v>646.1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1608</v>
+        <v>1621.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1088</v>
+        <v>1108.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1251</v>
+        <v>1245.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11793</v>
+        <v>11700</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2016</v>
+        <v>2032.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2378</v>
+        <v>2350.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174.16</v>
+        <v>175.1</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>244.5</v>
+        <v>247</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>409.4</v>
+        <v>414</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>528.55</v>
+        <v>524.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1941.7</v>
+        <v>1946</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>413.5</v>
+        <v>413</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>412.5</v>
+        <v>415.55</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48750</v>
+        <v>48200</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48800</v>
+        <v>48200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>308.7</v>
+        <v>311</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5548</v>
+        <v>5365</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5550</v>
+        <v>5350</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.6</v>
+        <v>129.96</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1888.9</v>
+        <v>1862.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1438</v>
+        <v>1432.2</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>402.5</v>
+        <v>405.2</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1882</v>
+        <v>1891.7</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1910</v>
+        <v>1889</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>519</v>
+        <v>515.05</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5205</v>
+        <v>5107.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>400</v>
+        <v>400.5</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1750.4</v>
+        <v>1747.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8570</v>
+        <v>8597</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>676.15</v>
+        <v>678.1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1180</v>
+        <v>1174.7</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8042</v>
+        <v>8010</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3092.1</v>
+        <v>3086.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>464.1</v>
+        <v>459.6</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>355.3</v>
+        <v>361</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172.5</v>
+        <v>172</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2332.9</v>
+        <v>2317.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2020</v>
+        <v>2035</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>841.6</v>
+        <v>858.15</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3300</v>
+        <v>3308</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>266.1</v>
+        <v>267.2</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4998</v>
+        <v>5000</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1278</v>
+        <v>1268</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1318.4</v>
+        <v>1302.5</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2624</v>
+        <v>2610</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>725.05</v>
+        <v>726.95</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>542</v>
+        <v>554.8</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2342,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5740.5</v>
+        <v>5735</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1029.85</v>
+        <v>1034</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>560.1</v>
+        <v>572.7</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>363.2</v>
+        <v>363.25</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.84</v>
+        <v>86.75</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.35</v>
+        <v>123.7</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>150.55</v>
+        <v>147.87</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>735.85</v>
+        <v>730</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1749.2</v>
+        <v>1742.2</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5165</v>
+        <v>5110</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5150</v>
+        <v>5100</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1008</v>
+        <v>1005.6</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>368.8</v>
+        <v>375.75</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>485.9</v>
+        <v>484.2</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>271.65</v>
+        <v>269.4</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1118.9</v>
+        <v>1127.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>542</v>
+        <v>544.95</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1299.7</v>
+        <v>1293.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>507.3</v>
+        <v>506.75</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>397.35</v>
+        <v>402.8</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>592.9</v>
+        <v>589.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1889.4</v>
+        <v>1894.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1825</v>
+        <v>1802</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>508.05</v>
+        <v>497</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4081</v>
+        <v>4093</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>314.75</v>
+        <v>317.15</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3579.1</v>
+        <v>3604.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2201.5</v>
+        <v>2201.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3424.8</v>
+        <v>3412.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>349.25</v>
+        <v>357.5</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>858.35</v>
+        <v>849.25</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>860</v>
+        <v>850</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13809</v>
+        <v>13565</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3126</v>
+        <v>3185</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3125</v>
+        <v>3175</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>540.8</v>
+        <v>556.95</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1137.8</v>
+        <v>1114.2</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>169.58</v>
+        <v>169.38</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134000</v>
+        <v>132665</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>134000</v>
+        <v>132500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2970</v>
+        <v>3022</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2975</v>
+        <v>3025</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>385.6</v>
+        <v>394.45</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1360.9</v>
+        <v>1350.1</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8256</v>
+        <v>8206.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8300</v>
+        <v>8200</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1458</v>
+        <v>1477.1</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>83.95</v>
+        <v>84.61</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>337.5</v>
+        <v>340</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1904.7</v>
+        <v>1886</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3665,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11826</v>
+        <v>11724</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>238.5</v>
+        <v>236.4</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35505</v>
+        <v>35480</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5674</v>
+        <v>5667.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>291.4</v>
+        <v>293</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>363.8</v>
+        <v>363</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1660</v>
+        <v>1649</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2482.5</v>
+        <v>2496.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>118</v>
+        <v>116.55</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3908,7 +3908,7 @@
         <v>5</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9125</v>
+        <v>8966</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9100</v>
+        <v>9000</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>264.8</v>
+        <v>272.4</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3962,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>392.3</v>
+        <v>392.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>328.1</v>
+        <v>326.65</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1313.2</v>
+        <v>1316</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>174.9</v>
+        <v>173.46</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>647.05</v>
+        <v>649</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1782</v>
+        <v>1792.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1048</v>
+        <v>1048.7</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24300</v>
+        <v>24280</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1128.2</v>
+        <v>1130</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3880</v>
+        <v>3920</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2574.5</v>
+        <v>2571.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1904</v>
+        <v>1902.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>477.55</v>
+        <v>472.05</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>395.5</v>
+        <v>407.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>634.5</v>
+        <v>626.75</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1677.5</v>
+        <v>1655.4</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1056.3</v>
+        <v>1049</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>375.25</v>
+        <v>374.3</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>183.5</v>
+        <v>183</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2298</v>
+        <v>2302</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1592.1</v>
+        <v>1584</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5068</v>
+        <v>5086.1</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5005</v>
+        <v>4896.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1248.7</v>
+        <v>1247.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2970</v>
+        <v>2924</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1338.5</v>
+        <v>1348.9</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11575</v>
+        <v>11570</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>184.68</v>
+        <v>183.45</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>571.9</v>
+        <v>569</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1219.5</v>
+        <v>1235</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181</v>
+        <v>180.79</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1107.7</v>
+        <v>1120</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  21-Aug-2026 13:49</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  24-Aug-2026 13:55</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>527.2</v>
+        <v>543.15</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7424</v>
+        <v>7504</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26230</v>
+        <v>26420</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26400</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>413</v>
+        <v>412.9</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.35</v>
+        <v>53.95</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1307.4</v>
+        <v>1300.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2997</v>
+        <v>2998.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1700</v>
+        <v>1672.1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>414.5</v>
+        <v>408.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>287.8</v>
+        <v>286</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8693</v>
+        <v>8702</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>439.7</v>
+        <v>445.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>173</v>
+        <v>173.29</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2640</v>
+        <v>2640.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1528.5</v>
+        <v>1532.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>646.1</v>
+        <v>639.6</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1621.3</v>
+        <v>1608</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1108.2</v>
+        <v>1114</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1245.8</v>
+        <v>1236</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2032.5</v>
+        <v>2001.7</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2350.8</v>
+        <v>2358.4</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>175.1</v>
+        <v>173.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>247</v>
+        <v>241.5</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>524.4</v>
+        <v>515.5</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1946</v>
+        <v>1935</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>413</v>
+        <v>411.4</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>415.55</v>
+        <v>409.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48200</v>
+        <v>48100</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48200</v>
+        <v>48000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>311</v>
+        <v>311.9</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5365</v>
+        <v>5311</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5350</v>
+        <v>5300</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>129.96</v>
+        <v>127.3</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1862.9</v>
+        <v>1846.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1432.2</v>
+        <v>1437.9</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>405.2</v>
+        <v>406.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1891.7</v>
+        <v>1873</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1889</v>
+        <v>1879</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>515.05</v>
+        <v>516.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5107.5</v>
+        <v>5190</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>400.5</v>
+        <v>398.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1747.1</v>
+        <v>1730.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8597</v>
+        <v>8496</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14850</v>
+        <v>14570</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14800</v>
+        <v>14600</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>678.1</v>
+        <v>689</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1174.7</v>
+        <v>1190</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8010</v>
+        <v>8047</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3086.6</v>
+        <v>3097.3</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>459.6</v>
+        <v>453.3</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>361</v>
+        <v>357.75</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172</v>
+        <v>173.75</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2317.9</v>
+        <v>2390.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2325</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>933</v>
+        <v>928.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2035</v>
+        <v>2039.9</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>858.15</v>
+        <v>855.3</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3308</v>
+        <v>3288</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>267.2</v>
+        <v>263.35</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>5000</v>
+        <v>4906</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2207,7 +2207,7 @@
         <v>100</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1268</v>
+        <v>1268.5</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1302.5</v>
+        <v>1322</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2610</v>
+        <v>2618</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>726.95</v>
+        <v>729</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>554.8</v>
+        <v>552.95</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5735</v>
+        <v>5685</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5750</v>
+        <v>5700</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1034</v>
+        <v>1058.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1030</v>
+        <v>1060</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>572.7</v>
+        <v>574.15</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>363.25</v>
+        <v>371.95</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2015</v>
+        <v>2030</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>86.75</v>
+        <v>85.89</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.7</v>
+        <v>123.01</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>147.87</v>
+        <v>147.72</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>730</v>
+        <v>728.9</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1742.2</v>
+        <v>1746</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5110</v>
+        <v>5115</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1005.6</v>
+        <v>1018.4</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>375.75</v>
+        <v>374.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>135.9</v>
+        <v>138.5</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>484.2</v>
+        <v>483.15</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>269.4</v>
+        <v>269.7</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1127.8</v>
+        <v>1149</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>544.95</v>
+        <v>544.7</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1293.7</v>
+        <v>1327</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>506.75</v>
+        <v>507.9</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>402.8</v>
+        <v>401.45</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>589.3</v>
+        <v>583.1</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1894.2</v>
+        <v>1883.8</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>497</v>
+        <v>491.4</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>317.15</v>
+        <v>315.85</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3604.6</v>
+        <v>3584.6</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2201.8</v>
+        <v>2188</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3412.2</v>
+        <v>3414.1</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>357.5</v>
+        <v>365.05</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>849.25</v>
+        <v>846.1</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13565</v>
+        <v>13620</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3185</v>
+        <v>3268</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3175</v>
+        <v>3275</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>556.95</v>
+        <v>563.35</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1585</v>
+        <v>1569.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1114.2</v>
+        <v>1127.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>169.38</v>
+        <v>169</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2430</v>
+        <v>2427</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132665</v>
+        <v>134365</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>132500</v>
+        <v>134500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3022</v>
+        <v>3209</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>3025</v>
+        <v>3200</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>394.45</v>
+        <v>403.3</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1350.1</v>
+        <v>1349</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8206.5</v>
+        <v>8187</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1477.1</v>
+        <v>1471.3</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>84.61</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>340</v>
+        <v>339.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1886</v>
+        <v>1870</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11724</v>
+        <v>11518</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>236.4</v>
+        <v>236.55</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35480</v>
+        <v>35560</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5667.5</v>
+        <v>5694</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>293</v>
+        <v>295.95</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1649</v>
+        <v>1660</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2496.8</v>
+        <v>2475</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>116.55</v>
+        <v>115.86</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8966</v>
+        <v>9054</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3935,7 +3935,7 @@
         <v>100</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>272.4</v>
+        <v>271.4</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>392.5</v>
+        <v>388</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>326.65</v>
+        <v>327.9</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1316</v>
+        <v>1309.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>173.46</v>
+        <v>179.65</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>649</v>
+        <v>650.3</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1792.9</v>
+        <v>1761.8</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1048.7</v>
+        <v>1039.5</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24280</v>
+        <v>24020</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24500</v>
+        <v>24000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1130</v>
+        <v>1119</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>3920</v>
+        <v>4114</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>3900</v>
+        <v>4100</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2571.9</v>
+        <v>2580.8</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4259,7 +4259,7 @@
         <v>50</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1902.4</v>
+        <v>1910</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>472.05</v>
+        <v>468.75</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>407.25</v>
+        <v>398.55</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>626.75</v>
+        <v>626.95</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1655.4</v>
+        <v>1688.5</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1049</v>
+        <v>1062.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>374.3</v>
+        <v>373.5</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>183</v>
+        <v>186.3</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2302</v>
+        <v>2284.1</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5086.1</v>
+        <v>5079</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4896.5</v>
+        <v>4886.5</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1247.7</v>
+        <v>1246.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2924</v>
+        <v>2905</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4390</v>
+        <v>4363.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4400</v>
+        <v>4375</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1348.9</v>
+        <v>1346.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11570</v>
+        <v>11504</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>183.45</v>
+        <v>183.6</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>569</v>
+        <v>571.9</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>180.79</v>
+        <v>181.31</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1120</v>
+        <v>1103.8</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  24-Aug-2026 13:55</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  25-Aug-2026 13:53</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>543.15</v>
+        <v>538.9</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7504</v>
+        <v>7627</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7500</v>
+        <v>7650</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26420</v>
+        <v>26415</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>412.9</v>
+        <v>410.85</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>53.95</v>
+        <v>54.48</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1300.9</v>
+        <v>1305.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2998.6</v>
+        <v>3110</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1672.1</v>
+        <v>1702.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5350</v>
+        <v>5368</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>408.75</v>
+        <v>413.1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>286</v>
+        <v>300.9</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8702</v>
+        <v>8889</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>445.85</v>
+        <v>441.4</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>173.29</v>
+        <v>174.69</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2640.8</v>
+        <v>2639.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1532.8</v>
+        <v>1540</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>639.6</v>
+        <v>640.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1608</v>
+        <v>1617.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1600</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1114</v>
+        <v>1128.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11800</v>
+        <v>11927</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2001.7</v>
+        <v>2004</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1077</v>
+        <v>1087.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2358.4</v>
+        <v>2366.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>173.9</v>
+        <v>173.5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>241.5</v>
+        <v>241</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>409</v>
+        <v>413.25</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>515.5</v>
+        <v>509.85</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1935</v>
+        <v>1947</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>411.4</v>
+        <v>417</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>409.4</v>
+        <v>417.2</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48100</v>
+        <v>48680</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48000</v>
+        <v>48600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>311.9</v>
+        <v>318.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5311</v>
+        <v>5382.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>127.3</v>
+        <v>128.81</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1846.7</v>
+        <v>1873</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1437.9</v>
+        <v>1422</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1450</v>
+        <v>1425</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>406.9</v>
+        <v>404</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1873</v>
+        <v>1892.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1879</v>
+        <v>1876.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>516.4</v>
+        <v>516</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5190</v>
+        <v>5239.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>398.45</v>
+        <v>395.05</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1730.3</v>
+        <v>1751</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8496</v>
+        <v>8744.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14570</v>
+        <v>14990</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14600</v>
+        <v>15000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>689</v>
+        <v>682.95</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1190</v>
+        <v>1193.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8047</v>
+        <v>8055</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8000</v>
+        <v>8100</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3097.3</v>
+        <v>3064.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>453.3</v>
+        <v>448.75</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>357.75</v>
+        <v>346.95</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.75</v>
+        <v>175.5</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2390.7</v>
+        <v>2400</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>928.9</v>
+        <v>929.2</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2039.9</v>
+        <v>2049</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>855.3</v>
+        <v>845.95</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3288</v>
+        <v>3289.6</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>263.35</v>
+        <v>259</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2180,7 +2180,7 @@
         <v>25</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4906</v>
+        <v>4900</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1268.5</v>
+        <v>1269.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1322</v>
+        <v>1315.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2618</v>
+        <v>2698</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>729</v>
+        <v>727.5</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>552.95</v>
+        <v>546.7</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5685</v>
+        <v>5624.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2369,7 +2369,7 @@
         <v>50</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1058.5</v>
+        <v>1051.05</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>574.15</v>
+        <v>532.65</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>575</v>
+        <v>535</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>371.95</v>
+        <v>373.2</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2030</v>
+        <v>2024.2</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2477,7 +2477,7 @@
         <v>50</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2050</v>
+        <v>2000</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85.89</v>
+        <v>85</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>123.01</v>
+        <v>124.2</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>147.72</v>
+        <v>148.68</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>728.9</v>
+        <v>730</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1746</v>
+        <v>1750.3</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2612,7 +2612,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5115</v>
+        <v>5218</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1018.4</v>
+        <v>1015</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>374.25</v>
+        <v>387.25</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1130</v>
+        <v>1144</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>138.5</v>
+        <v>139</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>483.15</v>
+        <v>482.55</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>269.7</v>
+        <v>271.4</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1149</v>
+        <v>1154.1</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>544.7</v>
+        <v>548.4</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1327</v>
+        <v>1320.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>507.9</v>
+        <v>515</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>401.45</v>
+        <v>401.6</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>583.1</v>
+        <v>592</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2963,7 +2963,7 @@
         <v>25</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1883.8</v>
+        <v>1913.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1801</v>
+        <v>1866.2</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1800</v>
+        <v>1865</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>491.4</v>
+        <v>506</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4090</v>
+        <v>4119</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>315.85</v>
+        <v>319.5</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3098,7 +3098,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3584.6</v>
+        <v>3568.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2188</v>
+        <v>2175.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3152,7 +3152,7 @@
         <v>25</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2200</v>
+        <v>2175</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3414.1</v>
+        <v>3443</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3400</v>
+        <v>3450</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>365.05</v>
+        <v>367.45</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>846.1</v>
+        <v>847.5</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13620</v>
+        <v>13678</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13600</v>
+        <v>13700</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3268</v>
+        <v>3280</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>563.35</v>
+        <v>566.7</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1569.8</v>
+        <v>1592.5</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1127.7</v>
+        <v>1101.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>169</v>
+        <v>166.45</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3395,7 +3395,7 @@
         <v>5</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2427</v>
+        <v>2431.9</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>134365</v>
+        <v>132295</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>134500</v>
+        <v>132500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3209</v>
+        <v>3201</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>403.3</v>
+        <v>397.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3503,7 +3503,7 @@
         <v>5</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8187</v>
+        <v>8209</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1471.3</v>
+        <v>1479</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>339.5</v>
+        <v>339.85</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1870</v>
+        <v>1880</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11518</v>
+        <v>11729</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>236.55</v>
+        <v>234</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3719,7 +3719,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35560</v>
+        <v>35500</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5694</v>
+        <v>5655</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>295.95</v>
+        <v>292.5</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3800,7 +3800,7 @@
         <v>10</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1660</v>
+        <v>1651.1</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2475</v>
+        <v>2508</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>115.86</v>
+        <v>115.93</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9054</v>
+        <v>9098</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>271.4</v>
+        <v>271</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>327.9</v>
+        <v>326</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1309.8</v>
+        <v>1317</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>179.65</v>
+        <v>184.59</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>650.3</v>
+        <v>651</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1761.8</v>
+        <v>1755</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1039.5</v>
+        <v>1048</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4151,7 +4151,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24020</v>
+        <v>24440</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24000</v>
+        <v>24500</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1119</v>
+        <v>1138.5</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1100</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4114</v>
+        <v>4090.5</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2580.8</v>
+        <v>2575</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1910</v>
+        <v>1922</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1900</v>
+        <v>1925</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>468.75</v>
+        <v>468.9</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>398.55</v>
+        <v>406.4</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4340,7 +4340,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>626.95</v>
+        <v>626.35</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1688.5</v>
+        <v>1699.9</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1062.5</v>
+        <v>1060.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>373.5</v>
+        <v>370.6</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>186.3</v>
+        <v>186.94</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2284.1</v>
+        <v>2296.2</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1584</v>
+        <v>1599.9</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1575</v>
+        <v>1600</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5079</v>
+        <v>5124.8</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4886.5</v>
+        <v>4932</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1246.3</v>
+        <v>1243.9</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2905</v>
+        <v>2930</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4363.5</v>
+        <v>4420</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4375</v>
+        <v>4425</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1346.7</v>
+        <v>1348.6</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11504</v>
+        <v>11540</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>183.6</v>
+        <v>186.98</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>571.9</v>
+        <v>585</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.31</v>
+        <v>180.09</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1103.8</v>
+        <v>1124.5</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  25-Aug-2026 13:53</t>
+          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  26-Aug-2026 13:58</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>538.9</v>
+        <v>542.95</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7627</v>
+        <v>7609</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7650</v>
+        <v>7600</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26415</v>
+        <v>26555</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26400</v>
+        <v>26600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>410.85</v>
+        <v>410</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1305.9</v>
+        <v>1331.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3110</v>
+        <v>3112</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1702.7</v>
+        <v>1691.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5368</v>
+        <v>5303.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>413.1</v>
+        <v>419.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>300.9</v>
+        <v>298.85</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8889</v>
+        <v>8766.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>441.4</v>
+        <v>443.05</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>174.69</v>
+        <v>179.05</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2639.8</v>
+        <v>2626.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1540</v>
+        <v>1526.1</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>640.25</v>
+        <v>643.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1617.8</v>
+        <v>1623</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1128.6</v>
+        <v>1113.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1235</v>
+        <v>1255</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11927</v>
+        <v>11724</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11900</v>
+        <v>11700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1087.4</v>
+        <v>1085</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2366.3</v>
+        <v>2328.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>241</v>
+        <v>242.5</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>413.25</v>
+        <v>406.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>509.85</v>
+        <v>503.7</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1947</v>
+        <v>1902.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1950</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>417</v>
+        <v>415.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>417.2</v>
+        <v>417.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48680</v>
+        <v>48895</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48600</v>
+        <v>48800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>318.1</v>
+        <v>318</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5382.5</v>
+        <v>5310</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>128.81</v>
+        <v>129.45</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1873</v>
+        <v>1868.1</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1422</v>
+        <v>1402.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>404</v>
+        <v>403.5</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1892.8</v>
+        <v>1880</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1876.8</v>
+        <v>1860</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>243</v>
+        <v>238.25</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5239.5</v>
+        <v>5200</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>395.05</v>
+        <v>392.2</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1751</v>
+        <v>1776.7</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>8744.5</v>
+        <v>9025</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>8700</v>
+        <v>9000</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14990</v>
+        <v>14735</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>15000</v>
+        <v>14700</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>682.95</v>
+        <v>672.5</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1193.5</v>
+        <v>1182</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>8055</v>
+        <v>8035</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8100</v>
+        <v>8000</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3064.8</v>
+        <v>3067</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>448.75</v>
+        <v>444</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>346.95</v>
+        <v>345.3</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.5</v>
+        <v>174.49</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2400</v>
+        <v>2438.3</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>929.2</v>
+        <v>922.8</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2049</v>
+        <v>2035.1</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>845.95</v>
+        <v>828.2</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3289.6</v>
+        <v>3299.9</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>259</v>
+        <v>256.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>750</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4900</v>
+        <v>4865.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>200</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1269.1</v>
+        <v>1258.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>500</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1315.8</v>
+        <v>1298.5</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>350</v>
@@ -2261,7 +2261,7 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2698</v>
+        <v>2667.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>200</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>727.5</v>
+        <v>727.2</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>550</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>546.7</v>
+        <v>553</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1500</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5624.5</v>
+        <v>5595</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>300</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1051.05</v>
+        <v>1053</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>2150</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>532.65</v>
+        <v>556.05</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>3650</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>373.2</v>
+        <v>375.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>2700</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>2024.2</v>
+        <v>2021</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>300</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>124.2</v>
+        <v>122</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>3750</v>
@@ -2531,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>148.68</v>
+        <v>148.72</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>1375</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>3000</v>
@@ -2585,7 +2585,7 @@
         <v>5</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1750.3</v>
+        <v>1751.9</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5218</v>
+        <v>5250.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>300</v>
@@ -2639,7 +2639,7 @@
         <v>50</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>500</v>
@@ -2666,7 +2666,7 @@
         <v>25</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>387.25</v>
+        <v>377.7</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>2800</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1144</v>
+        <v>1120</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>400</v>
@@ -2720,7 +2720,7 @@
         <v>25</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>139</v>
+        <v>139.48</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>3500</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>482.55</v>
+        <v>491.75</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>875</v>
@@ -2774,7 +2774,7 @@
         <v>25</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>271.4</v>
+        <v>270.25</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>3200</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1154.1</v>
+        <v>1175.4</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1250</v>
@@ -2828,7 +2828,7 @@
         <v>25</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>548.4</v>
+        <v>543.5</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>1500</v>
@@ -2855,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1320.3</v>
+        <v>1341</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>600</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>515</v>
+        <v>499.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>625</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>401.6</v>
+        <v>416.7</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>400</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>800</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1913.7</v>
+        <v>1937.3</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>300</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1866.2</v>
+        <v>1887</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>2500</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1865</v>
+        <v>1885</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>506</v>
+        <v>524.4</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>1600</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>4119</v>
+        <v>4038.1</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>150</v>
@@ -3071,7 +3071,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>319.5</v>
+        <v>322.2</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>5000</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3568.2</v>
+        <v>3543.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>200</v>
@@ -3125,7 +3125,7 @@
         <v>100</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2175.5</v>
+        <v>2185</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3443</v>
+        <v>3398.2</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>175</v>
@@ -3179,7 +3179,7 @@
         <v>50</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3450</v>
+        <v>3400</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>367.45</v>
+        <v>365.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>4000</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>847.5</v>
+        <v>833</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>1200</v>
@@ -3233,7 +3233,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>850</v>
+        <v>830</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>13678</v>
+        <v>13520</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>100</v>
@@ -3260,7 +3260,7 @@
         <v>100</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13700</v>
+        <v>13500</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3280</v>
+        <v>3350</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>25</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3275</v>
+        <v>3350</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>566.7</v>
+        <v>570.3</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>400</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1592.5</v>
+        <v>1600</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>1100</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1101.4</v>
+        <v>1115.3</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>550</v>
@@ -3368,7 +3368,7 @@
         <v>25</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>166.45</v>
+        <v>165</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>14000</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2431.9</v>
+        <v>2400</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>300</v>
@@ -3422,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132295</v>
+        <v>133520</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>5</v>
@@ -3449,7 +3449,7 @@
         <v>500</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>132500</v>
+        <v>133500</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>3201</v>
+        <v>3206.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>600</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>397.8</v>
+        <v>399.3</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>7500</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1350</v>
+        <v>1323.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>150</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8209</v>
+        <v>8553</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>200</v>
@@ -3557,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1479</v>
+        <v>1451.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>50</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.94</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>6750</v>
@@ -3611,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>339.85</v>
+        <v>334.6</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>2250</v>
@@ -3638,7 +3638,7 @@
         <v>10</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1880</v>
+        <v>1870</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>700</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>11729</v>
+        <v>11800</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>75</v>
@@ -3692,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>234</v>
+        <v>232.21</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>1925</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35500</v>
+        <v>35155</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>15</v>
@@ -3746,7 +3746,7 @@
         <v>500</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>35500</v>
+        <v>35000</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5655</v>
+        <v>5590.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>175</v>
@@ -3773,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>292.5</v>
+        <v>289</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>3000</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>367</v>
+        <v>364.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>2700</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1651.1</v>
+        <v>1650</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2508</v>
+        <v>2508.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>250</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>115.93</v>
+        <v>116.7</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>8000</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>9098</v>
+        <v>9060</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>271</v>
+        <v>265.2</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>2700</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>384</v>
+        <v>382.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>5000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>326</v>
+        <v>322.2</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>3000</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1317</v>
+        <v>1298</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>1250</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>184.59</v>
+        <v>194.9</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>8500</v>
@@ -4070,7 +4070,7 @@
         <v>5</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>651</v>
+        <v>660.1</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>1000</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1755</v>
+        <v>1768.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>750</v>
@@ -4124,7 +4124,7 @@
         <v>25</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>1500</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>24440</v>
+        <v>24865</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>25</v>
@@ -4178,7 +4178,7 @@
         <v>500</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1138.5</v>
+        <v>1117.5</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>300</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1150</v>
+        <v>1100</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4090.5</v>
+        <v>4043</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>275</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2575</v>
+        <v>2583</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>375</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1922</v>
+        <v>1899.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>350</v>
@@ -4286,7 +4286,7 @@
         <v>25</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>468.9</v>
+        <v>465.15</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>406.4</v>
+        <v>411.15</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1500</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>626.35</v>
+        <v>637.65</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>1100</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1699.9</v>
+        <v>1649.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>700</v>
@@ -4394,7 +4394,7 @@
         <v>25</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1060.5</v>
+        <v>1047.1</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>1100</v>
@@ -4421,7 +4421,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1060</v>
+        <v>1050</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>370.6</v>
+        <v>364</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>3375</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>186.94</v>
+        <v>188.01</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>5500</v>
@@ -4475,7 +4475,7 @@
         <v>5</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2296.2</v>
+        <v>2270</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>150</v>
@@ -4502,7 +4502,7 @@
         <v>50</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1599.9</v>
+        <v>1571</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>400</v>
@@ -4529,7 +4529,7 @@
         <v>25</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5124.8</v>
+        <v>5100</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4932</v>
+        <v>4890</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>500</v>
@@ -4583,7 +4583,7 @@
         <v>50</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1243.9</v>
+        <v>1258.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>1500</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2930</v>
+        <v>2908.2</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>375</v>
@@ -4637,7 +4637,7 @@
         <v>50</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4420</v>
+        <v>4464</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>350</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4425</v>
+        <v>4475</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1348.6</v>
+        <v>1353.7</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>700</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11540</v>
+        <v>11717</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>200</v>
@@ -4718,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>186.98</v>
+        <v>187.52</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>8400</v>
@@ -4745,7 +4745,7 @@
         <v>5</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>585</v>
+        <v>589.3</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>1300</v>
@@ -4772,7 +4772,7 @@
         <v>25</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>575</v>
+        <v>600</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>275</v>
+        <v>286.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>2750</v>
@@ -4799,7 +4799,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1243</v>
+        <v>1217</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1000</v>
@@ -4826,7 +4826,7 @@
         <v>25</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>180.09</v>
+        <v>177.35</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>1500</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>1124.5</v>
+        <v>1150</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>700</v>
@@ -4880,7 +4880,7 @@
         <v>25</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G162" s="7" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -510,7 +510,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:27-Aug-2026  NM:24-Sep-2026  |  27-Aug-2026 22:53</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  28-Aug-2026 22:57</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>253.95</v>
+        <v>250.35</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>750</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -510,7 +510,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  28-Aug-2026 22:57</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  31-Aug-2026 19:27</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>250.35</v>
+        <v>254.8</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>750</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -56,7 +56,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,6 +128,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -495,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -510,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  31-Aug-2026 19:27</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  01-Sep-2026 17:14</t>
         </is>
       </c>
     </row>
@@ -557,24 +574,4317 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>524.85</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND_CM | AARTIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>7396</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>7400</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ABB_CM | ABB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>26135</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>26200</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA_CM | ABBOTINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL_CM | ABCAPITAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ABFRL_CM | ABFRL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1272.3</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ACC_CM | ACC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2863.9</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT_CM | ADANIENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1647.5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS_CM | ADANIPORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ALKEM_CM | ALKEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>402.2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AMBUJACEM_CM | AMBUJACEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>281.55</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE_CM | ANGELONE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>8755</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP_CM | APOLLOHOSP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>442.7</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE_CM | APOLLOTYRE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>170.53</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY_CM | ASHOKLEY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2575.5</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT_CM | ASIANPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1507</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAL_CM | ASTRAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>613.65</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ATGL_CM | ATGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1683.3</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA_CM | AUROPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1079.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK_CM | AUBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1258</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AXISBANK_CM | AXISBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>12361</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>12400</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO_CM | BAJAJ-AUTO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1972</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1975</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV_CM | BAJAJFINSV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1053.9</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>BAJFINANCE_CM | BAJFINANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>BALKRISIND_CM | BALKRISIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK_CM | BANDHANBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>237.7</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>BANKBARODA_CM | BANKBARODA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>411.2</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>BEL_CM | BEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>490.85</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>BERGEPAINT_CM | BERGEPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1877.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>BHARTIARTL_CM | BHARTIARTL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>426.55</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>BHEL_CM | BHEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>401.05</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>BIOCON_CM | BIOCON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>48550</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>48600</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD_CM | BOSCHLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>317.65</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>BPCL_CM | BPCL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>5187</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>BRITANNIA_CM | BRITANNIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CANBK_CM | CANBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1814.7</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>CHOLAFIN_CM | CHOLAFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1423</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>401.6</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>COALINDIA_CM | COALINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1988.9</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE_CM | COFORGE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1859.8</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>COLPAL_CM | COLPAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>514</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR_CM | CONCOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>230</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>CROMPTON_CM | CROMPTON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>5105</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND_CM | CUMMINSIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>384</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>385</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>DABUR_CM | DABUR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1782.8</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR_CM | DEEPAKNTR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>9165</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>DIVISLAB_CM | DIVISLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>14461</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>DIXON_CM | DIXON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>680</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>DLF_CM | DLF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1171</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DRREDDY_CM | DRREDDY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>7970</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>EICHERMOT_CM | EICHERMOT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>3016.1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>ESCORTS_CM | ESCORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>436.25</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>435</v>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>EXIDEIND_CM | EXIDEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>349.25</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>350</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK_CM | FEDERALBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>172.69</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>175</v>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>GAIL_CM | GAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2470.4</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2475</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK_CM | GLENMARK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>905</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>900</v>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>GODREJCP_CM | GODREJCP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1978</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>GODREJPROP_CM | GODREJPROP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>837.2</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>835</v>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>GRANULES_CM | GRANULES_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>3305</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>475</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM_CM | GRASIM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
           <t>GUJGASLTD</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>254.8</v>
-      </c>
-      <c r="D3" s="3" t="n">
+      <c r="C62" s="9" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="D62" s="7" t="n">
         <v>750</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E62" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F62" s="10" t="n">
         <v>250</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>GUJGASLTD_CM | GUJGASLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>4807.6</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>HAL_CM | HAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>1222.8</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>HAVELLS_CM | HAVELLS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1351.4</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>HCLTECH_CM | HCLTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>2544.9</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>HDFCAMC_CM | HDFCAMC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>711.9</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>HDFCBANK_CM | HDFCBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>540.3</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>540</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>5555</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>5550</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>1014.4</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>HINDALCO_CM | HINDALCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>526.65</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>363.1</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>HINDPETRO_CM | HINDPETRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1994.8</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>IEX_CM | IEX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>IGL_CM | IGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>718</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>720</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>INDHOTEL_CM | INDHOTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>INDIAMART</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>1764.4</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>INDIAMART_CM | INDIAMART_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>5052</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO_CM | INDIGO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>992.6</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>1156</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>INFY_CM | INFY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>136.53</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>IOC_CM | IOC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>481.35</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>875</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>475</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>IRCTC_CM | IRCTC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>ITC_CM | ITC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>JSWENERGY_CM | JSWENERGY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>1313.5</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>1325</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>484.4</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>625</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>425</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>590</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>KPITTECH_CM | KPITTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>1904.4</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>1861.6</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>534.9</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>530</v>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>3980.1</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>LT_CM | LT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>309.05</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>310</v>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>LTF_CM | LTF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>3587.8</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>LTTS_CM | LTTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>2153</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>LUPIN_CM | LUPIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>3259</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>337</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>335</v>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>838.1</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>840</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MARICO_CM | MARICO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>12950</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>MARUTI_CM | MARUTI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>3303</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>MCX_CM | MCX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>582.25</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>1534.7</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>1525</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>MFSL_CM | MFSL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>1077.7</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>MGL_CM | MGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>2505.5</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>132335</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>132500</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>MRF_CM | MRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>2905</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>2900</v>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>370</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>1356</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>8636</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>1438.2</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>85.69</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>NMDC_CM | NMDC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>330</v>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>NTPC_CM | NTPC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>1880.7</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>12187</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>12200</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>OFSS_CM | OFSS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>236.45</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>240</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>ONGC_CM | ONGC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>35675</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>35500</v>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>292.3</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>290</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>PETRONET_CM | PETRONET_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>345</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>PFC_CM | PFC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>1643.5</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>2397.1</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>PIIND_CM | PIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>115.22</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>PNB_CM | PNB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>8895.5</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>8900</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>264.55</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>380</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>315</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>RECLTD_CM | RECLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>195</v>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>SAIL_CM | SAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>632.4</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>SBICARD_CM | SBICARD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>1739.3</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>1034.5</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>SBIN_CM | SBIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>23490</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>23500</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>1059.1</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>4030</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>275</v>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>4050</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>SRF_CM | SRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>1925</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>462.15</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>460</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>SUNTV_CM | SUNTV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>402.05</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>1733.8</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>1725</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>1030.5</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>184.07</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>2369</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>2350</v>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>TCS_CM | TCS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>TECHM_CM | TECHM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>5050</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>TITAN_CM | TITAN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>4965.5</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>1219.3</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>2855</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>TRENT_CM | TRENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>4203</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>4200</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>1308.9</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>UBL_CM | UBL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>567.1</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>575</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>UPL_CM | UPL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>VEDL_CM | VEDL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>WIPRO_CM | WIPRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="n">
+        <v>1167.8</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F162" s="10" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>
       </c>
     </row>
@@ -601,151 +4911,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Legend &amp; Column Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sheet Naming</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SYMBOL_CM = Current Month | SYMBOL_NM = Next Month</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Monthly Expiry</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Last Thursday of each month (NSE standard for stock F&amp;O)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ATM Row</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Yellow = At-The-Money strike (nearest to spot price)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CALL (CE)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Blue — buyer profits when stock RISES above strike</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PUT (PE)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Red — buyer profits when stock FALLS below strike</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Last traded price of the option contract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Open Interest — total outstanding contracts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Contracts traded in current session</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>IV (%)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Implied Volatility (%) from Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Open / Chg OI</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>0 = not available via Yahoo Finance option chain</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Yahoo Finance (yfinance) — NSE option chain</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>GitHub Actions — Every weekday Mon–Fri at 6:30 PM IST</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  01-Sep-2026 17:14</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  02-Sep-2026 17:04</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>524.85</v>
+        <v>505.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7396</v>
+        <v>7447.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7400</v>
+        <v>7450</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26135</v>
+        <v>26045</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>394.45</v>
+        <v>397.05</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>51.1</v>
+        <v>50.47</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1272.3</v>
+        <v>1266.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2863.9</v>
+        <v>2891.8</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2850</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1647.5</v>
+        <v>1672.7</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1650</v>
+        <v>1675</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5300</v>
+        <v>5210</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>402.2</v>
+        <v>402.7</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>281.55</v>
+        <v>279.25</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8755</v>
+        <v>8719</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>442.7</v>
+        <v>434.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>170.53</v>
+        <v>167.9</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2575.5</v>
+        <v>2527.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1507</v>
+        <v>1487</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>613.65</v>
+        <v>614.95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1683.3</v>
+        <v>1648.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1079.2</v>
+        <v>1077.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1258</v>
+        <v>1253.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>12361</v>
+        <v>12130</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12400</v>
+        <v>12100</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1972</v>
+        <v>1990</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1975</v>
+        <v>2000</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1053.9</v>
+        <v>1055.9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2331.8</v>
+        <v>2329.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>162.9</v>
+        <v>161.52</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>237.7</v>
+        <v>241.2</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>411.2</v>
+        <v>405.75</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>490.85</v>
+        <v>488.05</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1877.2</v>
+        <v>1862.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>426.55</v>
+        <v>427.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>401.05</v>
+        <v>401</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48550</v>
+        <v>47250</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48600</v>
+        <v>47200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>317.65</v>
+        <v>319.6</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5187</v>
+        <v>5154</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>125.6</v>
+        <v>126.3</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1814.7</v>
+        <v>1825.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1423</v>
+        <v>1412.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>401.6</v>
+        <v>417.85</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1988.9</v>
+        <v>1965.7</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1859.8</v>
+        <v>1861.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>231.1</v>
+        <v>227.72</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5105</v>
+        <v>5088.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1782.8</v>
+        <v>1734.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9165</v>
+        <v>9220</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14461</v>
+        <v>14590</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14500</v>
+        <v>14600</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>675.15</v>
+        <v>673.55</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1171</v>
+        <v>1156.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7970</v>
+        <v>7711.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>8000</v>
+        <v>7700</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3016.1</v>
+        <v>3019.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>436.25</v>
+        <v>425.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>349.25</v>
+        <v>353.35</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172.69</v>
+        <v>173</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2470.4</v>
+        <v>2460</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2475</v>
+        <v>2450</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1978</v>
+        <v>1970.7</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2000</v>
+        <v>1950</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>837.2</v>
+        <v>831.75</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3305</v>
+        <v>3294.9</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2167,24 +2167,24 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>GUJGASLTD</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>247.7</v>
+        <v>4780</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>750</v>
+        <v>200</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>250</v>
+        <v>4800</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>GUJGASLTD_CM | GUJGASLTD_NM</t>
+          <t>HAL_CM | HAL_NM</t>
         </is>
       </c>
     </row>
@@ -2194,24 +2194,24 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>4807.6</v>
+        <v>1193</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4800</v>
+        <v>1200</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>HAL_CM | HAL_NM</t>
+          <t>HAVELLS_CM | HAVELLS_NM</t>
         </is>
       </c>
     </row>
@@ -2221,24 +2221,24 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1222.8</v>
+        <v>1331.5</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1225</v>
+        <v>1325</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>HAVELLS_CM | HAVELLS_NM</t>
+          <t>HCLTECH_CM | HCLTECH_NM</t>
         </is>
       </c>
     </row>
@@ -2248,24 +2248,24 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1351.4</v>
+        <v>2525.7</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1350</v>
+        <v>2500</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>HCLTECH_CM | HCLTECH_NM</t>
+          <t>HDFCAMC_CM | HDFCAMC_NM</t>
         </is>
       </c>
     </row>
@@ -2275,24 +2275,24 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>2544.9</v>
+        <v>700.8</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>200</v>
+        <v>550</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2500</v>
+        <v>700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>HDFCAMC_CM | HDFCAMC_NM</t>
+          <t>HDFCBANK_CM | HDFCBANK_NM</t>
         </is>
       </c>
     </row>
@@ -2302,24 +2302,24 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>711.9</v>
+        <v>533</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>550</v>
+        <v>1500</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>700</v>
+        <v>530</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>HDFCBANK_CM | HDFCBANK_NM</t>
+          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
         </is>
       </c>
     </row>
@@ -2329,24 +2329,24 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>540.3</v>
+        <v>5300</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>1500</v>
+        <v>300</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>540</v>
+        <v>5300</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
+          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
         </is>
       </c>
     </row>
@@ -2356,24 +2356,24 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>5555</v>
+        <v>1009.7</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>300</v>
+        <v>2150</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>5550</v>
+        <v>1010</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
+          <t>HINDALCO_CM | HINDALCO_NM</t>
         </is>
       </c>
     </row>
@@ -2383,24 +2383,24 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1014.4</v>
+        <v>520.95</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>2150</v>
+        <v>3650</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>1010</v>
+        <v>520</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>HINDALCO_CM | HINDALCO_NM</t>
+          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
         </is>
       </c>
     </row>
@@ -2410,24 +2410,24 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>526.65</v>
+        <v>359</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3650</v>
+        <v>2700</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>525</v>
+        <v>360</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
+          <t>HINDPETRO_CM | HINDPETRO_NM</t>
         </is>
       </c>
     </row>
@@ -2437,24 +2437,24 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>363.1</v>
+        <v>1975</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>2700</v>
+        <v>300</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>365</v>
+        <v>2000</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>HINDPETRO_CM | HINDPETRO_NM</t>
+          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
         </is>
       </c>
     </row>
@@ -2464,24 +2464,24 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>1994.8</v>
+        <v>85.09</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>300</v>
+        <v>7500</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>2000</v>
+        <v>85</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
+          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
         </is>
       </c>
     </row>
@@ -2491,24 +2491,24 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>84.90000000000001</v>
+        <v>118.86</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
+          <t>IEX_CM | IEX_NM</t>
         </is>
       </c>
     </row>
@@ -2518,24 +2518,24 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>119.2</v>
+        <v>147.94</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3750</v>
+        <v>1375</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>IEX_CM | IEX_NM</t>
+          <t>IGL_CM | IGL_NM</t>
         </is>
       </c>
     </row>
@@ -2545,24 +2545,24 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>149.85</v>
+        <v>727.7</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>1375</v>
+        <v>3000</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>150</v>
+        <v>730</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>IGL_CM | IGL_NM</t>
+          <t>INDHOTEL_CM | INDHOTEL_NM</t>
         </is>
       </c>
     </row>
@@ -2572,24 +2572,24 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>718</v>
+        <v>1740.8</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>720</v>
+        <v>1700</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>INDHOTEL_CM | INDHOTEL_NM</t>
+          <t>INDIAMART_CM | INDIAMART_NM</t>
         </is>
       </c>
     </row>
@@ -2599,24 +2599,24 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>1764.4</v>
+        <v>5020</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>INDIAMART_CM | INDIAMART_NM</t>
+          <t>INDIGO_CM | INDIGO_NM</t>
         </is>
       </c>
     </row>
@@ -2626,24 +2626,24 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>5052</v>
+        <v>978</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>5050</v>
+        <v>975</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>INDIGO_CM | INDIGO_NM</t>
+          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
         </is>
       </c>
     </row>
@@ -2653,24 +2653,24 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>992.6</v>
+        <v>379</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
+          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
         </is>
       </c>
     </row>
@@ -2680,24 +2680,24 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>375</v>
+        <v>1140</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>2800</v>
+        <v>400</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>375</v>
+        <v>1150</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
+          <t>INFY_CM | INFY_NM</t>
         </is>
       </c>
     </row>
@@ -2707,24 +2707,24 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>1156</v>
+        <v>137</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>1150</v>
+        <v>135</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>INFY_CM | INFY_NM</t>
+          <t>IOC_CM | IOC_NM</t>
         </is>
       </c>
     </row>
@@ -2734,24 +2734,24 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>136.53</v>
+        <v>472.6</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>3500</v>
+        <v>875</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>135</v>
+        <v>475</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>IOC_CM | IOC_NM</t>
+          <t>IRCTC_CM | IRCTC_NM</t>
         </is>
       </c>
     </row>
@@ -2761,24 +2761,24 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>481.35</v>
+        <v>266.3</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>875</v>
+        <v>3200</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>475</v>
+        <v>270</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>IRCTC_CM | IRCTC_NM</t>
+          <t>ITC_CM | ITC_NM</t>
         </is>
       </c>
     </row>
@@ -2788,24 +2788,24 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>266.6</v>
+        <v>1159.4</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>3200</v>
+        <v>1250</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>270</v>
+        <v>1150</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>ITC_CM | ITC_NM</t>
+          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
         </is>
       </c>
     </row>
@@ -2815,24 +2815,24 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>1160</v>
+        <v>539.8</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>1150</v>
+        <v>540</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
+          <t>JSWENERGY_CM | JSWENERGY_NM</t>
         </is>
       </c>
     </row>
@@ -2842,24 +2842,24 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>518</v>
+        <v>1306</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>520</v>
+        <v>1300</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>JSWENERGY_CM | JSWENERGY_NM</t>
+          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
         </is>
       </c>
     </row>
@@ -2869,24 +2869,24 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>1313.5</v>
+        <v>486.5</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>600</v>
+        <v>625</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>1325</v>
+        <v>475</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
+          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
         </is>
       </c>
     </row>
@@ -2896,24 +2896,24 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>484.4</v>
+        <v>423.5</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>625</v>
+        <v>400</v>
       </c>
       <c r="E89" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>475</v>
+        <v>425</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
+          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
         </is>
       </c>
     </row>
@@ -2923,24 +2923,24 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>425</v>
+        <v>588</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E90" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>425</v>
+        <v>600</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
+          <t>KPITTECH_CM | KPITTECH_NM</t>
         </is>
       </c>
     </row>
@@ -2950,24 +2950,24 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>590</v>
+        <v>1916.1</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>600</v>
+        <v>1900</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>KPITTECH_CM | KPITTECH_NM</t>
+          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
         </is>
       </c>
     </row>
@@ -2977,24 +2977,24 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1904.4</v>
+        <v>1864</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1900</v>
+        <v>1865</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
+          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
         </is>
       </c>
     </row>
@@ -3004,24 +3004,24 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1861.6</v>
+        <v>541.25</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2500</v>
+        <v>1600</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>1860</v>
+        <v>540</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
+          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
         </is>
       </c>
     </row>
@@ -3031,24 +3031,24 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>534.9</v>
+        <v>3981</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>1600</v>
+        <v>150</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>530</v>
+        <v>4000</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
+          <t>LT_CM | LT_NM</t>
         </is>
       </c>
     </row>
@@ -3058,24 +3058,24 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>3980.1</v>
+        <v>312.8</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>150</v>
+        <v>5000</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>4000</v>
+        <v>315</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>LT_CM | LT_NM</t>
+          <t>LTF_CM | LTF_NM</t>
         </is>
       </c>
     </row>
@@ -3085,24 +3085,24 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>309.05</v>
+        <v>3505</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>310</v>
+        <v>3500</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>LTF_CM | LTF_NM</t>
+          <t>LTTS_CM | LTTS_NM</t>
         </is>
       </c>
     </row>
@@ -3112,24 +3112,24 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3587.8</v>
+        <v>2155.2</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>3600</v>
+        <v>2150</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>LTTS_CM | LTTS_NM</t>
+          <t>LUPIN_CM | LUPIN_NM</t>
         </is>
       </c>
     </row>
@@ -3139,24 +3139,24 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2153</v>
+        <v>3190</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>500</v>
+        <v>175</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>2150</v>
+        <v>3200</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>LUPIN_CM | LUPIN_NM</t>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
         </is>
       </c>
     </row>
@@ -3166,24 +3166,24 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>3259</v>
+        <v>340.9</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>175</v>
+        <v>4000</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>3250</v>
+        <v>340</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>M&amp;M_CM | M&amp;M_NM</t>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
         </is>
       </c>
     </row>
@@ -3193,24 +3193,24 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>337</v>
+        <v>829.35</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>335</v>
+        <v>830</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+          <t>MARICO_CM | MARICO_NM</t>
         </is>
       </c>
     </row>
@@ -3220,24 +3220,24 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>838.1</v>
+        <v>12849</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>840</v>
+        <v>12800</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>MARICO_CM | MARICO_NM</t>
+          <t>MARUTI_CM | MARUTI_NM</t>
         </is>
       </c>
     </row>
@@ -3247,24 +3247,24 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>12950</v>
+        <v>3286</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>13000</v>
+        <v>3275</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>MARUTI_CM | MARUTI_NM</t>
+          <t>MCX_CM | MCX_NM</t>
         </is>
       </c>
     </row>
@@ -3274,24 +3274,24 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>3303</v>
+        <v>582.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>3300</v>
+        <v>600</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>MCX_CM | MCX_NM</t>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
         </is>
       </c>
     </row>
@@ -3301,24 +3301,24 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>582.25</v>
+        <v>1505</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+          <t>MFSL_CM | MFSL_NM</t>
         </is>
       </c>
     </row>
@@ -3328,24 +3328,24 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1534.7</v>
+        <v>1065.2</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1525</v>
+        <v>1075</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>MFSL_CM | MFSL_NM</t>
+          <t>MGL_CM | MGL_NM</t>
         </is>
       </c>
     </row>
@@ -3355,24 +3355,24 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>1077.7</v>
+        <v>163.3</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>550</v>
+        <v>14000</v>
       </c>
       <c r="E106" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>1075</v>
+        <v>165</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>MGL_CM | MGL_NM</t>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
         </is>
       </c>
     </row>
@@ -3382,24 +3382,24 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>165.6</v>
+        <v>2480</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>14000</v>
+        <v>300</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
         </is>
       </c>
     </row>
@@ -3409,24 +3409,24 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>2505.5</v>
+        <v>131880</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>2500</v>
+        <v>132000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>MPHASIS_CM | MPHASIS_NM</t>
+          <t>MRF_CM | MRF_NM</t>
         </is>
       </c>
     </row>
@@ -3436,24 +3436,24 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>132335</v>
+        <v>2937.7</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>132500</v>
+        <v>2950</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>MRF_CM | MRF_NM</t>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
         </is>
       </c>
     </row>
@@ -3463,24 +3463,24 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>2905</v>
+        <v>370</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>600</v>
+        <v>7500</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>2900</v>
+        <v>370</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
         </is>
       </c>
     </row>
@@ -3490,24 +3490,24 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>372</v>
+        <v>1343.7</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>7500</v>
+        <v>150</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>370</v>
+        <v>1300</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
         </is>
       </c>
     </row>
@@ -3517,24 +3517,24 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1356</v>
+        <v>8542.5</v>
       </c>
       <c r="D112" s="7" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E112" s="7" t="n">
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1400</v>
+        <v>8500</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>NAUKRI_CM | NAUKRI_NM</t>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
         </is>
       </c>
     </row>
@@ -3544,24 +3544,24 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>8636</v>
+        <v>1425</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>8600</v>
+        <v>1400</v>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
         </is>
       </c>
     </row>
@@ -3571,24 +3571,24 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>1438.2</v>
+        <v>85.75</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>50</v>
+        <v>6750</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>1400</v>
+        <v>85</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+          <t>NMDC_CM | NMDC_NM</t>
         </is>
       </c>
     </row>
@@ -3598,24 +3598,24 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>85.69</v>
+        <v>330</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>6750</v>
+        <v>2250</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>NMDC_CM | NMDC_NM</t>
+          <t>NTPC_CM | NTPC_NM</t>
         </is>
       </c>
     </row>
@@ -3625,24 +3625,24 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>327.5</v>
+        <v>1866</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>2250</v>
+        <v>700</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>330</v>
+        <v>1875</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>NTPC_CM | NTPC_NM</t>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
         </is>
       </c>
     </row>
@@ -3652,24 +3652,24 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>1880.7</v>
+        <v>12158</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>1875</v>
+        <v>12200</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+          <t>OFSS_CM | OFSS_NM</t>
         </is>
       </c>
     </row>
@@ -3679,24 +3679,24 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>12187</v>
+        <v>237.5</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>75</v>
+        <v>1925</v>
       </c>
       <c r="E118" s="7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>12200</v>
+        <v>240</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>OFSS_CM | OFSS_NM</t>
+          <t>ONGC_CM | ONGC_NM</t>
         </is>
       </c>
     </row>
@@ -3706,24 +3706,24 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>236.45</v>
+        <v>36200</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>1925</v>
+        <v>15</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>240</v>
+        <v>36000</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>ONGC_CM | ONGC_NM</t>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
         </is>
       </c>
     </row>
@@ -3733,24 +3733,24 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>35675</v>
+        <v>5690</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="E120" s="7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>35500</v>
+        <v>5700</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>PAGEIND_CM | PAGEIND_NM</t>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
         </is>
       </c>
     </row>
@@ -3760,24 +3760,24 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>5800</v>
+        <v>289.2</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>175</v>
+        <v>3000</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>5800</v>
+        <v>290</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+          <t>PETRONET_CM | PETRONET_NM</t>
         </is>
       </c>
     </row>
@@ -3787,24 +3787,24 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>292.3</v>
+        <v>346.5</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>290</v>
+        <v>345</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>PETRONET_CM | PETRONET_NM</t>
+          <t>PFC_CM | PFC_NM</t>
         </is>
       </c>
     </row>
@@ -3814,24 +3814,24 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>345.8</v>
+        <v>1637</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>2700</v>
+        <v>250</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>345</v>
+        <v>1650</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>PFC_CM | PFC_NM</t>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
         </is>
       </c>
     </row>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>1643.5</v>
+        <v>2393</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,11 +3854,11 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>1650</v>
+        <v>2400</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+          <t>PIIND_CM | PIIND_NM</t>
         </is>
       </c>
     </row>
@@ -3868,24 +3868,24 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>2397.1</v>
+        <v>117</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>250</v>
+        <v>8000</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>2400</v>
+        <v>115</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>PIIND_CM | PIIND_NM</t>
+          <t>PNB_CM | PNB_NM</t>
         </is>
       </c>
     </row>
@@ -3895,24 +3895,24 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>115.22</v>
+        <v>8804</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>8000</v>
+        <v>175</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>115</v>
+        <v>8800</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>PNB_CM | PNB_NM</t>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
         </is>
       </c>
     </row>
@@ -3922,24 +3922,24 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8895.5</v>
+        <v>266.8</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>175</v>
+        <v>2700</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>8900</v>
+        <v>270</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>POLYCAB_CM | POLYCAB_NM</t>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
         </is>
       </c>
     </row>
@@ -3949,24 +3949,24 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>264.55</v>
+        <v>389.4</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>2700</v>
+        <v>5000</v>
       </c>
       <c r="E128" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>POWERGRID_CM | POWERGRID_NM</t>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
         </is>
       </c>
     </row>
@@ -3976,24 +3976,24 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>380.5</v>
+        <v>316.45</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>RBLBANK_CM | RBLBANK_NM</t>
+          <t>RECLTD_CM | RECLTD_NM</t>
         </is>
       </c>
     </row>
@@ -4003,24 +4003,24 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>314.05</v>
+        <v>1313.1</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>3000</v>
+        <v>1250</v>
       </c>
       <c r="E130" s="7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>315</v>
+        <v>1300</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>RECLTD_CM | RECLTD_NM</t>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
         </is>
       </c>
     </row>
@@ -4030,24 +4030,24 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>1309</v>
+        <v>196.5</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>1250</v>
+        <v>8500</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>1300</v>
+        <v>195</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>RELIANCE_CM | RELIANCE_NM</t>
+          <t>SAIL_CM | SAIL_NM</t>
         </is>
       </c>
     </row>
@@ -4057,24 +4057,24 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>193</v>
+        <v>635.15</v>
       </c>
       <c r="D132" s="7" t="n">
-        <v>8500</v>
+        <v>1000</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>195</v>
+        <v>625</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>SAIL_CM | SAIL_NM</t>
+          <t>SBICARD_CM | SBICARD_NM</t>
         </is>
       </c>
     </row>
@@ -4084,24 +4084,24 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>632.4</v>
+        <v>1719.9</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>625</v>
+        <v>1725</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>SBICARD_CM | SBICARD_NM</t>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
         </is>
       </c>
     </row>
@@ -4111,24 +4111,24 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1739.3</v>
+        <v>1020.9</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1750</v>
+        <v>1020</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>SBILIFE_CM | SBILIFE_NM</t>
+          <t>SBIN_CM | SBIN_NM</t>
         </is>
       </c>
     </row>
@@ -4138,24 +4138,24 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>1034.5</v>
+        <v>23680</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>1030</v>
+        <v>23500</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>SBIN_CM | SBIN_NM</t>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
         </is>
       </c>
     </row>
@@ -4165,24 +4165,24 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>23490</v>
+        <v>1047</v>
       </c>
       <c r="D136" s="7" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="E136" s="7" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>23500</v>
+        <v>1050</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>SHREECEM_CM | SHREECEM_NM</t>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
         </is>
       </c>
     </row>
@@ -4192,24 +4192,24 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>1059.1</v>
+        <v>4018.9</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="E137" s="3" t="n">
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>1050</v>
+        <v>4000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
         </is>
       </c>
     </row>
@@ -4219,24 +4219,24 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>4030</v>
+        <v>2598.4</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>275</v>
+        <v>375</v>
       </c>
       <c r="E138" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4050</v>
+        <v>2600</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>SIEMENS_CM | SIEMENS_NM</t>
+          <t>SRF_CM | SRF_NM</t>
         </is>
       </c>
     </row>
@@ -4246,24 +4246,24 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>2592</v>
+        <v>1931.7</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>2600</v>
+        <v>1925</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>SRF_CM | SRF_NM</t>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
         </is>
       </c>
     </row>
@@ -4273,24 +4273,24 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>1929</v>
+        <v>460.6</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="E140" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>1925</v>
+        <v>460</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+          <t>SUNTV_CM | SUNTV_NM</t>
         </is>
       </c>
     </row>
@@ -4300,11 +4300,11 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>462.15</v>
+        <v>398.6</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,11 +4313,11 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>460</v>
+        <v>400</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>SUNTV_CM | SUNTV_NM</t>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
         </is>
       </c>
     </row>
@@ -4327,24 +4327,24 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>402.05</v>
+        <v>633.95</v>
       </c>
       <c r="D142" s="7" t="n">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="E142" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>400</v>
+        <v>625</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>SYNGENE_CM | SYNGENE_NM</t>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
         </is>
       </c>
     </row>
@@ -4354,24 +4354,24 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>633.6</v>
+        <v>1710</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E143" s="3" t="n">
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>625</v>
+        <v>1700</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>TATACHEM_CM | TATACHEM_NM</t>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1733.8</v>
+        <v>1012</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E144" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1725</v>
+        <v>1010</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>TATACOMM_CM | TATACOMM_NM</t>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
         </is>
       </c>
     </row>
@@ -4408,24 +4408,24 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>1030.5</v>
+        <v>364</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>1100</v>
+        <v>3375</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>1030</v>
+        <v>365</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
         </is>
       </c>
     </row>
@@ -4435,24 +4435,24 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>350.55</v>
+        <v>183.85</v>
       </c>
       <c r="D146" s="7" t="n">
-        <v>3375</v>
+        <v>5500</v>
       </c>
       <c r="E146" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>350</v>
+        <v>185</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
         </is>
       </c>
     </row>
@@ -4462,24 +4462,24 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>184.07</v>
+        <v>2348</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>5500</v>
+        <v>150</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>185</v>
+        <v>2350</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+          <t>TCS_CM | TCS_NM</t>
         </is>
       </c>
     </row>
@@ -4489,24 +4489,24 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>2369</v>
+        <v>1623</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="E148" s="7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>2350</v>
+        <v>1625</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
-          <t>TCS_CM | TCS_NM</t>
+          <t>TECHM_CM | TECHM_NM</t>
         </is>
       </c>
     </row>
@@ -4516,24 +4516,24 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1638</v>
+        <v>5074</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>1650</v>
+        <v>5050</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>TECHM_CM | TECHM_NM</t>
+          <t>TITAN_CM | TITAN_NM</t>
         </is>
       </c>
     </row>
@@ -4543,24 +4543,24 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5050</v>
+        <v>5012</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="E150" s="7" t="n">
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
-          <t>TITAN_CM | TITAN_NM</t>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
         </is>
       </c>
     </row>
@@ -4570,24 +4570,24 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>4965.5</v>
+        <v>1248.9</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>4950</v>
+        <v>1250</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
         </is>
       </c>
     </row>
@@ -4597,24 +4597,24 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>1219.3</v>
+        <v>2852.3</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>1500</v>
+        <v>375</v>
       </c>
       <c r="E152" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>1225</v>
+        <v>2850</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
-          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+          <t>TRENT_CM | TRENT_NM</t>
         </is>
       </c>
     </row>
@@ -4624,24 +4624,24 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2855</v>
+        <v>4200</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>2850</v>
+        <v>4200</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>TRENT_CM | TRENT_NM</t>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
         </is>
       </c>
     </row>
@@ -4651,24 +4651,24 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>4203</v>
+        <v>1282.6</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="E154" s="7" t="n">
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>4200</v>
+        <v>1275</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
-          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+          <t>UBL_CM | UBL_NM</t>
         </is>
       </c>
     </row>
@@ -4678,24 +4678,24 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>1308.9</v>
+        <v>11393</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>1300</v>
+        <v>11400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>UBL_CM | UBL_NM</t>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
         </is>
       </c>
     </row>
@@ -4705,24 +4705,24 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>11400</v>
+        <v>186.86</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>200</v>
+        <v>8400</v>
       </c>
       <c r="E156" s="7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11400</v>
+        <v>185</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
         </is>
       </c>
     </row>
@@ -4732,24 +4732,24 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>184.9</v>
+        <v>578.45</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>8400</v>
+        <v>1300</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>185</v>
+        <v>575</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+          <t>UPL_CM | UPL_NM</t>
         </is>
       </c>
     </row>
@@ -4759,24 +4759,24 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>567.1</v>
+        <v>270.7</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>1300</v>
+        <v>2750</v>
       </c>
       <c r="E158" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>575</v>
+        <v>270</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
-          <t>UPL_CM | UPL_NM</t>
+          <t>VEDL_CM | VEDL_NM</t>
         </is>
       </c>
     </row>
@@ -4786,24 +4786,24 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>274</v>
+        <v>1152.1</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>2750</v>
+        <v>1000</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>270</v>
+        <v>1150</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>VEDL_CM | VEDL_NM</t>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
         </is>
       </c>
     </row>
@@ -4813,24 +4813,24 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>1205</v>
+        <v>177.09</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E160" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>VOLTAS_CM | VOLTAS_NM</t>
+          <t>WIPRO_CM | WIPRO_NM</t>
         </is>
       </c>
     </row>
@@ -4840,49 +4840,22 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>181.7</v>
+        <v>1154.2</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>180</v>
+        <v>1150</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
-        <is>
-          <t>WIPRO_CM | WIPRO_NM</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="7" t="n">
-        <v>160</v>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="n">
-        <v>1167.8</v>
-      </c>
-      <c r="D162" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="E162" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F162" s="10" t="n">
-        <v>1175</v>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
         <is>
           <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  02-Sep-2026 17:04</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  03-Sep-2026 16:59</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>505.2</v>
+        <v>501.9</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7447.5</v>
+        <v>7432</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26045</v>
+        <v>25945</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>397.05</v>
+        <v>402</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50.47</v>
+        <v>50.41</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1266.6</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2891.8</v>
+        <v>2901</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1672.7</v>
+        <v>1706.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5210</v>
+        <v>5193</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>402.7</v>
+        <v>405</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>279.25</v>
+        <v>286</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8719</v>
+        <v>8692</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>434.15</v>
+        <v>433.85</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>167.9</v>
+        <v>169.35</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2527.5</v>
+        <v>2541.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1487</v>
+        <v>1495.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1475</v>
+        <v>1500</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>614.95</v>
+        <v>614.05</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1648.2</v>
+        <v>1637.3</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1650</v>
+        <v>1625</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1077.9</v>
+        <v>1072</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1253.9</v>
+        <v>1267</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>12130</v>
+        <v>11920</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>12100</v>
+        <v>11900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1990</v>
+        <v>1992.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1055.9</v>
+        <v>1049</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2329.1</v>
+        <v>2327.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>161.52</v>
+        <v>164.23</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>241.2</v>
+        <v>240.44</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405.75</v>
+        <v>408.6</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>488.05</v>
+        <v>491.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1862.8</v>
+        <v>1869</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>427.5</v>
+        <v>431.8</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47250</v>
+        <v>47000</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47200</v>
+        <v>47000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>319.6</v>
+        <v>320.05</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5154</v>
+        <v>5130</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>126.3</v>
+        <v>125.8</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1825.9</v>
+        <v>1849.3</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1412.8</v>
+        <v>1394.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1425</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>417.85</v>
+        <v>420.05</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1965.7</v>
+        <v>1971.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1861.5</v>
+        <v>1850</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>510</v>
+        <v>508.85</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>227.72</v>
+        <v>226.51</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5088.5</v>
+        <v>5071</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>379</v>
+        <v>380.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1734.1</v>
+        <v>1725.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9220</v>
+        <v>9250</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14590</v>
+        <v>14445</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14600</v>
+        <v>14400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>673.55</v>
+        <v>681.65</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1156.5</v>
+        <v>1155</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7711.5</v>
+        <v>7690</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3019.4</v>
+        <v>2978.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>425.65</v>
+        <v>423</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>353.35</v>
+        <v>344.6</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173</v>
+        <v>174.67</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1970.7</v>
+        <v>2001.5</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>831.75</v>
+        <v>853.85</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>830</v>
+        <v>855</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3294.9</v>
+        <v>3310</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4780</v>
+        <v>4765.6</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1193</v>
+        <v>1200</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1331.5</v>
+        <v>1319</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2525.7</v>
+        <v>2510.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>700.8</v>
+        <v>706.65</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>533</v>
+        <v>533.5</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5300</v>
+        <v>5308.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1009.7</v>
+        <v>1010</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>520.95</v>
+        <v>518.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>359</v>
+        <v>361.35</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1975</v>
+        <v>1962</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2450,7 +2450,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>2000</v>
+        <v>1950</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>85.09</v>
+        <v>87.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>118.86</v>
+        <v>119.15</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>147.94</v>
+        <v>149.42</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>727.7</v>
+        <v>732</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1740.8</v>
+        <v>1729.5</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>5020</v>
+        <v>4980</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>978</v>
+        <v>1004.8</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>975</v>
+        <v>1000</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>379</v>
+        <v>374.95</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1140</v>
+        <v>1130.3</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>137</v>
+        <v>137.8</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>472.6</v>
+        <v>474.6</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>266.3</v>
+        <v>263</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1159.4</v>
+        <v>1145</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>539.8</v>
+        <v>539.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>486.5</v>
+        <v>482.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>423.5</v>
+        <v>421.15</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>588</v>
+        <v>583.5</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1916.1</v>
+        <v>1925.2</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1864</v>
+        <v>1868.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1865</v>
+        <v>1870</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>541.25</v>
+        <v>554</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3981</v>
+        <v>3975</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>312.8</v>
+        <v>316.9</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3505</v>
+        <v>3501.2</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2155.2</v>
+        <v>2132</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2150</v>
+        <v>2125</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3190</v>
+        <v>3150</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3200</v>
+        <v>3150</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>340.9</v>
+        <v>341</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>829.35</v>
+        <v>827.4</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12849</v>
+        <v>12857</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12800</v>
+        <v>12900</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3286</v>
+        <v>3170.2</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3275</v>
+        <v>3175</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>582.2</v>
+        <v>591.9</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1505</v>
+        <v>1537</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1065.2</v>
+        <v>1066.4</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>163.3</v>
+        <v>162</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2480</v>
+        <v>2471</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>131880</v>
+        <v>130510</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>132000</v>
+        <v>130500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2937.7</v>
+        <v>2926.5</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2950</v>
+        <v>2925</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1343.7</v>
+        <v>1330</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8542.5</v>
+        <v>8697</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8500</v>
+        <v>8700</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1425</v>
+        <v>1416</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>85.75</v>
+        <v>84.19</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>330</v>
+        <v>330.9</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1866</v>
+        <v>1902</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>12158</v>
+        <v>12149</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>12200</v>
+        <v>12100</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>237.5</v>
+        <v>236</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>36200</v>
+        <v>35865</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5690</v>
+        <v>5657</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>289.2</v>
+        <v>289.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>346.5</v>
+        <v>345.5</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1637</v>
+        <v>1638.3</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2393</v>
+        <v>2419.9</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>117</v>
+        <v>116.32</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8804</v>
+        <v>8807.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>266.8</v>
+        <v>265.6</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>389.4</v>
+        <v>408.1</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>316.45</v>
+        <v>313.6</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1313.1</v>
+        <v>1302.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>196.5</v>
+        <v>197</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>635.15</v>
+        <v>661</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1719.9</v>
+        <v>1715</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1020.9</v>
+        <v>1023.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>23680</v>
+        <v>23910</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1047</v>
+        <v>1044.2</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>4018.9</v>
+        <v>4030</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>4000</v>
+        <v>4050</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2598.4</v>
+        <v>2617</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1931.7</v>
+        <v>1916</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>460.6</v>
+        <v>465.9</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>398.6</v>
+        <v>400.8</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>633.95</v>
+        <v>641.35</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1710</v>
+        <v>1696.4</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1012</v>
+        <v>1019.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>364</v>
+        <v>365.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>183.85</v>
+        <v>184.2</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2348</v>
+        <v>2320.1</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1623</v>
+        <v>1598</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1625</v>
+        <v>1600</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5074</v>
+        <v>5027</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>5012</v>
+        <v>4905.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1248.9</v>
+        <v>1289.3</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2852.3</v>
+        <v>2815.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1282.6</v>
+        <v>1284.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11393</v>
+        <v>11275</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11400</v>
+        <v>11300</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>186.86</v>
+        <v>189</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>578.45</v>
+        <v>585.35</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>270.7</v>
+        <v>270.5</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1152.1</v>
+        <v>1178</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>177.09</v>
+        <v>175.72</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1154.2</v>
+        <v>1143</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  03-Sep-2026 16:59</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  04-Sep-2026 16:49</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>501.9</v>
+        <v>492.05</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7432</v>
+        <v>7410</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7450</v>
+        <v>7400</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25945</v>
+        <v>26065</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>402</v>
+        <v>404.9</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50.41</v>
+        <v>52.97</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1272</v>
+        <v>1283.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2901</v>
+        <v>2938</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2900</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1706.5</v>
+        <v>1707.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5193</v>
+        <v>5190</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>286</v>
+        <v>299.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8692</v>
+        <v>8650</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>433.85</v>
+        <v>429.55</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>169.35</v>
+        <v>169</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2541.6</v>
+        <v>2527.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1495.2</v>
+        <v>1492.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>614.05</v>
+        <v>612.35</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1637.3</v>
+        <v>1653.1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11920</v>
+        <v>11919</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1992.1</v>
+        <v>1970</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>2000</v>
+        <v>1975</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1049</v>
+        <v>1060.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2327.3</v>
+        <v>2284.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>164.23</v>
+        <v>164.95</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>240.44</v>
+        <v>239</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>408.6</v>
+        <v>405.35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>491.4</v>
+        <v>485.3</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1869</v>
+        <v>1840</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>431.8</v>
+        <v>431.1</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>402</v>
+        <v>397.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47000</v>
+        <v>46820</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47000</v>
+        <v>46800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>320.05</v>
+        <v>315.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5130</v>
+        <v>5101.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5150</v>
+        <v>5100</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>125.8</v>
+        <v>125.5</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1849.3</v>
+        <v>1839</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1394.7</v>
+        <v>1385</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>420.05</v>
+        <v>415.35</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1971.8</v>
+        <v>1972.8</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1850</v>
+        <v>1829.2</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>508.85</v>
+        <v>508</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>226.51</v>
+        <v>232.4</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5071</v>
+        <v>5035</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>380.7</v>
+        <v>380.9</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1725.3</v>
+        <v>1712.4</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9250</v>
+        <v>9100</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9200</v>
+        <v>9100</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14445</v>
+        <v>14240</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14400</v>
+        <v>14200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>681.65</v>
+        <v>681.9</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7690</v>
+        <v>7630.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2978.2</v>
+        <v>2968.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>423</v>
+        <v>424.35</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>344.6</v>
+        <v>343</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.67</v>
+        <v>173.4</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2459</v>
+        <v>2437.2</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2450</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2001.5</v>
+        <v>1982</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>853.85</v>
+        <v>848.3</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3310</v>
+        <v>3322</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3300</v>
+        <v>3325</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4765.6</v>
+        <v>4856</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2180,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1200</v>
+        <v>1154</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1319</v>
+        <v>1293.4</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2510.8</v>
+        <v>2458.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>706.65</v>
+        <v>712.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>533.5</v>
+        <v>546.4</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5308.5</v>
+        <v>5300</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>518.5</v>
+        <v>521.65</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>361.35</v>
+        <v>356.5</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1962</v>
+        <v>1973.4</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>87.5</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>119.15</v>
+        <v>118.91</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>149.42</v>
+        <v>158.04</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2531,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1729.5</v>
+        <v>1726.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4980</v>
+        <v>4977</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1004.8</v>
+        <v>1008.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>374.95</v>
+        <v>376.8</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1130.3</v>
+        <v>1130</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>137.8</v>
+        <v>137.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>474.6</v>
+        <v>476.05</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>263</v>
+        <v>264.1</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1145</v>
+        <v>1165</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>539.5</v>
+        <v>539.85</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1308</v>
+        <v>1325</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1300</v>
+        <v>1325</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>482.9</v>
+        <v>482.7</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>421.15</v>
+        <v>424.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>583.5</v>
+        <v>575.45</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1925.2</v>
+        <v>1877.5</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1868.5</v>
+        <v>1840</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1870</v>
+        <v>1840</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>554</v>
+        <v>562.05</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3975</v>
+        <v>3964.1</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>316.9</v>
+        <v>314</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3501.2</v>
+        <v>3493.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2132</v>
+        <v>2110</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2125</v>
+        <v>2100</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3150</v>
+        <v>3170</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>341</v>
+        <v>339.7</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>827.4</v>
+        <v>815.15</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12857</v>
+        <v>12694</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12900</v>
+        <v>12700</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3170.2</v>
+        <v>3275.4</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3175</v>
+        <v>3275</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>591.9</v>
+        <v>588.7</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1537</v>
+        <v>1548.4</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1066.4</v>
+        <v>1096.6</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>162</v>
+        <v>160.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2471</v>
+        <v>2422</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>130510</v>
+        <v>129945</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>130500</v>
+        <v>130000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2926.5</v>
+        <v>2913.8</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>374</v>
+        <v>374.1</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1330</v>
+        <v>1319.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8697</v>
+        <v>8557.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8700</v>
+        <v>8600</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1416</v>
+        <v>1410.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>84.19</v>
+        <v>84.7</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>330.9</v>
+        <v>332.5</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1902</v>
+        <v>1875.6</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>12149</v>
+        <v>12058</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>236</v>
+        <v>234.65</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35865</v>
+        <v>36300</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>36000</v>
+        <v>36500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5657</v>
+        <v>5643</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>289.5</v>
+        <v>288.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>345.5</v>
+        <v>355.6</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3800,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1638.3</v>
+        <v>1629.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2419.9</v>
+        <v>2465</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116.32</v>
+        <v>117</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8807.5</v>
+        <v>8300</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8800</v>
+        <v>8300</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>265.6</v>
+        <v>266</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>408.1</v>
+        <v>414.35</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>313.6</v>
+        <v>318.7</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1302.5</v>
+        <v>1322</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>197</v>
+        <v>196.8</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>661</v>
+        <v>658.25</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1715</v>
+        <v>1775</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1725</v>
+        <v>1775</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1023.4</v>
+        <v>1016.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>23910</v>
+        <v>23855</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1044.2</v>
+        <v>1041</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>4030</v>
+        <v>3977</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>4050</v>
+        <v>4000</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2617</v>
+        <v>2547</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1916</v>
+        <v>1899</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1925</v>
+        <v>1900</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>465.9</v>
+        <v>470.9</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>400.8</v>
+        <v>395.6</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>641.35</v>
+        <v>625.1</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1696.4</v>
+        <v>1756.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1019.2</v>
+        <v>1010</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>365.7</v>
+        <v>368</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>184.2</v>
+        <v>188.79</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2320.1</v>
+        <v>2304</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1598</v>
+        <v>1596.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5027</v>
+        <v>5020</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4905.5</v>
+        <v>4857</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1289.3</v>
+        <v>1299.1</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2815.6</v>
+        <v>2853</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4200</v>
+        <v>4133.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4200</v>
+        <v>4125</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1284.2</v>
+        <v>1279.4</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11275</v>
+        <v>11408</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11300</v>
+        <v>11400</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>189</v>
+        <v>187.22</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>585.35</v>
+        <v>582.15</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>270.5</v>
+        <v>272.1</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>175.72</v>
+        <v>176.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1143</v>
+        <v>1120</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  04-Sep-2026 16:49</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  07-Sep-2026 18:10</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>492.05</v>
+        <v>490.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7410</v>
+        <v>7434</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7400</v>
+        <v>7450</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26065</v>
+        <v>25940</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>404.9</v>
+        <v>403.25</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>52.97</v>
+        <v>53.21</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1283.8</v>
+        <v>1268.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1707.3</v>
+        <v>1694.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5190</v>
+        <v>5242.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>405</v>
+        <v>398.6</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>299.8</v>
+        <v>303.8</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8650</v>
+        <v>8760</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8600</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>429.55</v>
+        <v>420.8</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2527.3</v>
+        <v>2500.9</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1492.9</v>
+        <v>1498.2</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>612.35</v>
+        <v>603.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1653.1</v>
+        <v>1660</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1273</v>
+        <v>1266</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11919</v>
+        <v>11800</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11900</v>
+        <v>11800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1970</v>
+        <v>1938.6</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1975</v>
+        <v>1950</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1060.5</v>
+        <v>1060</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2284.6</v>
+        <v>2287.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>164.95</v>
+        <v>164.7</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405.35</v>
+        <v>404</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>485.3</v>
+        <v>484.5</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1840</v>
+        <v>1854</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>431.1</v>
+        <v>421.45</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>397.4</v>
+        <v>391.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>46820</v>
+        <v>48025</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>46800</v>
+        <v>48000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>315.7</v>
+        <v>312.9</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5101.5</v>
+        <v>5042.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>125.5</v>
+        <v>124</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1839</v>
+        <v>1848.2</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>415.35</v>
+        <v>418.85</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1972.8</v>
+        <v>1935</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1829.2</v>
+        <v>1813.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>508</v>
+        <v>503.9</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>232.4</v>
+        <v>231.02</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5035</v>
+        <v>5030</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>380.9</v>
+        <v>375.5</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1712.4</v>
+        <v>1642.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9100</v>
+        <v>9315</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14240</v>
+        <v>14180</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>681.9</v>
+        <v>672.7</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1151</v>
+        <v>1144.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7630.5</v>
+        <v>7672</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2968.8</v>
+        <v>2957.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>424.35</v>
+        <v>425.75</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.4</v>
+        <v>176</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2437.2</v>
+        <v>2451.9</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2450</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>878</v>
+        <v>861.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1982</v>
+        <v>1922.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>848.3</v>
+        <v>867.3</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3322</v>
+        <v>3302.4</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3325</v>
+        <v>3300</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4856</v>
+        <v>4855.2</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1293.4</v>
+        <v>1282.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2458.3</v>
+        <v>2432</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2261,7 +2261,7 @@
         <v>100</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>712.1</v>
+        <v>710.5</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>546.4</v>
+        <v>533.2</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5300</v>
+        <v>5270</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5300</v>
+        <v>5250</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>521.65</v>
+        <v>509.1</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>356.5</v>
+        <v>356.9</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1973.4</v>
+        <v>1960</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.70999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>118.91</v>
+        <v>117.5</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>158.04</v>
+        <v>154.8</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2531,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>720</v>
+        <v>716.2</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1726.4</v>
+        <v>1706.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4977</v>
+        <v>5001</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1008.5</v>
+        <v>998</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>376.8</v>
+        <v>376.45</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1130</v>
+        <v>1087.5</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>137.6</v>
+        <v>135.15</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>476.05</v>
+        <v>474.5</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>264.1</v>
+        <v>263.5</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1165</v>
+        <v>1147.9</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>539.85</v>
+        <v>530</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1325</v>
+        <v>1302</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1325</v>
+        <v>1300</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>482.7</v>
+        <v>475.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>424.5</v>
+        <v>422.1</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>575.45</v>
+        <v>562.25</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1877.5</v>
+        <v>1901.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1840</v>
+        <v>1876.7</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1840</v>
+        <v>1875</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>562.05</v>
+        <v>552</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3950</v>
+        <v>4000</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3493.3</v>
+        <v>3414.2</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3098,7 +3098,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>339.7</v>
+        <v>325.6</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>815.15</v>
+        <v>806</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12694</v>
+        <v>12760</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12700</v>
+        <v>12800</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3275.4</v>
+        <v>3330.2</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3275</v>
+        <v>3325</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>588.7</v>
+        <v>577.75</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1548.4</v>
+        <v>1520</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1096.6</v>
+        <v>1092.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>160.7</v>
+        <v>162</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2422</v>
+        <v>2369.1</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>129945</v>
+        <v>128890</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>130000</v>
+        <v>129000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2913.8</v>
+        <v>2880</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2925</v>
+        <v>2875</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>374.1</v>
+        <v>365.9</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1319.8</v>
+        <v>1302.5</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8557.5</v>
+        <v>8603.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1410.5</v>
+        <v>1398</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>84.7</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1875.6</v>
+        <v>1847.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>12058</v>
+        <v>11847</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>12100</v>
+        <v>11800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>234.65</v>
+        <v>233.7</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>36300</v>
+        <v>35825</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>36500</v>
+        <v>36000</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5643</v>
+        <v>5540</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>288.1</v>
+        <v>290.95</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>355.6</v>
+        <v>353.1</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1629.5</v>
+        <v>1575</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2465</v>
+        <v>2430</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>117</v>
+        <v>115.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8300</v>
+        <v>8261</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>266</v>
+        <v>266.45</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>414.35</v>
+        <v>415</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>318.7</v>
+        <v>316.4</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1322</v>
+        <v>1309.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>196.8</v>
+        <v>187.9</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>658.25</v>
+        <v>674.65</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>650</v>
+        <v>675</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1775</v>
+        <v>1732</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1016.1</v>
+        <v>1005.9</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>23855</v>
+        <v>23365</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>24000</v>
+        <v>23500</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3977</v>
+        <v>3927</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>470.9</v>
+        <v>452.85</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>395.6</v>
+        <v>389.3</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>625.1</v>
+        <v>613.35</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1756.1</v>
+        <v>1738.5</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>368</v>
+        <v>365.7</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>188.79</v>
+        <v>185.61</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2304</v>
+        <v>2270</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1596.9</v>
+        <v>1564</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1600</v>
+        <v>1575</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5020</v>
+        <v>4995</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4857</v>
+        <v>4914</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1299.1</v>
+        <v>1275.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2853</v>
+        <v>2814.5</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4133.1</v>
+        <v>4132</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1279.4</v>
+        <v>1291</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11408</v>
+        <v>11175</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11400</v>
+        <v>11200</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>187.22</v>
+        <v>186.04</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>582.15</v>
+        <v>573</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>272.1</v>
+        <v>268</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1170</v>
+        <v>1167.2</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>176.4</v>
+        <v>172.8</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1120</v>
+        <v>1156.9</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  07-Sep-2026 18:10</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  08-Sep-2026 17:08</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>490.7</v>
+        <v>503.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7434</v>
+        <v>7387</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7450</v>
+        <v>7400</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25940</v>
+        <v>25555</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26000</v>
+        <v>25600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>403.25</v>
+        <v>396.95</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>53.21</v>
+        <v>52.24</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -695,7 +695,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1268.7</v>
+        <v>1262.8</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2950</v>
+        <v>2953.1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1694.3</v>
+        <v>1710</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5242.5</v>
+        <v>5181</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>398.6</v>
+        <v>398.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>303.8</v>
+        <v>298</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8760</v>
+        <v>8837.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>420.8</v>
+        <v>411.5</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2500.9</v>
+        <v>2481.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1498.2</v>
+        <v>1500.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>603.7</v>
+        <v>609.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1660</v>
+        <v>1692</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1053</v>
+        <v>1073.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1266</v>
+        <v>1244.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11800</v>
+        <v>11880</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1938.6</v>
+        <v>1938.1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1060</v>
+        <v>1054.1</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2287.1</v>
+        <v>2258</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>164.7</v>
+        <v>171.58</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>237</v>
+        <v>236.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>404</v>
+        <v>410.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>484.5</v>
+        <v>479.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1854</v>
+        <v>1844</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>421.45</v>
+        <v>422.15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>391.4</v>
+        <v>392.3</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48025</v>
+        <v>48785</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48000</v>
+        <v>48800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>312.9</v>
+        <v>303.85</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5042.5</v>
+        <v>5064</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124</v>
+        <v>124.68</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1848.2</v>
+        <v>1823.4</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>418.85</v>
+        <v>420.25</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1935</v>
+        <v>1950</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1813.5</v>
+        <v>1819.9</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>503.9</v>
+        <v>502</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>231.02</v>
+        <v>231.9</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>375.5</v>
+        <v>375</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1642.1</v>
+        <v>1647.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9315</v>
+        <v>9575</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9300</v>
+        <v>9600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14180</v>
+        <v>14100</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14200</v>
+        <v>14100</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>672.7</v>
+        <v>675.1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1144.2</v>
+        <v>1151</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7672</v>
+        <v>7747.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2957.4</v>
+        <v>3013.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>425.75</v>
+        <v>418.15</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>342</v>
+        <v>344.15</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>176</v>
+        <v>175.09</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2451.9</v>
+        <v>2474.5</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2450</v>
+        <v>2475</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>861.9</v>
+        <v>865</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1922.2</v>
+        <v>1906.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>867.3</v>
+        <v>895.35</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>865</v>
+        <v>895</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3302.4</v>
+        <v>3306.8</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4855.2</v>
+        <v>5031.1</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2180,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1282.8</v>
+        <v>1277</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2432</v>
+        <v>2447.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>710.5</v>
+        <v>703</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>533.2</v>
+        <v>533.8</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5270</v>
+        <v>5333.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>509.1</v>
+        <v>532.85</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>510</v>
+        <v>535</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>356.9</v>
+        <v>347</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1960</v>
+        <v>1980</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2450,7 +2450,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.44</v>
+        <v>86.5</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>117.5</v>
+        <v>116.54</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>154.8</v>
+        <v>154.02</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>716.2</v>
+        <v>720</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1706.4</v>
+        <v>1684.5</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>5001</v>
+        <v>5000</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>998</v>
+        <v>997.7</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>376.45</v>
+        <v>373.05</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1087.5</v>
+        <v>1082</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>135.15</v>
+        <v>134.35</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>474.5</v>
+        <v>472.45</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1147.9</v>
+        <v>1136.3</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>530</v>
+        <v>526.5</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1302</v>
+        <v>1297.3</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>475.4</v>
+        <v>480.4</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>422.1</v>
+        <v>419.25</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>562.25</v>
+        <v>562</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1901.9</v>
+        <v>1912.5</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1876.7</v>
+        <v>1946.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1875</v>
+        <v>1945</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>312.5</v>
+        <v>308.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3414.2</v>
+        <v>3389.1</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2105</v>
+        <v>2104.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>325.6</v>
+        <v>325</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>806</v>
+        <v>823.9</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12760</v>
+        <v>12641</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12800</v>
+        <v>12600</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3330.2</v>
+        <v>3342</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3325</v>
+        <v>3350</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>577.75</v>
+        <v>582.2</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1520</v>
+        <v>1498.7</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1092.1</v>
+        <v>1103.2</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>162</v>
+        <v>163.85</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2369.1</v>
+        <v>2355</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>128890</v>
+        <v>128245</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>129000</v>
+        <v>128000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2880</v>
+        <v>2899.7</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2875</v>
+        <v>2900</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>365.9</v>
+        <v>371.05</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1302.5</v>
+        <v>1292</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8603.5</v>
+        <v>8731</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1398</v>
+        <v>1400.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>83.84999999999999</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>332</v>
+        <v>330.8</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1847.5</v>
+        <v>1833.8</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11847</v>
+        <v>11780</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>233.7</v>
+        <v>236</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35825</v>
+        <v>35915</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5540</v>
+        <v>5560</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>290.95</v>
+        <v>285.8</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>353.1</v>
+        <v>355.9</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1575</v>
+        <v>1593</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2430</v>
+        <v>2395</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>115.6</v>
+        <v>116</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8261</v>
+        <v>8373.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>266.45</v>
+        <v>265.75</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>415</v>
+        <v>418.5</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>316.4</v>
+        <v>317.85</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1309.5</v>
+        <v>1294.9</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>187.9</v>
+        <v>186.1</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>674.65</v>
+        <v>668</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1732</v>
+        <v>1696.6</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1005.9</v>
+        <v>1008</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>23365</v>
+        <v>23160</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>23500</v>
+        <v>23000</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1037</v>
+        <v>1029</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3927</v>
+        <v>3951.3</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2546</v>
+        <v>2522</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1895</v>
+        <v>1885.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1900</v>
+        <v>1875</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>452.85</v>
+        <v>453.5</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>389.3</v>
+        <v>387.55</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>613.35</v>
+        <v>607.7</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1738.5</v>
+        <v>1752.8</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1015</v>
+        <v>1014.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>365.7</v>
+        <v>365.55</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>185.61</v>
+        <v>184.15</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2270</v>
+        <v>2255.5</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4995</v>
+        <v>4987</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4914</v>
+        <v>4960</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1275.7</v>
+        <v>1270.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2814.5</v>
+        <v>2793.6</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4132</v>
+        <v>4133.2</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1291</v>
+        <v>1252.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11175</v>
+        <v>11009</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11200</v>
+        <v>11000</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>186.04</v>
+        <v>183.22</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>573</v>
+        <v>576.75</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1167.2</v>
+        <v>1144.8</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>172.8</v>
+        <v>171.5</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1156.9</v>
+        <v>1145.5</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  08-Sep-2026 17:08</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  09-Sep-2026 17:05</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>503.7</v>
+        <v>496.2</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7387</v>
+        <v>7401.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25555</v>
+        <v>25225</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25600</v>
+        <v>25200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>396.95</v>
+        <v>400</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>52.24</v>
+        <v>51.33</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1262.8</v>
+        <v>1257.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2953.1</v>
+        <v>3104.7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>3100</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1700</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5181</v>
+        <v>5139</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>398.3</v>
+        <v>397</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>298</v>
+        <v>299.05</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8837.5</v>
+        <v>8967</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>9000</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>411.5</v>
+        <v>422.25</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2481.6</v>
+        <v>2489</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1500.8</v>
+        <v>1474.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>609.4</v>
+        <v>612.3</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1692</v>
+        <v>1698.9</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1073.7</v>
+        <v>1060.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1244.9</v>
+        <v>1238.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11880</v>
+        <v>11790</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11900</v>
+        <v>11800</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1938.1</v>
+        <v>1927</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1054.1</v>
+        <v>1039.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1181,7 +1181,7 @@
         <v>100</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2258</v>
+        <v>2208.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>171.58</v>
+        <v>171.7</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>236.6</v>
+        <v>234.1</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>410.55</v>
+        <v>406</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>479.45</v>
+        <v>470.8</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1844</v>
+        <v>1814.7</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>422.15</v>
+        <v>433.7</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>392.3</v>
+        <v>395</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48785</v>
+        <v>49100</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48800</v>
+        <v>49200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>303.85</v>
+        <v>303.55</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5064</v>
+        <v>5090</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.68</v>
+        <v>124.08</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1823.4</v>
+        <v>1829</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1384</v>
+        <v>1363.1</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>420.25</v>
+        <v>431</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1950</v>
+        <v>1845</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1613,7 +1613,7 @@
         <v>100</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1819.9</v>
+        <v>1800</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>231.9</v>
+        <v>232.96</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5040</v>
+        <v>5170.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5050</v>
+        <v>5150</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>375</v>
+        <v>371.55</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1647.8</v>
+        <v>1641.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9575</v>
+        <v>9488</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>14100</v>
+        <v>13845</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>14100</v>
+        <v>13800</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>675.1</v>
+        <v>655.1</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7747.5</v>
+        <v>7734.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>3013.2</v>
+        <v>2989.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>418.15</v>
+        <v>410.75</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>344.15</v>
+        <v>345</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>175.09</v>
+        <v>174.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2474.5</v>
+        <v>2435</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2475</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>865</v>
+        <v>863.8</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1906.6</v>
+        <v>1857.1</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1900</v>
+        <v>1850</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>895.35</v>
+        <v>884.8</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3306.8</v>
+        <v>3300</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>5031.1</v>
+        <v>5000.5</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1140</v>
+        <v>1120.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1277</v>
+        <v>1229.8</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1225</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2447.3</v>
+        <v>2440</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>703</v>
+        <v>687.1</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2288,7 +2288,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>533.8</v>
+        <v>514</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5333.5</v>
+        <v>5218</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5350</v>
+        <v>5200</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1009</v>
+        <v>1026.9</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1010</v>
+        <v>1030</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>532.85</v>
+        <v>532.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>347</v>
+        <v>348.9</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1980</v>
+        <v>1945</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2450,7 +2450,7 @@
         <v>50</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>2000</v>
+        <v>1950</v>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>116.54</v>
+        <v>117.95</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>154.02</v>
+        <v>152.92</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>720</v>
+        <v>722.75</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1684.5</v>
+        <v>1671.9</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>5000</v>
+        <v>4975</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>997.7</v>
+        <v>1004</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>373.05</v>
+        <v>373.7</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1082</v>
+        <v>1035</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1075</v>
+        <v>1025</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>134.35</v>
+        <v>135.6</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>472.45</v>
+        <v>469.5</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>263.5</v>
+        <v>260.8</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1136.3</v>
+        <v>1146.5</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>526.5</v>
+        <v>534.8</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1297.3</v>
+        <v>1310</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>480.4</v>
+        <v>475.95</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>419.25</v>
+        <v>414</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>562</v>
+        <v>553.1</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1912.5</v>
+        <v>1919.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1946.9</v>
+        <v>1937</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3389.1</v>
+        <v>3364</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2104.7</v>
+        <v>2100</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3160</v>
+        <v>3150</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>823.9</v>
+        <v>813.9</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12641</v>
+        <v>12618</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3342</v>
+        <v>3350</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>582.2</v>
+        <v>602.1</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1498.7</v>
+        <v>1468.5</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1500</v>
+        <v>1475</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1103.2</v>
+        <v>1084.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>163.85</v>
+        <v>163.7</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2355</v>
+        <v>2307.5</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2350</v>
+        <v>2300</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>128245</v>
+        <v>128315</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>128000</v>
+        <v>128500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2899.7</v>
+        <v>2815</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2900</v>
+        <v>2825</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>371.05</v>
+        <v>377.6</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1292</v>
+        <v>1267</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8731</v>
+        <v>8775.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1400.5</v>
+        <v>1393</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>84.70999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>330.8</v>
+        <v>334.5</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1833.8</v>
+        <v>1800</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11780</v>
+        <v>11630</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11800</v>
+        <v>11600</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>236</v>
+        <v>234.02</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35915</v>
+        <v>35395</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>36000</v>
+        <v>35500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5560</v>
+        <v>5419</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5600</v>
+        <v>5400</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>285.8</v>
+        <v>285.9</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>355.9</v>
+        <v>351.4</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3800,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1593</v>
+        <v>1572</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116</v>
+        <v>115.61</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8373.5</v>
+        <v>8354</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>265.75</v>
+        <v>265.85</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>418.5</v>
+        <v>416</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>317.85</v>
+        <v>314.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1294.9</v>
+        <v>1279</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>186.1</v>
+        <v>186.4</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>668</v>
+        <v>668.4</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1696.6</v>
+        <v>1684</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1008</v>
+        <v>1000.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>23160</v>
+        <v>22950</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3951.3</v>
+        <v>3949.1</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1885.9</v>
+        <v>1864.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>453.5</v>
+        <v>449.3</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>387.55</v>
+        <v>386.8</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>607.7</v>
+        <v>603.05</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1752.8</v>
+        <v>1772.8</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1014.1</v>
+        <v>1001</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>365.55</v>
+        <v>370</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>184.15</v>
+        <v>188.75</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2255.5</v>
+        <v>2208</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4987</v>
+        <v>5005</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4960</v>
+        <v>4930</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1270.2</v>
+        <v>1305.7</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2793.6</v>
+        <v>2820</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4133.2</v>
+        <v>4151.1</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4125</v>
+        <v>4150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1252.5</v>
+        <v>1266.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11009</v>
+        <v>10900</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11000</v>
+        <v>10900</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>183.22</v>
+        <v>183.89</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>576.75</v>
+        <v>575.7</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>272</v>
+        <v>272.5</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1144.8</v>
+        <v>1143.8</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>171.5</v>
+        <v>167</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1145.5</v>
+        <v>1127.4</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  09-Sep-2026 17:05</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  10-Sep-2026 16:56</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>496.2</v>
+        <v>504.05</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7401.5</v>
+        <v>7329</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7400</v>
+        <v>7350</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25225</v>
+        <v>25260</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>51.33</v>
+        <v>50.89</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1257.7</v>
+        <v>1254.3</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5139</v>
+        <v>5138</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>397</v>
+        <v>395.6</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>299.05</v>
+        <v>297.3</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8967</v>
+        <v>8900</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9000</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>422.25</v>
+        <v>419.55</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>167</v>
+        <v>166.12</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2489</v>
+        <v>2498.1</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1474.8</v>
+        <v>1459</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1475</v>
+        <v>1450</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>612.3</v>
+        <v>602.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1698.9</v>
+        <v>1668.4</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1060.5</v>
+        <v>1054.7</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1238.5</v>
+        <v>1246</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11790</v>
+        <v>11768</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1927</v>
+        <v>1940.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1039.3</v>
+        <v>1043.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2208.6</v>
+        <v>2193</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>171.7</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>234.1</v>
+        <v>237.62</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>470.8</v>
+        <v>463.8</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1814.7</v>
+        <v>1839</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>433.7</v>
+        <v>429.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>395</v>
+        <v>391.65</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>49100</v>
+        <v>48775</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>49200</v>
+        <v>48800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>303.55</v>
+        <v>303</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5090</v>
+        <v>5009</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5100</v>
+        <v>5000</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.08</v>
+        <v>124.6</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1829</v>
+        <v>1859</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1363.1</v>
+        <v>1373.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1845</v>
+        <v>1833.1</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1800</v>
+        <v>1808.5</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>510</v>
+        <v>504.15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>232.96</v>
+        <v>230</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5170.5</v>
+        <v>5155</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>371.55</v>
+        <v>376.45</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1641.9</v>
+        <v>1645.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9488</v>
+        <v>9438.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13845</v>
+        <v>13500</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13800</v>
+        <v>13500</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>655.1</v>
+        <v>655.85</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7734.5</v>
+        <v>7697</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2989.2</v>
+        <v>2958.4</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>410.75</v>
+        <v>420.85</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.9</v>
+        <v>174.49</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2435</v>
+        <v>2415</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>863.8</v>
+        <v>869.9</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1857.1</v>
+        <v>1872</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>884.8</v>
+        <v>899.25</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3300</v>
+        <v>3319</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3300</v>
+        <v>3325</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>5000.5</v>
+        <v>4950</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1120.4</v>
+        <v>1116</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1229.8</v>
+        <v>1207</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2440</v>
+        <v>2433.8</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>687.1</v>
+        <v>693.8</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2288,7 +2288,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>675</v>
+        <v>700</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>514</v>
+        <v>526.15</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5218</v>
+        <v>5280</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1026.9</v>
+        <v>1014</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>532.3</v>
+        <v>527.3</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>348.9</v>
+        <v>352.65</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1945</v>
+        <v>1942.3</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86</v>
+        <v>86.84</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>117.95</v>
+        <v>116.63</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>152.92</v>
+        <v>153.46</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>722.75</v>
+        <v>715.75</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1671.9</v>
+        <v>1637.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2585,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4975</v>
+        <v>4945</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>1004</v>
+        <v>993.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>373.7</v>
+        <v>372</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1035</v>
+        <v>1036.5</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>135.6</v>
+        <v>134.94</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>469.5</v>
+        <v>467.75</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>260.8</v>
+        <v>259.3</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1146.5</v>
+        <v>1137</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1150</v>
+        <v>1125</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>534.8</v>
+        <v>530.45</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1310</v>
+        <v>1304</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>475.95</v>
+        <v>473.8</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>414</v>
+        <v>416.55</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>553.1</v>
+        <v>550.95</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1919.7</v>
+        <v>1916.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1937</v>
+        <v>1945</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1935</v>
+        <v>1945</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>555</v>
+        <v>552.3</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3364</v>
+        <v>3377.9</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2100</v>
+        <v>2077.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3150</v>
+        <v>3123.8</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>320</v>
+        <v>330.8</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>813.9</v>
+        <v>803</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12618</v>
+        <v>12590</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3350</v>
+        <v>3300</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>602.1</v>
+        <v>595.65</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1468.5</v>
+        <v>1479.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1084.3</v>
+        <v>1100.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>163.7</v>
+        <v>163.2</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2307.5</v>
+        <v>2291.7</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>128315</v>
+        <v>128270</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2815</v>
+        <v>2841.5</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2825</v>
+        <v>2850</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>377.6</v>
+        <v>373.35</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8775.5</v>
+        <v>8700.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1393</v>
+        <v>1386.2</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>85.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>334.5</v>
+        <v>335</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1800</v>
+        <v>1792</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11630</v>
+        <v>11725</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11600</v>
+        <v>11700</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>234.02</v>
+        <v>237.27</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35395</v>
+        <v>35750</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>35500</v>
+        <v>36000</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5419</v>
+        <v>5509.5</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>285.9</v>
+        <v>288.7</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>351.4</v>
+        <v>352.8</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3800,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2394</v>
+        <v>2365</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>115.61</v>
+        <v>116.85</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8354</v>
+        <v>8358</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>265.85</v>
+        <v>271.75</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>416</v>
+        <v>410.8</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>314.5</v>
+        <v>313.8</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4016,7 +4016,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>186.4</v>
+        <v>183.75</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>668.4</v>
+        <v>666.3</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1684</v>
+        <v>1700.6</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1000.5</v>
+        <v>1009.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22950</v>
+        <v>22785</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1029</v>
+        <v>1038</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3949.1</v>
+        <v>3954.4</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1864.9</v>
+        <v>1861</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>449.3</v>
+        <v>455.55</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>386.8</v>
+        <v>384</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>603.05</v>
+        <v>610.55</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1772.8</v>
+        <v>1764.4</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1001</v>
+        <v>999.6</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>188.75</v>
+        <v>186.78</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2208</v>
+        <v>2204.1</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1508</v>
+        <v>1525.8</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5005</v>
+        <v>5021</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1305.7</v>
+        <v>1296.3</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2820</v>
+        <v>2818.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4151.1</v>
+        <v>4121.5</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4150</v>
+        <v>4125</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1266.7</v>
+        <v>1256.7</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>10900</v>
+        <v>10979</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>10900</v>
+        <v>11000</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>183.89</v>
+        <v>179.2</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>575.7</v>
+        <v>575.3</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>272.5</v>
+        <v>269.05</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1143.8</v>
+        <v>1158.5</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>167</v>
+        <v>166.3</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1127.4</v>
+        <v>1117.8</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  10-Sep-2026 16:56</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  11-Sep-2026 16:58</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>504.05</v>
+        <v>492.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7329</v>
+        <v>7274</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7350</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25260</v>
+        <v>25550</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25200</v>
+        <v>25600</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50.89</v>
+        <v>50.44</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1254.3</v>
+        <v>1246.5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1768</v>
+        <v>1764.6</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5138</v>
+        <v>5087.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>395.6</v>
+        <v>391.85</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>297.3</v>
+        <v>305</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8900</v>
+        <v>8836</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>419.55</v>
+        <v>417.65</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>166.12</v>
+        <v>163.75</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2498.1</v>
+        <v>2472.5</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1459</v>
+        <v>1411.4</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1450</v>
+        <v>1400</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>602.7</v>
+        <v>594.8</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1668.4</v>
+        <v>1679.8</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1054.7</v>
+        <v>1058.9</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11768</v>
+        <v>11678</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11800</v>
+        <v>11700</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1940.5</v>
+        <v>1913.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1950</v>
+        <v>1925</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1043.5</v>
+        <v>1034.5</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2193</v>
+        <v>2164.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>174</v>
+        <v>176.52</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>237.62</v>
+        <v>238.13</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>405</v>
+        <v>404.35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>463.8</v>
+        <v>458.05</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1839</v>
+        <v>1831.1</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>429.5</v>
+        <v>431</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>391.65</v>
+        <v>390.65</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48775</v>
+        <v>48385</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48800</v>
+        <v>48400</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>303</v>
+        <v>304.5</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>5009</v>
+        <v>4962</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124.6</v>
+        <v>124</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1859</v>
+        <v>1845.9</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1373.3</v>
+        <v>1366</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>432</v>
+        <v>426.4</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1833.1</v>
+        <v>1846.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1808.5</v>
+        <v>1797.4</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>504.15</v>
+        <v>499.25</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5155</v>
+        <v>5070</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>376.45</v>
+        <v>376</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1645.8</v>
+        <v>1587.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9438.5</v>
+        <v>9322</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9400</v>
+        <v>9300</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13500</v>
+        <v>13425</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13500</v>
+        <v>13400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>655.85</v>
+        <v>644.5</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1143</v>
+        <v>1165.5</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7697</v>
+        <v>7530</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7700</v>
+        <v>7500</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2958.4</v>
+        <v>2899.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>420.85</v>
+        <v>412.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>346</v>
+        <v>344.5</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>174.49</v>
+        <v>173.62</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2415</v>
+        <v>2419.2</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>869.9</v>
+        <v>865</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1872</v>
+        <v>1748</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1850</v>
+        <v>1750</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>899.25</v>
+        <v>909.3</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3319</v>
+        <v>3281.9</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3325</v>
+        <v>3275</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4950</v>
+        <v>4905</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2180,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1207</v>
+        <v>1206.1</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2433.8</v>
+        <v>2403.9</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>693.8</v>
+        <v>708.25</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>526.15</v>
+        <v>530</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5280</v>
+        <v>5221.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1014</v>
+        <v>981.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1010</v>
+        <v>980</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>527.3</v>
+        <v>514.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>352.65</v>
+        <v>352</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1942.3</v>
+        <v>1927</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.84</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>116.63</v>
+        <v>113.88</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>153.46</v>
+        <v>151.98</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>715.75</v>
+        <v>718.5</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1637.7</v>
+        <v>1695</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2585,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4945</v>
+        <v>4973</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>993.3</v>
+        <v>978.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1036.5</v>
+        <v>1037.7</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>134.94</v>
+        <v>135.11</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>467.75</v>
+        <v>462.9</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>259.3</v>
+        <v>259.85</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1137</v>
+        <v>1120.5</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>530.45</v>
+        <v>526.45</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1304</v>
+        <v>1265</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>473.8</v>
+        <v>470.25</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>416.55</v>
+        <v>419</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>550.95</v>
+        <v>553.75</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1916.7</v>
+        <v>1909</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1945</v>
+        <v>1969</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1945</v>
+        <v>1970</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>552.3</v>
+        <v>562.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>311.3</v>
+        <v>309.1</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3098,7 +3098,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2077.8</v>
+        <v>2095</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2075</v>
+        <v>2100</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3123.8</v>
+        <v>3107</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>330.8</v>
+        <v>329</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>803</v>
+        <v>802.1</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12590</v>
+        <v>12400</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3300</v>
+        <v>3276</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3300</v>
+        <v>3275</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>595.65</v>
+        <v>585.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1479.9</v>
+        <v>1477</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1100.8</v>
+        <v>1084.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>163.2</v>
+        <v>164.45</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2291.7</v>
+        <v>2295</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>128270</v>
+        <v>128290</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2841.5</v>
+        <v>2792.1</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>373.35</v>
+        <v>361</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1265</v>
+        <v>1250.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8700.5</v>
+        <v>8543.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8700</v>
+        <v>8500</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1386.2</v>
+        <v>1383.3</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>84.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3584,7 +3584,7 @@
         <v>5</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>335</v>
+        <v>333.4</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1792</v>
+        <v>1741.1</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1800</v>
+        <v>1750</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11725</v>
+        <v>11763</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11700</v>
+        <v>11800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>237.27</v>
+        <v>232.5</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35750</v>
+        <v>35365</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>36000</v>
+        <v>35500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5509.5</v>
+        <v>5516</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>288.7</v>
+        <v>287.2</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>352.8</v>
+        <v>353.45</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1569</v>
+        <v>1566.9</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2365</v>
+        <v>2259</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2350</v>
+        <v>2250</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116.85</v>
+        <v>116.75</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8358</v>
+        <v>8241</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8400</v>
+        <v>8200</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>271.75</v>
+        <v>269.1</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>410.8</v>
+        <v>412.55</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>313.8</v>
+        <v>312.7</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1274</v>
+        <v>1257.5</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>183.75</v>
+        <v>179</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>666.3</v>
+        <v>655.2</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1700.6</v>
+        <v>1684.7</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>1009.7</v>
+        <v>995.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22785</v>
+        <v>22570</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>23000</v>
+        <v>22500</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1038</v>
+        <v>1028.6</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3954.4</v>
+        <v>3957</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2519</v>
+        <v>2482.4</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1861</v>
+        <v>1840</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>455.55</v>
+        <v>476</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>384</v>
+        <v>382.65</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>610.55</v>
+        <v>612.45</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1764.4</v>
+        <v>1761.6</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>999.6</v>
+        <v>991</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>367</v>
+        <v>364.65</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>186.78</v>
+        <v>183</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2204.1</v>
+        <v>2200.8</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1525.8</v>
+        <v>1541</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5021</v>
+        <v>5009.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4930</v>
+        <v>4965.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1296.3</v>
+        <v>1297.6</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2818.7</v>
+        <v>2802.4</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4121.5</v>
+        <v>4125</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1256.7</v>
+        <v>1256.1</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>10979</v>
+        <v>11000</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>179.2</v>
+        <v>178.1</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>575.3</v>
+        <v>572.95</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>269.05</v>
+        <v>263.7</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4772,7 +4772,7 @@
         <v>10</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1158.5</v>
+        <v>1165</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>166.3</v>
+        <v>167.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1117.8</v>
+        <v>1119.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  11-Sep-2026 16:58</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  14-Sep-2026 18:27</t>
         </is>
       </c>
     </row>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  14-Sep-2026 18:27</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  15-Sep-2026 17:34</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>492.7</v>
+        <v>468.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7274</v>
+        <v>7005</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7250</v>
+        <v>7000</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25550</v>
+        <v>26125</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>25600</v>
+        <v>26200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>395</v>
+        <v>378.8</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50.44</v>
+        <v>49.02</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1246.5</v>
+        <v>1225.2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3050</v>
+        <v>2950</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5087.5</v>
+        <v>5161</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>391.85</v>
+        <v>381.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>305</v>
+        <v>297.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8836</v>
+        <v>8714</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8700</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>417.65</v>
+        <v>406.2</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>163.75</v>
+        <v>156.65</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2472.5</v>
+        <v>2402.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1411.4</v>
+        <v>1379.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1400</v>
+        <v>1375</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>594.8</v>
+        <v>580.15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1679.8</v>
+        <v>1660</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1058.9</v>
+        <v>1028</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1246</v>
+        <v>1222.9</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11700</v>
+        <v>11400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1913.5</v>
+        <v>1855.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1925</v>
+        <v>1850</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2164.6</v>
+        <v>2129</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>176.52</v>
+        <v>172.45</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>238.13</v>
+        <v>232.7</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>404.35</v>
+        <v>382.9</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>458.05</v>
+        <v>447.1</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1831.1</v>
+        <v>1830.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>431</v>
+        <v>412.85</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>390.65</v>
+        <v>382</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48385</v>
+        <v>47070</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48400</v>
+        <v>47000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>304.5</v>
+        <v>298.65</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4962</v>
+        <v>4947.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>124</v>
+        <v>122.37</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1845.9</v>
+        <v>1791.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1850</v>
+        <v>1800</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1366</v>
+        <v>1351</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>426.4</v>
+        <v>419.25</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1846.5</v>
+        <v>1775.5</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1797.4</v>
+        <v>1820.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1800</v>
+        <v>1825</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>499.25</v>
+        <v>483.7</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>231</v>
+        <v>226.15</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5070</v>
+        <v>4874</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5050</v>
+        <v>4850</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>376</v>
+        <v>384.9</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1587.8</v>
+        <v>1561.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1600</v>
+        <v>1550</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9322</v>
+        <v>9198</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13425</v>
+        <v>13180</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13400</v>
+        <v>13200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>644.5</v>
+        <v>620.85</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1165.5</v>
+        <v>1145</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7530</v>
+        <v>7452.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2899.7</v>
+        <v>2835.8</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2900</v>
+        <v>2850</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>412.65</v>
+        <v>409.2</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>344.5</v>
+        <v>343</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.62</v>
+        <v>170.88</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2419.2</v>
+        <v>2371.7</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2375</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>909.3</v>
+        <v>872.6</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>910</v>
+        <v>875</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3281.9</v>
+        <v>3171</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3275</v>
+        <v>3175</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4905</v>
+        <v>4695</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2180,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1111</v>
+        <v>1087</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1206.1</v>
+        <v>1253.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2403.9</v>
+        <v>2409</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>708.25</v>
+        <v>716.55</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2288,7 +2288,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>700</v>
+        <v>725</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>530</v>
+        <v>516.1</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5221.5</v>
+        <v>5166</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>981.5</v>
+        <v>958.7</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>514.5</v>
+        <v>492.1</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>352</v>
+        <v>345.3</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1927</v>
+        <v>1938.1</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.20999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>113.88</v>
+        <v>112</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>151.98</v>
+        <v>150.03</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>718.5</v>
+        <v>715</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1695</v>
+        <v>1659.5</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4973</v>
+        <v>4776</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>4950</v>
+        <v>4800</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>978.2</v>
+        <v>956.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1037.7</v>
+        <v>1077</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1050</v>
+        <v>1075</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>135.11</v>
+        <v>132.03</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>462.9</v>
+        <v>458.55</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2747,7 +2747,7 @@
         <v>25</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>259.85</v>
+        <v>258</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1120.5</v>
+        <v>1095</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>526.45</v>
+        <v>505</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1265</v>
+        <v>1229.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1275</v>
+        <v>1225</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>470.25</v>
+        <v>466</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>419</v>
+        <v>409.8</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>553.75</v>
+        <v>563</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1909</v>
+        <v>1906.4</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1969</v>
+        <v>1926.9</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1970</v>
+        <v>1925</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>562.9</v>
+        <v>542</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3930.7</v>
+        <v>3850.7</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3950</v>
+        <v>3850</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>309.1</v>
+        <v>296.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3337.4</v>
+        <v>3312.2</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2095</v>
+        <v>2063.2</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3107</v>
+        <v>3029.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>329</v>
+        <v>318.85</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>802.1</v>
+        <v>791.25</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12400</v>
+        <v>12231</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12400</v>
+        <v>12200</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3276</v>
+        <v>3173.5</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3275</v>
+        <v>3175</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>585.5</v>
+        <v>572.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>50</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1477</v>
+        <v>1425.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1475</v>
+        <v>1425</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1084.3</v>
+        <v>1071.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>164.45</v>
+        <v>158.15</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2295</v>
+        <v>2378</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>128290</v>
+        <v>125795</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>128500</v>
+        <v>126000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2792.1</v>
+        <v>2722.3</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2800</v>
+        <v>2725</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>361</v>
+        <v>350.55</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1250.8</v>
+        <v>1261.5</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8543.5</v>
+        <v>8228</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8500</v>
+        <v>8200</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1383.3</v>
+        <v>1362</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>82.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>333.4</v>
+        <v>329.5</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1741.1</v>
+        <v>1668.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1750</v>
+        <v>1675</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11763</v>
+        <v>11803</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>232.5</v>
+        <v>235.95</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35365</v>
+        <v>34580</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>35500</v>
+        <v>34500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5516</v>
+        <v>5477.5</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>287.2</v>
+        <v>283.95</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3773,7 +3773,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>353.45</v>
+        <v>344</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3800,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1566.9</v>
+        <v>1521.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1550</v>
+        <v>1500</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116.75</v>
+        <v>114.7</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8241</v>
+        <v>8143.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>269.1</v>
+        <v>262.8</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3935,7 +3935,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>412.55</v>
+        <v>403.6</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>312.7</v>
+        <v>308.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>655.2</v>
+        <v>618.6</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1684.7</v>
+        <v>1654.1</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1675</v>
+        <v>1650</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>995.7</v>
+        <v>968</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22570</v>
+        <v>21905</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>22500</v>
+        <v>22000</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1028.6</v>
+        <v>979.8</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4178,7 +4178,7 @@
         <v>50</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3957</v>
+        <v>3770</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>3950</v>
+        <v>3750</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2482.4</v>
+        <v>2455.2</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1840</v>
+        <v>1835</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>476</v>
+        <v>464.25</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>382.65</v>
+        <v>378.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>612.45</v>
+        <v>734.9</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1761.6</v>
+        <v>1748.2</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>991</v>
+        <v>986.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>364.65</v>
+        <v>363</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>183</v>
+        <v>183.65</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2200.8</v>
+        <v>2251</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1541</v>
+        <v>1575.9</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>5009.5</v>
+        <v>4856</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>5000</v>
+        <v>4850</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4965.5</v>
+        <v>4850</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1297.6</v>
+        <v>1300.9</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2802.4</v>
+        <v>2730</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4125</v>
+        <v>4050</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4125</v>
+        <v>4050</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1256.1</v>
+        <v>1241.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11000</v>
+        <v>10697</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11000</v>
+        <v>10700</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>178.1</v>
+        <v>175</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>572.95</v>
+        <v>560.8</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4745,7 +4745,7 @@
         <v>25</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>263.7</v>
+        <v>257</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1165</v>
+        <v>1137</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1175</v>
+        <v>1125</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>167.4</v>
+        <v>170</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1119.1</v>
+        <v>1099</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  15-Sep-2026 17:34</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  16-Sep-2026 17:33</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>468.7</v>
+        <v>472.85</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7005</v>
+        <v>6980</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>378.8</v>
+        <v>381.3</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.02</v>
+        <v>49.74</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1225.2</v>
+        <v>1226.6</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5161</v>
+        <v>5175</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>381.75</v>
+        <v>381.05</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>297.5</v>
+        <v>293.5</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8714</v>
+        <v>8696.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>406.2</v>
+        <v>411.95</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>156.65</v>
+        <v>156.5</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2402.8</v>
+        <v>2416.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1379.6</v>
+        <v>1382.5</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>580.15</v>
+        <v>586.5</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1660</v>
+        <v>1643</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1028</v>
+        <v>1033.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1222.9</v>
+        <v>1241</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11424</v>
+        <v>11593</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11400</v>
+        <v>11600</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1855.5</v>
+        <v>1837</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1850</v>
+        <v>1825</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2129</v>
+        <v>2124.9</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>172.45</v>
+        <v>172.5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>232.7</v>
+        <v>234.98</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>382.9</v>
+        <v>385.75</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>447.1</v>
+        <v>448.15</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1830.4</v>
+        <v>1835</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>412.85</v>
+        <v>410.6</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>382</v>
+        <v>374.4</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47070</v>
+        <v>47555</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47000</v>
+        <v>47600</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>298.65</v>
+        <v>303.35</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4947.5</v>
+        <v>4999.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>122.37</v>
+        <v>123.2</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1791.6</v>
+        <v>1765.6</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>419.25</v>
+        <v>422.25</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1775.5</v>
+        <v>1766.7</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1820.3</v>
+        <v>1860</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>483.7</v>
+        <v>488.8</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>226.15</v>
+        <v>223.4</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>4874</v>
+        <v>4940</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4850</v>
+        <v>4950</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>384.9</v>
+        <v>382</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1561.3</v>
+        <v>1590.5</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9198</v>
+        <v>9158</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13180</v>
+        <v>13181</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>620.85</v>
+        <v>622.8</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7452.5</v>
+        <v>7500</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2835.8</v>
+        <v>2815.6</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>409.2</v>
+        <v>415.5</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>343</v>
+        <v>341.8</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>170.88</v>
+        <v>170.65</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2371.7</v>
+        <v>2410</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2375</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2072,7 +2072,7 @@
         <v>25</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1659.3</v>
+        <v>1665.3</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>872.6</v>
+        <v>835.6</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>875</v>
+        <v>835</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4695</v>
+        <v>4695.6</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1087</v>
+        <v>1089.9</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1253.7</v>
+        <v>1253</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2409</v>
+        <v>2373.1</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>716.55</v>
+        <v>721.5</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>516.1</v>
+        <v>530.2</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5166</v>
+        <v>5235</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5150</v>
+        <v>5250</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>492.1</v>
+        <v>481.6</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>345.3</v>
+        <v>350.05</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1938.1</v>
+        <v>1962</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>84.8</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>150.03</v>
+        <v>148.77</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>715</v>
+        <v>713.4</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1659.5</v>
+        <v>1706.3</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4776</v>
+        <v>4733.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>4800</v>
+        <v>4750</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>956.5</v>
+        <v>946.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>379</v>
+        <v>375.6</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1075</v>
+        <v>1050</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>132.03</v>
+        <v>134.75</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>458.55</v>
+        <v>452.95</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>258</v>
+        <v>264.15</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>505</v>
+        <v>504.7</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1229.2</v>
+        <v>1248.9</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>409.8</v>
+        <v>415</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1906.4</v>
+        <v>1895.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1926.9</v>
+        <v>1905.5</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1925</v>
+        <v>1905</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3850.7</v>
+        <v>3807.7</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3850</v>
+        <v>3800</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>296.8</v>
+        <v>295.5</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3312.2</v>
+        <v>3351.5</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3098,7 +3098,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2063.2</v>
+        <v>2045</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2075</v>
+        <v>2050</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3029.5</v>
+        <v>3070</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>318.85</v>
+        <v>319.9</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>791.25</v>
+        <v>810.15</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12231</v>
+        <v>12166</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3173.5</v>
+        <v>3211.2</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3175</v>
+        <v>3200</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>572.5</v>
+        <v>580.85</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3287,7 +3287,7 @@
         <v>50</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1425.9</v>
+        <v>1487.6</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1425</v>
+        <v>1500</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1071.7</v>
+        <v>1080.1</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>158.15</v>
+        <v>158.27</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2378</v>
+        <v>2316.7</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3395,7 +3395,7 @@
         <v>50</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>125795</v>
+        <v>125010</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>126000</v>
+        <v>125000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2722.3</v>
+        <v>2771.4</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2725</v>
+        <v>2775</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>350.55</v>
+        <v>356</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1261.5</v>
+        <v>1256</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8228</v>
+        <v>8160.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1362</v>
+        <v>1384.5</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>80.5</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>329.5</v>
+        <v>327</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1668.5</v>
+        <v>1706.9</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1675</v>
+        <v>1700</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11803</v>
+        <v>11510</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11800</v>
+        <v>11500</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>235.95</v>
+        <v>236.8</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>34580</v>
+        <v>34275</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5477.5</v>
+        <v>5440</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>283.95</v>
+        <v>282.1</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1521.1</v>
+        <v>1543.8</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>114.7</v>
+        <v>116.8</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8143.5</v>
+        <v>8121.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>403.6</v>
+        <v>404</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>308.5</v>
+        <v>312.65</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>173</v>
+        <v>173.55</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>618.6</v>
+        <v>618.1</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1654.1</v>
+        <v>1697.9</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>968</v>
+        <v>991.4</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>21905</v>
+        <v>21795</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>979.8</v>
+        <v>979</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3770</v>
+        <v>3742</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2455.2</v>
+        <v>2480.1</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1835</v>
+        <v>1853.5</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>464.25</v>
+        <v>462.45</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>378.85</v>
+        <v>380.1</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>734.9</v>
+        <v>731.8</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1748.2</v>
+        <v>1799.3</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>986.1</v>
+        <v>1000.1</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>363</v>
+        <v>360.4</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>183.65</v>
+        <v>183</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2251</v>
+        <v>2188.8</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2250</v>
+        <v>2200</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1575.9</v>
+        <v>1558</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1575</v>
+        <v>1550</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4856</v>
+        <v>4908.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4850</v>
+        <v>4812.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4850</v>
+        <v>4800</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1300.9</v>
+        <v>1295.3</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2730</v>
+        <v>2769.7</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4050</v>
+        <v>4033</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4050</v>
+        <v>4025</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1241.8</v>
+        <v>1227.3</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>175</v>
+        <v>178.2</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>560.8</v>
+        <v>550.6</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>170</v>
+        <v>166.89</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1099</v>
+        <v>1107.5</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  16-Sep-2026 17:33</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  17-Sep-2026 17:33</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>472.85</v>
+        <v>476.6</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6980</v>
+        <v>7130.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7000</v>
+        <v>7150</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26125</v>
+        <v>25910</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26200</v>
+        <v>26000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.74</v>
+        <v>50.45</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1226.6</v>
+        <v>1232.5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5175</v>
+        <v>5348.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>381.05</v>
+        <v>383.25</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>293.5</v>
+        <v>295</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8696.5</v>
+        <v>8768.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8700</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>411.95</v>
+        <v>412.15</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>156.5</v>
+        <v>158.62</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2416.6</v>
+        <v>2454</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1382.5</v>
+        <v>1398.9</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>586.5</v>
+        <v>587</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1643</v>
+        <v>1690</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1033.2</v>
+        <v>1039.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11593</v>
+        <v>11500</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11600</v>
+        <v>11500</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1837</v>
+        <v>1859.2</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1006.2</v>
+        <v>1015</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2124.9</v>
+        <v>2170.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2100</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>172.5</v>
+        <v>171.5</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>234.98</v>
+        <v>232.3</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>385.75</v>
+        <v>395.45</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>448.15</v>
+        <v>448.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>410.6</v>
+        <v>429.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>374.4</v>
+        <v>380</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47555</v>
+        <v>47735</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47600</v>
+        <v>47800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>303.35</v>
+        <v>307</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4999.5</v>
+        <v>4982</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>123.2</v>
+        <v>123.9</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1765.6</v>
+        <v>1764.5</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1358</v>
+        <v>1376.3</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1350</v>
+        <v>1375</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>422.25</v>
+        <v>418</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1766.7</v>
+        <v>1793</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1860</v>
+        <v>1840.3</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>488.8</v>
+        <v>488.15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>223.4</v>
+        <v>225.1</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>4940</v>
+        <v>5020</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>382</v>
+        <v>384.55</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1590.5</v>
+        <v>1604.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9158</v>
+        <v>9323</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13181</v>
+        <v>13290</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>622.8</v>
+        <v>640</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1883,7 +1883,7 @@
         <v>50</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7500</v>
+        <v>7493.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2815.6</v>
+        <v>2830</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>415.5</v>
+        <v>418.6</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>341.8</v>
+        <v>332.75</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>170.65</v>
+        <v>172</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2410</v>
+        <v>2416</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2400</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1665.3</v>
+        <v>1678.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>835.6</v>
+        <v>870.4</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4695.6</v>
+        <v>4788</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2180,7 +2180,7 @@
         <v>100</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1089.9</v>
+        <v>1092</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1253</v>
+        <v>1258.3</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2373.1</v>
+        <v>2387.7</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>721.5</v>
+        <v>713</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>530.2</v>
+        <v>557</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5235</v>
+        <v>5325</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>481.6</v>
+        <v>485.5</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>350.05</v>
+        <v>350.6</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1962</v>
+        <v>1942.2</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>85.01000000000001</v>
+        <v>86.33</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>112</v>
+        <v>113.4</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>148.77</v>
+        <v>148.67</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>713.4</v>
+        <v>726.65</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>715</v>
+        <v>725</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1706.3</v>
+        <v>1662.7</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4733.5</v>
+        <v>4845</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>4750</v>
+        <v>4850</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>946.5</v>
+        <v>958.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>375.6</v>
+        <v>381.35</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1060</v>
+        <v>1058.6</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>134.75</v>
+        <v>134.27</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>452.95</v>
+        <v>457</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>264.15</v>
+        <v>266.2</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1103</v>
+        <v>1128.4</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>504.7</v>
+        <v>512</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1248.9</v>
+        <v>1253.4</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>471</v>
+        <v>480.2</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>415</v>
+        <v>416.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>555</v>
+        <v>559.3</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1895.7</v>
+        <v>1924.7</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1905.5</v>
+        <v>1948.1</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1905</v>
+        <v>1950</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>543</v>
+        <v>545.9</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3807.7</v>
+        <v>3836.2</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3800</v>
+        <v>3850</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>295.5</v>
+        <v>302.3</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3351.5</v>
+        <v>3324.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3098,7 +3098,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2045</v>
+        <v>2098.1</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2050</v>
+        <v>2100</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3070</v>
+        <v>3076.5</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3050</v>
+        <v>3100</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>319.9</v>
+        <v>316.05</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>810.15</v>
+        <v>817</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12166</v>
+        <v>12338</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3211.2</v>
+        <v>3265.2</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3200</v>
+        <v>3275</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>580.85</v>
+        <v>586.3</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1487.6</v>
+        <v>1554</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1080.1</v>
+        <v>1071.2</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>158.27</v>
+        <v>161.87</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2316.7</v>
+        <v>2320</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>125010</v>
+        <v>124585</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>125000</v>
+        <v>124500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2771.4</v>
+        <v>2770.2</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>356</v>
+        <v>355.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8160.5</v>
+        <v>8220</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1384.5</v>
+        <v>1370.6</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>80.31999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>327</v>
+        <v>329.6</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1706.9</v>
+        <v>1740.7</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11510</v>
+        <v>11620</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>236.8</v>
+        <v>232.43</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3692,7 +3692,7 @@
         <v>10</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>34275</v>
+        <v>35020</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>34500</v>
+        <v>35000</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5440</v>
+        <v>5473</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>282.1</v>
+        <v>283.45</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>346</v>
+        <v>344.95</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1543.8</v>
+        <v>1551.5</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2256</v>
+        <v>2307</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116.8</v>
+        <v>116.47</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8121.5</v>
+        <v>8208.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>262.8</v>
+        <v>263.75</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>404</v>
+        <v>404.15</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>312.65</v>
+        <v>310.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>173.55</v>
+        <v>175.01</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>618.1</v>
+        <v>636.95</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1697.9</v>
+        <v>1766.9</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1700</v>
+        <v>1775</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>991.4</v>
+        <v>988.7</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>21795</v>
+        <v>21960</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3742</v>
+        <v>3763.5</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2480.1</v>
+        <v>2536</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2500</v>
+        <v>2550</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1853.5</v>
+        <v>1867.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>462.45</v>
+        <v>468.4</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>380.1</v>
+        <v>380.2</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>731.8</v>
+        <v>779.3</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>725</v>
+        <v>775</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1799.3</v>
+        <v>1791.6</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1000.1</v>
+        <v>1013.7</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1000</v>
+        <v>1010</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>360.4</v>
+        <v>369</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>183</v>
+        <v>187.29</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2188.8</v>
+        <v>2190</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4908.5</v>
+        <v>4841</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4812.5</v>
+        <v>4875</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1295.3</v>
+        <v>1276.4</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2769.7</v>
+        <v>2789</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2750</v>
+        <v>2800</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4033</v>
+        <v>4101.7</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4025</v>
+        <v>4100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1227.3</v>
+        <v>1216.8</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>178.2</v>
+        <v>178.09</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>550.6</v>
+        <v>554.75</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>256</v>
+        <v>257.45</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>166.89</v>
+        <v>166.4</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1107.5</v>
+        <v>1135.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  17-Sep-2026 17:33</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  18-Sep-2026 17:00</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>476.6</v>
+        <v>491.15</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7130.5</v>
+        <v>7270.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7150</v>
+        <v>7250</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25910</v>
+        <v>27270</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26000</v>
+        <v>27200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>50.45</v>
+        <v>50.16</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1232.5</v>
+        <v>1259.7</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1750</v>
+        <v>1825</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5348.5</v>
+        <v>5466.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5500</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>383.25</v>
+        <v>388.3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>295</v>
+        <v>299.1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8768.5</v>
+        <v>8944.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>412.15</v>
+        <v>409.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>158.62</v>
+        <v>163</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2454</v>
+        <v>2451.3</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1398.9</v>
+        <v>1427.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>587</v>
+        <v>660.7</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>575</v>
+        <v>650</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1690</v>
+        <v>1734</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1039.3</v>
+        <v>1058.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1240</v>
+        <v>1257</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11500</v>
+        <v>11414</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11500</v>
+        <v>11400</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1859.2</v>
+        <v>1852.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1015</v>
+        <v>1040.3</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2170.8</v>
+        <v>2265.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>171.5</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>232.3</v>
+        <v>234.94</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1262,7 +1262,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>395.45</v>
+        <v>393.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>448.6</v>
+        <v>458.65</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1836</v>
+        <v>1893.3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1900</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>429.2</v>
+        <v>439.9</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47735</v>
+        <v>47000</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47800</v>
+        <v>47000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4982</v>
+        <v>4998</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>123.9</v>
+        <v>123.78</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1764.5</v>
+        <v>1800</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1376.3</v>
+        <v>1394.5</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>418</v>
+        <v>409.9</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1793</v>
+        <v>1841</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1840.3</v>
+        <v>1917.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1850</v>
+        <v>1925</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>488.15</v>
+        <v>504.55</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>225.1</v>
+        <v>227.12</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5020</v>
+        <v>5099.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>384.55</v>
+        <v>395.25</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1604.8</v>
+        <v>1586.3</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9323</v>
+        <v>9375</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13290</v>
+        <v>13005</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13300</v>
+        <v>13000</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>640</v>
+        <v>644.35</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1175</v>
+        <v>1185</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7493.5</v>
+        <v>7516</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2830</v>
+        <v>2798.2</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2850</v>
+        <v>2800</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>418.6</v>
+        <v>435.85</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172</v>
+        <v>173.9</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2416</v>
+        <v>2447.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2450</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1678.2</v>
+        <v>1691.1</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>870.4</v>
+        <v>875.5</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3175</v>
+        <v>3200</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4788</v>
+        <v>4800.3</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1092</v>
+        <v>1132.4</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2207,7 +2207,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1258.3</v>
+        <v>1249.3</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2387.7</v>
+        <v>2425</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>557</v>
+        <v>550.95</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5325</v>
+        <v>5285.5</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>485.5</v>
+        <v>497.4</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>350.6</v>
+        <v>359</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1942.2</v>
+        <v>1932</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>86.33</v>
+        <v>85.92</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>113.4</v>
+        <v>115.46</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>148.67</v>
+        <v>148.56</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>726.65</v>
+        <v>732.75</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>725</v>
+        <v>735</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1662.7</v>
+        <v>1646.3</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2585,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4845</v>
+        <v>4920</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>958.2</v>
+        <v>966.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>950</v>
+        <v>975</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>381.35</v>
+        <v>375.9</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1058.6</v>
+        <v>1051.4</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>134.27</v>
+        <v>137</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>457</v>
+        <v>476.75</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2747,7 +2747,7 @@
         <v>25</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>266.2</v>
+        <v>262.3</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1128.4</v>
+        <v>1119.5</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1253.4</v>
+        <v>1275.6</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>480.2</v>
+        <v>500</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>416.5</v>
+        <v>412.5</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>559.3</v>
+        <v>532</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2936,7 +2936,7 @@
         <v>25</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>550</v>
+        <v>525</v>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1924.7</v>
+        <v>1896.9</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>1948.1</v>
+        <v>1954</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>545.9</v>
+        <v>548.15</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3836.2</v>
+        <v>3885</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>302.3</v>
+        <v>312.8</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3324.3</v>
+        <v>3347.5</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2098.1</v>
+        <v>2083</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2100</v>
+        <v>2075</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3076.5</v>
+        <v>3052</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>316.05</v>
+        <v>319.15</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>817</v>
+        <v>803.9</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12338</v>
+        <v>12103</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12300</v>
+        <v>12100</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3265.2</v>
+        <v>3260</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3275</v>
+        <v>3250</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>586.3</v>
+        <v>597.45</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1554</v>
+        <v>1559</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1071.2</v>
+        <v>1081.7</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>161.87</v>
+        <v>162.57</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2320</v>
+        <v>2300.4</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>124585</v>
+        <v>125670</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>124500</v>
+        <v>125500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2770.2</v>
+        <v>2841.1</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2775</v>
+        <v>2850</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>355.7</v>
+        <v>350.5</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1265</v>
+        <v>1251.2</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8220</v>
+        <v>8590</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1370.6</v>
+        <v>1372.4</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>80.8</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>329.6</v>
+        <v>323.65</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1740.7</v>
+        <v>1785</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3638,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>11620</v>
+        <v>11896</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11600</v>
+        <v>11900</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>232.43</v>
+        <v>232.8</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>35020</v>
+        <v>36400</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>35000</v>
+        <v>36500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5473</v>
+        <v>5416</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>283.45</v>
+        <v>292.6</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3773,7 +3773,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>344.95</v>
+        <v>342.55</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1551.5</v>
+        <v>1572.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2307</v>
+        <v>2366.8</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3854,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>2300</v>
+        <v>2350</v>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>116.47</v>
+        <v>117.27</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8208.5</v>
+        <v>8400</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>263.75</v>
+        <v>270.3</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3935,7 +3935,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>404.15</v>
+        <v>415.9</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>310.5</v>
+        <v>312</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>175.01</v>
+        <v>177.33</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>636.95</v>
+        <v>651.15</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1766.9</v>
+        <v>1731</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4097,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>1775</v>
+        <v>1725</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>988.7</v>
+        <v>996.2</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>21960</v>
+        <v>22600</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3763.5</v>
+        <v>3913.9</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>3750</v>
+        <v>3900</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2536</v>
+        <v>2512</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4232,7 +4232,7 @@
         <v>50</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2550</v>
+        <v>2500</v>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1867.3</v>
+        <v>1837.3</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1875</v>
+        <v>1825</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>468.4</v>
+        <v>451.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>380.2</v>
+        <v>369.05</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="6" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>779.3</v>
+        <v>693.25</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>775</v>
+        <v>700</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1791.6</v>
+        <v>1780.1</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>1013.7</v>
+        <v>996</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>369</v>
+        <v>374.8</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>187.29</v>
+        <v>185.54</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2190</v>
+        <v>2105</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4475,7 +4475,7 @@
         <v>50</v>
       </c>
       <c r="F147" s="6" t="n">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1561</v>
+        <v>1537.1</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4502,7 +4502,7 @@
         <v>25</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1550</v>
+        <v>1525</v>
       </c>
       <c r="G148" s="7" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4841</v>
+        <v>4798.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4850</v>
+        <v>4800</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4875</v>
+        <v>4840</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1276.4</v>
+        <v>1258.8</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
       <c r="F151" s="6" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2789</v>
+        <v>2824</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4101.7</v>
+        <v>4171.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4100</v>
+        <v>4175</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1216.8</v>
+        <v>1251.5</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>178.09</v>
+        <v>176.56</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4718,7 +4718,7 @@
         <v>5</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G156" s="7" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>554.75</v>
+        <v>580</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4745,7 +4745,7 @@
         <v>25</v>
       </c>
       <c r="F157" s="6" t="n">
-        <v>550</v>
+        <v>575</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>257.45</v>
+        <v>267.6</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4772,7 +4772,7 @@
         <v>10</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1135</v>
+        <v>1110.9</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1125</v>
+        <v>1100</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>166.4</v>
+        <v>166.83</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1135.1</v>
+        <v>1160</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -42,9 +42,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,10 +51,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,11 +118,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  21-Sep-2026 18:33</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  22-Sep-2026 17:35</t>
         </is>
       </c>
     </row>
@@ -536,6 +565,4299 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>496</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>495</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND_CM | AARTIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>7120.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>7100</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ABB_CM | ABB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>27225</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>27200</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA_CM | ABBOTINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>397</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>395</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL_CM | ABCAPITAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ABFRL_CM | ABFRL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1238.2</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ACC_CM | ACC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2997</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT_CM | ADANIENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1795</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS_CM | ADANIPORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5331.5</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ALKEM_CM | ALKEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>390</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AMBUJACEM_CM | AMBUJACEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE_CM | ANGELONE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>8835.5</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP_CM | APOLLOHOSP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE_CM | APOLLOTYRE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>160.75</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY_CM | ASHOKLEY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2448.5</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT_CM | ASIANPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1381.6</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAL_CM | ASTRAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>626.25</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>625</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ATGL_CM | ATGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA_CM | AUROPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1036.4</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK_CM | AUBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1242.7</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AXISBANK_CM | AXISBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>11363</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>11400</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO_CM | BAJAJ-AUTO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1823.4</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV_CM | BAJAJFINSV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1008.8</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>BAJFINANCE_CM | BAJFINANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2216.9</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>BALKRISIND_CM | BALKRISIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK_CM | BANDHANBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>234.35</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>235</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>BANKBARODA_CM | BANKBARODA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>397.9</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>BEL_CM | BEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>452.6</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>BERGEPAINT_CM | BERGEPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1817.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>BHARTIARTL_CM | BHARTIARTL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>425.8</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>BHEL_CM | BHEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>BIOCON_CM | BIOCON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>48290</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>48200</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD_CM | BOSCHLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>313.6</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>BPCL_CM | BPCL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>4918</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>BRITANNIA_CM | BRITANNIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CANBK_CM | CANBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1759.1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>CHOLAFIN_CM | CHOLAFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1384.1</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>428</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>430</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>COALINDIA_CM | COALINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1803</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE_CM | COFORGE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1875</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>COLPAL_CM | COLPAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>467</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR_CM | CONCOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>222</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>220</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>CROMPTON_CM | CROMPTON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>4962.5</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND_CM | CUMMINSIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>390</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>DABUR_CM | DABUR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1613.2</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>DEEPAKNTR_CM | DEEPAKNTR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>9352</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>9400</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>DIVISLAB_CM | DIVISLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>13084</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>13100</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>DIXON_CM | DIXON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>669.5</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>670</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>DLF_CM | DLF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DRREDDY_CM | DRREDDY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>7427</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>7400</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>EICHERMOT_CM | EICHERMOT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>2793.6</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>ESCORTS_CM | ESCORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>429.7</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>430</v>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>EXIDEIND_CM | EXIDEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>327</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>325</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>FEDERALBNK_CM | FEDERALBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="n">
+        <v>171.84</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>GAIL_CM | GAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2461.4</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK_CM | GLENMARK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>873.6</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>875</v>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>GODREJCP_CM | GODREJCP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1699.5</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>GODREJPROP_CM | GODREJPROP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>864.05</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>865</v>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>GRANULES_CM | GRANULES_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>3128.2</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>475</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>3125</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM_CM | GRASIM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>HAL_CM | HAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>1088.9</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>HAVELLS_CM | HAVELLS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>1270.4</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>HCLTECH_CM | HCLTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>2430</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>HDFCAMC_CM | HDFCAMC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>738.6</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>550</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>HDFCBANK_CM | HDFCBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>559.2</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE_CM | HDFCLIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>5373</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO_CM | HEROMOTOCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>973</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>970</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO_CM | HINDALCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>508.2</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>3650</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>510</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>HINDCOPPER_CM | HINDCOPPER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>360.7</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>360</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>HINDPETRO_CM | HINDPETRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>1933.8</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>HINDUNILVR_CM | HINDUNILVR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>85.37</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB_CM | IDFCFIRSTB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>IEX</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>IEX_CM | IEX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>146.68</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1375</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>IGL_CM | IGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>736.25</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>735</v>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>INDHOTEL_CM | INDHOTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>INDIAMART</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>1635.2</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>INDIAMART_CM | INDIAMART_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>5030</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>5050</v>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>INDIGO_CM | INDIGO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>955</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>950</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>INDUSINDBK_CM | INDUSINDBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>380</v>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>INDUSTOWER_CM | INDUSTOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>1029.4</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>INFY_CM | INFY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n">
+        <v>137.8</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>IOC_CM | IOC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>469.65</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC_CM | IRCTC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>270</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>ITC_CM | ITC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1141</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>JINDALSTEL_CM | JINDALSTEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="n">
+        <v>518</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>520</v>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>JSWENERGY_CM | JSWENERGY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1267</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>1275</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>JSWSTEEL_CM | JSWSTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="n">
+        <v>491.1</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>JUBLFOOD_CM | JUBLFOOD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>425</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK_CM | KOTAKBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="n">
+        <v>529.05</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>525</v>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>KPITTECH_CM | KPITTECH_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>1909.8</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>LALPATHLAB_CM | LALPATHLAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="n">
+        <v>2006.5</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>2005</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>LAURUSLABS_CM | LAURUSLABS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>565</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>LICHSGFIN_CM | LICHSGFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n">
+        <v>3866.4</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>LT_CM | LT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>304.9</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>LTF_CM | LTF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="n">
+        <v>3293.6</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>LTTS_CM | LTTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>2135</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>2125</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN_CM | LUPIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="n">
+        <v>3044.5</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>3050</v>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>M&amp;M_CM | M&amp;M_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>MANAPPURAM_CM | MANAPPURAM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>830</v>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>MARICO_CM | MARICO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>12190</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>12200</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI_CM | MARUTI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n">
+        <v>3262.6</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>3275</v>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>MCX_CM | MCX_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>592.4</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>METROPOLIS_CM | METROPOLIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>1554.2</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>MFSL_CM | MFSL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>MGL</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>1067.3</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>MGL_CM | MGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>161.77</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>160</v>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>MOTHERSON_CM | MOTHERSON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>2265</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>MPHASIS_CM | MPHASIS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>MRF</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n">
+        <v>124770</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>125000</v>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>MRF_CM | MRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>2831.5</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>2825</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN_CM | MUTHOOTFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>350</v>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>NATIONALUM_CM | NATIONALUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>NAUKRI_CM | NAUKRI_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>8438</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR_CM | NAVINFLUOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>1363.9</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>NESTLEIND_CM | NESTLEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>6750</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>NMDC_CM | NMDC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>327.8</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>NTPC_CM | NTPC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>1845.6</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY_CM | OBEROIRLTY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>10989</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>OFSS_CM | OFSS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>236.13</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>ONGC_CM | ONGC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>37150</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F119" s="6" t="n">
+        <v>37000</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>PAGEIND_CM | PAGEIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>5366</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>5400</v>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>PERSISTENT_CM | PERSISTENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F121" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>PETRONET_CM | PETRONET_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>345.8</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>345</v>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>PFC_CM | PFC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND_CM | PIDILITIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="n">
+        <v>2410</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>PIIND_CM | PIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>PNB_CM | PNB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="n">
+        <v>8350</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>POLYCAB_CM | POLYCAB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>POWERGRID_CM | POWERGRID_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="n">
+        <v>423.2</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>RBLBANK_CM | RBLBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>307.1</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>RECLTD_CM | RECLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>1240.4</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>RELIANCE_CM | RELIANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>SAIL_CM | SAIL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="n">
+        <v>634.95</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>625</v>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>SBICARD_CM | SBICARD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>1756.3</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>SBILIFE_CM | SBILIFE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>987</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>990</v>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>SBIN_CM | SBIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>22000</v>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>SHREECEM_CM | SHREECEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN_CM | SHRIRAMFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>3858</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>3850</v>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>SIEMENS_CM | SIEMENS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>SRF</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>2538.3</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F138" s="10" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>SRF_CM | SRF_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>1846.4</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>1850</v>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA_CM | SUNPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="n">
+        <v>490.1</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E140" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F140" s="10" t="n">
+        <v>490</v>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>SUNTV_CM | SUNTV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>SYNGENE</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>380</v>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>SYNGENE_CM | SYNGENE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="n">
+        <v>674</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E142" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F142" s="10" t="n">
+        <v>675</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>TATACHEM_CM | TATACHEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>1692.4</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>TATACOMM_CM | TATACOMM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="7" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F144" s="10" t="n">
+        <v>980</v>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>TATACONSUM_CM | TATACONSUM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>3375</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>365</v>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER_CM | TATAPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="C146" s="9" t="n">
+        <v>184.97</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>TATASTEEL_CM | TATASTEEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>2105</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>TCS_CM | TCS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="7" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>1551.6</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F148" s="10" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>TECHM_CM | TECHM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>4928.5</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>TITAN_CM | TITAN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>4935</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F150" s="10" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>TORNTPHARM_CM | TORNTPHARM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="n">
+        <v>1246.3</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>TORNTPOWER_CM | TORNTPOWER_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="C152" s="9" t="n">
+        <v>2782.9</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>375</v>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F152" s="10" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>TRENT_CM | TRENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>4140</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F153" s="6" t="n">
+        <v>4150</v>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>TVSMOTOR_CM | TVSMOTOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>UBL</t>
+        </is>
+      </c>
+      <c r="C154" s="9" t="n">
+        <v>1215.2</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F154" s="10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>UBL_CM | UBL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F155" s="6" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO_CM | ULTRACEMCO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C156" s="9" t="n">
+        <v>178</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F156" s="10" t="n">
+        <v>180</v>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>UNIONBANK_CM | UNIONBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>559.9</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F157" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>UPL_CM | UPL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="n">
+        <v>263</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F158" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>VEDL_CM | VEDL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>VOLTAS</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>1100.8</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F159" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>VOLTAS_CM | VOLTAS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C160" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E160" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F160" s="10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>WIPRO_CM | WIPRO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>1162.3</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F161" s="6" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE_CM | ZYDUSLIFE_NM</t>
         </is>
       </c>
     </row>
@@ -562,151 +4884,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Legend &amp; Column Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sheet Naming</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SYMBOL_CM = Current Month | SYMBOL_NM = Next Month</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Monthly Expiry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Last Thursday of each month (NSE standard for stock F&amp;O)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ATM Row</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Yellow = At-The-Money strike (nearest to spot price)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CALL (CE)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Blue — buyer profits when stock RISES above strike</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PUT (PE)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Red — buyer profits when stock FALLS below strike</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Last traded price of the option contract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Open Interest — total outstanding contracts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Contracts traded in current session</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>IV (%)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Implied Volatility (%) from Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Open / Chg OI</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>0 = not available via Yahoo Finance option chain</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Yahoo Finance (yfinance) — NSE option chain</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>GitHub Actions — Every weekday Mon–Fri at 6:30 PM IST</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  22-Sep-2026 17:35</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  23-Sep-2026 17:46</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>496</v>
+        <v>491.35</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7120.5</v>
+        <v>7120</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27225</v>
+        <v>26935</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27200</v>
+        <v>27000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>397</v>
+        <v>402.45</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.22</v>
+        <v>49.09</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1238.2</v>
+        <v>1251.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2997</v>
+        <v>2993.2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1795</v>
+        <v>1807.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5331.5</v>
+        <v>5417.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>386.9</v>
+        <v>392.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>295.1</v>
+        <v>300</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8835.5</v>
+        <v>9069</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8800</v>
+        <v>9100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>402.55</v>
+        <v>405.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>160.75</v>
+        <v>162.89</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2448.5</v>
+        <v>2455</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1381.6</v>
+        <v>1394.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -992,7 +992,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>626.25</v>
+        <v>625.25</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1700</v>
+        <v>1721.5</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1036.4</v>
+        <v>1053</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1242.7</v>
+        <v>1243.2</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11363</v>
+        <v>11400</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1823.4</v>
+        <v>1846.5</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1008.8</v>
+        <v>1043.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2216.9</v>
+        <v>2199.6</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>184.7</v>
+        <v>191.38</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>234.35</v>
+        <v>236.87</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>397.9</v>
+        <v>396.05</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>452.6</v>
+        <v>459.75</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1817.2</v>
+        <v>1833.2</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>425.8</v>
+        <v>423.1</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>48290</v>
+        <v>47955</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48200</v>
+        <v>48000</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>313.6</v>
+        <v>315.75</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4918</v>
+        <v>4929</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>122.9</v>
+        <v>126</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1759.1</v>
+        <v>1774</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1384.1</v>
+        <v>1383</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>428</v>
+        <v>424.55</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1803</v>
+        <v>1782.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1869</v>
+        <v>1886.7</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>467</v>
+        <v>464.65</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>222</v>
+        <v>223.43</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>4962.5</v>
+        <v>5010</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>388.1</v>
+        <v>387.4</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1613.2</v>
+        <v>1635.8</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9352</v>
+        <v>9624</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1802,7 +1802,7 @@
         <v>100</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>9400</v>
+        <v>9600</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13084</v>
+        <v>13200</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13100</v>
+        <v>13200</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>669.5</v>
+        <v>675</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1211</v>
+        <v>1211.2</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7427</v>
+        <v>7470</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2793.6</v>
+        <v>2796.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>429.7</v>
+        <v>425.95</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1964,7 +1964,7 @@
         <v>5</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>327</v>
+        <v>331.3</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>171.84</v>
+        <v>172.95</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2461.4</v>
+        <v>2475</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2450</v>
+        <v>2475</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>873.6</v>
+        <v>879.75</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1699.5</v>
+        <v>1707.6</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>864.05</v>
+        <v>860.25</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3128.2</v>
+        <v>3188.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3125</v>
+        <v>3200</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4800</v>
+        <v>4836</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1088.9</v>
+        <v>1096.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1270.4</v>
+        <v>1256.7</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2234,7 +2234,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2430</v>
+        <v>2448.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>738.6</v>
+        <v>737.25</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2288,7 +2288,7 @@
         <v>25</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>750</v>
+        <v>725</v>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>559.2</v>
+        <v>561.5</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5373</v>
+        <v>5394</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>973</v>
+        <v>1003.8</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>508.2</v>
+        <v>513</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>360.7</v>
+        <v>360</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1933.8</v>
+        <v>1950</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>85.37</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>112.9</v>
+        <v>113.16</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>146.68</v>
+        <v>147.09</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>736.25</v>
+        <v>743.7</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1635.2</v>
+        <v>1652.4</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2585,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>5030</v>
+        <v>5028.5</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>955</v>
+        <v>959.3</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>382.1</v>
+        <v>384.8</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1029.4</v>
+        <v>1020.5</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>137.8</v>
+        <v>138.15</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>469.65</v>
+        <v>463.8</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>265.8</v>
+        <v>270.15</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1141</v>
+        <v>1175.3</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1267</v>
+        <v>1297.8</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1275</v>
+        <v>1300</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>491.1</v>
+        <v>483.3</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2882,7 +2882,7 @@
         <v>25</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>412.65</v>
+        <v>413.25</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>529.05</v>
+        <v>527</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1909.8</v>
+        <v>1924.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>2006.5</v>
+        <v>2034</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>2005</v>
+        <v>2035</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>565</v>
+        <v>572.5</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3866.4</v>
+        <v>3929.9</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3850</v>
+        <v>3950</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>304.9</v>
+        <v>310</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3293.6</v>
+        <v>3231.3</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3098,7 +3098,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2135</v>
+        <v>2102.8</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3125,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>2125</v>
+        <v>2100</v>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3044.5</v>
+        <v>3035</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>319.3</v>
+        <v>320.4</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>830</v>
+        <v>832.3</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12190</v>
+        <v>12230</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3262.6</v>
+        <v>3374</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3275</v>
+        <v>3375</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>592.4</v>
+        <v>585.5</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1554.2</v>
+        <v>1562.9</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1550</v>
+        <v>1575</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1067.3</v>
+        <v>1092.8</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>161.77</v>
+        <v>164.4</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2265</v>
+        <v>2259</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>124770</v>
+        <v>124580</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>125000</v>
+        <v>124500</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2831.5</v>
+        <v>2856.5</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2825</v>
+        <v>2850</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>352.2</v>
+        <v>363.45</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1304</v>
+        <v>1297</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8438</v>
+        <v>8457.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1363.9</v>
+        <v>1387.2</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>80.2</v>
+        <v>82</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>327.8</v>
+        <v>326</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1845.6</v>
+        <v>1850</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>10989</v>
+        <v>10849</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>11000</v>
+        <v>10800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>236.13</v>
+        <v>236.9</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>37150</v>
+        <v>37340</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3719,7 +3719,7 @@
         <v>500</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>37000</v>
+        <v>37500</v>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5366</v>
+        <v>5240</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5400</v>
+        <v>5200</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>281.75</v>
+        <v>285.85</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3773,7 +3773,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>345.8</v>
+        <v>346</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1572.7</v>
+        <v>1588.1</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1550</v>
+        <v>1600</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2410</v>
+        <v>2386</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>117</v>
+        <v>118.3</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3881,7 +3881,7 @@
         <v>5</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8350</v>
+        <v>8417</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>265.95</v>
+        <v>270.2</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>423.2</v>
+        <v>428</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>307.1</v>
+        <v>311.5</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>174.01</v>
+        <v>185.44</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4043,7 +4043,7 @@
         <v>5</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>634.95</v>
+        <v>635</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1756.3</v>
+        <v>1760</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>987</v>
+        <v>994.1</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22200</v>
+        <v>22500</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>500</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1006</v>
+        <v>1010.8</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3858</v>
+        <v>3886</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2538.3</v>
+        <v>2550</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1846.4</v>
+        <v>1865</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1850</v>
+        <v>1875</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>490.1</v>
+        <v>490.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>377.5</v>
+        <v>381.85</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>674</v>
+        <v>669.9</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1692.4</v>
+        <v>1700.6</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>984.1</v>
+        <v>994.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>184.97</v>
+        <v>190.82</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4448,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2105</v>
+        <v>2089.6</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1551.6</v>
+        <v>1557</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4928.5</v>
+        <v>4880</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4935</v>
+        <v>4985</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1246.3</v>
+        <v>1259.4</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2782.9</v>
+        <v>2774</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4140</v>
+        <v>4135</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4150</v>
+        <v>4125</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1215.2</v>
+        <v>1242.3</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11000</v>
+        <v>11155</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11000</v>
+        <v>11200</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>559.9</v>
+        <v>553.15</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4772,7 +4772,7 @@
         <v>10</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G158" s="7" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1100.8</v>
+        <v>1130</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4799,7 +4799,7 @@
         <v>25</v>
       </c>
       <c r="F159" s="6" t="n">
-        <v>1100</v>
+        <v>1125</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>166</v>
+        <v>164.9</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4826,7 +4826,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1162.3</v>
+        <v>1170.1</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  23-Sep-2026 17:46</t>
+          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  24-Sep-2026 17:48</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>491.35</v>
+        <v>489.45</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7120</v>
+        <v>7129</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7100</v>
+        <v>7150</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26935</v>
+        <v>26860</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27000</v>
+        <v>26800</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>402.45</v>
+        <v>390.1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>49.09</v>
+        <v>48.06</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1251.4</v>
+        <v>1236.1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -722,7 +722,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>1250</v>
+        <v>1225</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2993.2</v>
+        <v>2900</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1807.3</v>
+        <v>1785.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5417.5</v>
+        <v>5326</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -803,7 +803,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>392.75</v>
+        <v>384.1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -830,7 +830,7 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>300</v>
+        <v>290.7</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>9069</v>
+        <v>8888.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>9100</v>
+        <v>8900</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>405.7</v>
+        <v>397.95</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>162.89</v>
+        <v>157.3</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2455</v>
+        <v>2392.7</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1394.8</v>
+        <v>1392</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>625.25</v>
+        <v>612.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1019,7 +1019,7 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1721.5</v>
+        <v>1716</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1053</v>
+        <v>1000.1</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1243.2</v>
+        <v>1186.5</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1250</v>
+        <v>1175</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11400</v>
+        <v>11208</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11400</v>
+        <v>11200</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1846.5</v>
+        <v>1762.3</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1850</v>
+        <v>1750</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1043.2</v>
+        <v>982</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2199.6</v>
+        <v>2167.8</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2200</v>
+        <v>2150</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>191.38</v>
+        <v>182.9</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>236.87</v>
+        <v>234.3</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>396.05</v>
+        <v>392</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>459.75</v>
+        <v>449.4</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1833.2</v>
+        <v>1795.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>423.1</v>
+        <v>415.35</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47955</v>
+        <v>47750</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>48000</v>
+        <v>47800</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>315.75</v>
+        <v>307.1</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1451,7 +1451,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4929</v>
+        <v>4895</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>4950</v>
+        <v>4900</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>126</v>
+        <v>125.9</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1774</v>
+        <v>1681.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1532,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>1775</v>
+        <v>1675</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1383</v>
+        <v>1399</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,7 +1559,7 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>1375</v>
+        <v>1400</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>424.55</v>
+        <v>422</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1782.4</v>
+        <v>1785.9</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1886.7</v>
+        <v>1854.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1640,7 +1640,7 @@
         <v>25</v>
       </c>
       <c r="F42" s="10" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>464.65</v>
+        <v>466.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>223.43</v>
+        <v>219.8</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1694,7 +1694,7 @@
         <v>5</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>5010</v>
+        <v>4973</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1721,7 +1721,7 @@
         <v>50</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>387.4</v>
+        <v>385.7</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1635.8</v>
+        <v>1600.9</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1775,7 +1775,7 @@
         <v>50</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>1650</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9624</v>
+        <v>9602</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13200</v>
+        <v>13299</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>675</v>
+        <v>670.4</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1211.2</v>
+        <v>1200.4</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7470</v>
+        <v>7338.5</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7500</v>
+        <v>7300</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2796.9</v>
+        <v>2822.9</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>425.95</v>
+        <v>426.55</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>331.3</v>
+        <v>329.5</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>172.95</v>
+        <v>173.85</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2475</v>
+        <v>2430.4</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2475</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>879.75</v>
+        <v>875</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1707.6</v>
+        <v>1671.2</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1700</v>
+        <v>1650</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>860.25</v>
+        <v>853</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3188.5</v>
+        <v>3166.5</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3200</v>
+        <v>3175</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4836</v>
+        <v>4774.2</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1096.5</v>
+        <v>1090</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1256.7</v>
+        <v>1243.6</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2448.3</v>
+        <v>2380.3</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>737.25</v>
+        <v>728.9</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>561.5</v>
+        <v>526.9</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2315,7 +2315,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5394</v>
+        <v>5296</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1003.8</v>
+        <v>982</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>513</v>
+        <v>495.7</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>360</v>
+        <v>350.4</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1950</v>
+        <v>1933.5</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>87.90000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2477,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>113.16</v>
+        <v>111.2</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>147.09</v>
+        <v>145.74</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>743.7</v>
+        <v>728.8</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>745</v>
+        <v>730</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1652.4</v>
+        <v>1635.9</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2585,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>5028.5</v>
+        <v>4890</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>959.3</v>
+        <v>919.5</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>384.8</v>
+        <v>379.85</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1020.5</v>
+        <v>1014.5</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>138.15</v>
+        <v>136.27</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2720,7 +2720,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>463.8</v>
+        <v>461.2</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2747,7 +2747,7 @@
         <v>25</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>270.15</v>
+        <v>268</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1175.3</v>
+        <v>1157.8</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1175</v>
+        <v>1150</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1297.8</v>
+        <v>1273.2</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2855,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>483.3</v>
+        <v>478.9</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>413.25</v>
+        <v>405</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2909,7 +2909,7 @@
         <v>25</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>425</v>
+        <v>400</v>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>527</v>
+        <v>516.85</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1924.3</v>
+        <v>1961.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2963,7 +2963,7 @@
         <v>100</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>2034</v>
+        <v>2026.2</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>2035</v>
+        <v>2025</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>572.5</v>
+        <v>564.25</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3929.9</v>
+        <v>3858.4</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3950</v>
+        <v>3850</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3231.3</v>
+        <v>3209.1</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2102.8</v>
+        <v>2100.7</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>3035</v>
+        <v>2982.7</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3050</v>
+        <v>3000</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>320.4</v>
+        <v>324.95</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>832.3</v>
+        <v>824.55</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3206,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>12230</v>
+        <v>11990</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12200</v>
+        <v>12000</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3374</v>
+        <v>3427.7</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3375</v>
+        <v>3425</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>585.5</v>
+        <v>582.95</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1562.9</v>
+        <v>1410</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1575</v>
+        <v>1400</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1092.8</v>
+        <v>1079.6</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3341,7 +3341,7 @@
         <v>25</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>164.4</v>
+        <v>162.5</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2259</v>
+        <v>2248.2</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>124580</v>
+        <v>123985</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3422,7 +3422,7 @@
         <v>500</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>124500</v>
+        <v>124000</v>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2856.5</v>
+        <v>2825.3</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>2850</v>
+        <v>2825</v>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>363.45</v>
+        <v>358.4</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1297</v>
+        <v>1224</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3503,7 +3503,7 @@
         <v>100</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8457.5</v>
+        <v>8461</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1387.2</v>
+        <v>1351</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>82</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C115" s="5" t="n">
-        <v>326</v>
+        <v>326.6</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>2250</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1850</v>
+        <v>1837.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>10849</v>
+        <v>10925</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>236.9</v>
+        <v>239</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>37340</v>
+        <v>37500</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5240</v>
+        <v>5277</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>285.85</v>
+        <v>286.6</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>346</v>
+        <v>339.35</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3800,7 +3800,7 @@
         <v>5</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1588.1</v>
+        <v>1522</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3827,7 +3827,7 @@
         <v>50</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2386</v>
+        <v>2393.5</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>118.3</v>
+        <v>117.12</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3881,7 +3881,7 @@
         <v>5</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8417</v>
+        <v>8366.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>270.2</v>
+        <v>266.4</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>428</v>
+        <v>412.75</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3962,7 +3962,7 @@
         <v>5</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>311.5</v>
+        <v>308.25</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1248</v>
+        <v>1219.2</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4016,7 +4016,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>1250</v>
+        <v>1200</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>185.44</v>
+        <v>184</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>635</v>
+        <v>618.4</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>994.1</v>
+        <v>978.5</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4124,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22500</v>
+        <v>22350</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>1010.8</v>
+        <v>990</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3886</v>
+        <v>3841.8</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>3900</v>
+        <v>3850</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2550</v>
+        <v>2533.8</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1865</v>
+        <v>1849.9</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4259,7 +4259,7 @@
         <v>25</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>1875</v>
+        <v>1850</v>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>490.2</v>
+        <v>512.7</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4286,7 +4286,7 @@
         <v>10</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>381.85</v>
+        <v>380.35</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>669.9</v>
+        <v>652.2</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4340,7 +4340,7 @@
         <v>25</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>675</v>
+        <v>650</v>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1700.6</v>
+        <v>1670</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4367,7 +4367,7 @@
         <v>25</v>
       </c>
       <c r="F143" s="6" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>994.3</v>
+        <v>986.3</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>369</v>
+        <v>363.45</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>190.82</v>
+        <v>188.02</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2089.6</v>
+        <v>2087</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1557</v>
+        <v>1543</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4880</v>
+        <v>4832.5</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4900</v>
+        <v>4850</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4985</v>
+        <v>4928.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1259.4</v>
+        <v>1244.2</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2774</v>
+        <v>2700</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2750</v>
+        <v>2700</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4135</v>
+        <v>4091</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4125</v>
+        <v>4100</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1242.3</v>
+        <v>1270.2</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1250</v>
+        <v>1275</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11155</v>
+        <v>11056</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11200</v>
+        <v>11100</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>180</v>
+        <v>179.45</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>553.15</v>
+        <v>549.6</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>271</v>
+        <v>267.5</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1130</v>
+        <v>1113.4</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>164.9</v>
+        <v>163.64</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1170.1</v>
+        <v>1180.3</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:24-Sep-2026  NM:29-Oct-2026  |  24-Sep-2026 17:48</t>
+          <t>NSE Stock Options  |  CM:29-Oct-2026  NM:26-Nov-2026  |  25-Sep-2026 17:50</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>489.45</v>
+        <v>489.25</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>7129</v>
+        <v>7052.5</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>7150</v>
+        <v>7050</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26860</v>
+        <v>26955</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -641,7 +641,7 @@
         <v>200</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>26800</v>
+        <v>27000</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>390.1</v>
+        <v>390</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>48.06</v>
+        <v>49.14</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1236.1</v>
+        <v>1236.4</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1775</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5326</v>
+        <v>5274</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>384.1</v>
+        <v>383.8</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>290.7</v>
+        <v>288</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8888.5</v>
+        <v>8889</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>397.95</v>
+        <v>400.1</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>157.3</v>
+        <v>159.08</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2392.7</v>
+        <v>2444</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -965,7 +965,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2400</v>
+        <v>2450</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1392</v>
+        <v>1399</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>612.4</v>
+        <v>611.65</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1725</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1000.1</v>
+        <v>1018</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1073,7 +1073,7 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1000</v>
+        <v>1025</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1186.5</v>
+        <v>1222.4</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1175</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11208</v>
+        <v>11281</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>11200</v>
+        <v>11300</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1762.3</v>
+        <v>1771</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1775</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>982</v>
+        <v>996.9</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2167.8</v>
+        <v>2185.3</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2200</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>182.9</v>
+        <v>187.7</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>234.3</v>
+        <v>235.26</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>392</v>
+        <v>393.55</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>449.4</v>
+        <v>458.35</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1795.8</v>
+        <v>1785.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1800</v>
+        <v>1775</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>415.35</v>
+        <v>418.95</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1370,7 +1370,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>387</v>
+        <v>382.15</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>47750</v>
+        <v>48250</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>47800</v>
+        <v>48200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>307.1</v>
+        <v>308.5</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4895</v>
+        <v>4937.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1478,7 +1478,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>125.9</v>
+        <v>124.99</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1681.7</v>
+        <v>1662.7</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1399</v>
+        <v>1399.7</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>422</v>
+        <v>426.1</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2100</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1785.9</v>
+        <v>1784</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>200</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>1854.8</v>
+        <v>1855.8</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>350</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>466.3</v>
+        <v>461.5</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>1250</v>
@@ -1667,7 +1667,7 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>219.8</v>
+        <v>218.6</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>3000</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>4973</v>
+        <v>4945</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>600</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>385.7</v>
+        <v>385.6</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>2750</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1600.9</v>
+        <v>1587.1</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>300</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>9602</v>
+        <v>9619.5</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>200</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>13299</v>
+        <v>13390</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>150</v>
@@ -1829,7 +1829,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>670.4</v>
+        <v>683</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>1650</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1200.4</v>
+        <v>1201</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>250</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>7338.5</v>
+        <v>7360</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>175</v>
@@ -1910,7 +1910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2822.9</v>
+        <v>2855.7</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>275</v>
@@ -1937,7 +1937,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>426.55</v>
+        <v>423.65</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>3600</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>329.5</v>
+        <v>322</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>5000</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>173.85</v>
+        <v>172.7</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>6400</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>2430.4</v>
+        <v>2380</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>1150</v>
@@ -2045,7 +2045,7 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>2425</v>
+        <v>2375</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>1000</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1671.2</v>
+        <v>1700.1</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>400</v>
@@ -2099,7 +2099,7 @@
         <v>50</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>853</v>
+        <v>868.65</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>2700</v>
@@ -2126,7 +2126,7 @@
         <v>5</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>475</v>
@@ -2153,7 +2153,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>3175</v>
+        <v>3200</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>4774.2</v>
+        <v>4800</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>200</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1090</v>
+        <v>1096.5</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>500</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>1243.6</v>
+        <v>1258</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>350</v>
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="C65" s="5" t="n">
-        <v>2380.3</v>
+        <v>2378</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>200</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>728.9</v>
+        <v>735.6</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>550</v>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>526.9</v>
+        <v>531</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1500</v>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>5296</v>
+        <v>5360</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>300</v>
@@ -2342,7 +2342,7 @@
         <v>50</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>5300</v>
+        <v>5350</v>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>2150</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>495.7</v>
+        <v>494.65</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3650</v>
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="C71" s="5" t="n">
-        <v>350.4</v>
+        <v>351</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>2700</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>1933.5</v>
+        <v>1942.9</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>300</v>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>83.76000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>7500</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>111.2</v>
+        <v>112.7</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>3750</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>145.74</v>
+        <v>144.95</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>1375</v>
@@ -2531,7 +2531,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>728.8</v>
+        <v>726.8</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>3000</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="C77" s="5" t="n">
-        <v>1635.9</v>
+        <v>1642.1</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>150</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>4890</v>
+        <v>4940</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>300</v>
@@ -2612,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>919.5</v>
+        <v>912.2</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>500</v>
@@ -2639,7 +2639,7 @@
         <v>25</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>379.85</v>
+        <v>374.65</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>2800</v>
@@ -2666,7 +2666,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1014.5</v>
+        <v>1000.2</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>400</v>
@@ -2693,7 +2693,7 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>136.27</v>
+        <v>135.7</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>3500</v>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="C83" s="5" t="n">
-        <v>461.2</v>
+        <v>458.7</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>875</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>3200</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1157.8</v>
+        <v>1164.8</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>1250</v>
@@ -2801,7 +2801,7 @@
         <v>25</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>1150</v>
+        <v>1175</v>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>510</v>
+        <v>506.55</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>1500</v>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1273.2</v>
+        <v>1277</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>600</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>478.9</v>
+        <v>484.55</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>625</v>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="C89" s="5" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>400</v>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>516.85</v>
+        <v>519.4</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>800</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1961.3</v>
+        <v>1952.3</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>300</v>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>2026.2</v>
+        <v>2007</v>
       </c>
       <c r="D92" s="7" t="n">
         <v>2500</v>
@@ -2990,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>2025</v>
+        <v>2005</v>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>564.25</v>
+        <v>566</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>1600</v>
@@ -3017,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>3858.4</v>
+        <v>3876.2</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>150</v>
@@ -3044,7 +3044,7 @@
         <v>50</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="C95" s="5" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>5000</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>3209.1</v>
+        <v>3206.1</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>200</v>
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>2100.7</v>
+        <v>2092</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>500</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>2982.7</v>
+        <v>3035</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>175</v>
@@ -3152,7 +3152,7 @@
         <v>50</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>324.95</v>
+        <v>334</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>4000</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>824.55</v>
+        <v>819</v>
       </c>
       <c r="D100" s="7" t="n">
         <v>1200</v>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="C101" s="5" t="n">
-        <v>11990</v>
+        <v>12065</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>12000</v>
+        <v>12100</v>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>3427.7</v>
+        <v>3324.9</v>
       </c>
       <c r="D102" s="7" t="n">
         <v>400</v>
@@ -3260,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>3425</v>
+        <v>3325</v>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>582.95</v>
+        <v>582.6</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>400</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>1410</v>
+        <v>1458</v>
       </c>
       <c r="D104" s="7" t="n">
         <v>1100</v>
@@ -3314,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>1079.6</v>
+        <v>1071.3</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>550</v>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>162.5</v>
+        <v>165.71</v>
       </c>
       <c r="D106" s="7" t="n">
         <v>14000</v>
@@ -3368,7 +3368,7 @@
         <v>5</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C107" s="5" t="n">
-        <v>2248.2</v>
+        <v>2234</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>300</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>123985</v>
+        <v>124035</v>
       </c>
       <c r="D108" s="7" t="n">
         <v>5</v>
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2825.3</v>
+        <v>2835</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>600</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>358.4</v>
+        <v>358.7</v>
       </c>
       <c r="D110" s="7" t="n">
         <v>7500</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>1224</v>
+        <v>1254.8</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>150</v>
@@ -3503,7 +3503,7 @@
         <v>100</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>8461</v>
+        <v>8584.5</v>
       </c>
       <c r="D112" s="7" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>8500</v>
+        <v>8600</v>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1351</v>
+        <v>1362.6</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>50</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>80.81999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>6750</v>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>1837.5</v>
+        <v>1858.5</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>700</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C117" s="5" t="n">
-        <v>10925</v>
+        <v>10770</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>75</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>10900</v>
+        <v>10800</v>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>239</v>
+        <v>235.86</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>1925</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>37500</v>
+        <v>37695</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>15</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>5277</v>
+        <v>5372</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>175</v>
@@ -3746,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>286.6</v>
+        <v>286.5</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>3000</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>339.35</v>
+        <v>338</v>
       </c>
       <c r="D122" s="7" t="n">
         <v>2700</v>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="C123" s="5" t="n">
-        <v>1522</v>
+        <v>1517.2</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>250</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>2393.5</v>
+        <v>2400</v>
       </c>
       <c r="D124" s="7" t="n">
         <v>250</v>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>117.12</v>
+        <v>116.6</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>8000</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>8366.5</v>
+        <v>8408.5</v>
       </c>
       <c r="D126" s="7" t="n">
         <v>175</v>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C127" s="5" t="n">
-        <v>266.4</v>
+        <v>269.5</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>2700</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>412.75</v>
+        <v>415.05</v>
       </c>
       <c r="D128" s="7" t="n">
         <v>5000</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>308.25</v>
+        <v>312.95</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>3000</v>
@@ -3989,7 +3989,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="D130" s="7" t="n">
         <v>1250</v>
@@ -4016,7 +4016,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>8500</v>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>618.4</v>
+        <v>611.2</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>1000</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>625</v>
+        <v>600</v>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>1755</v>
+        <v>1742</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>750</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>978.5</v>
+        <v>983</v>
       </c>
       <c r="D134" s="7" t="n">
         <v>1500</v>
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>22350</v>
+        <v>22520</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>990</v>
+        <v>994.1</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>300</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3841.8</v>
+        <v>3877</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>275</v>
@@ -4205,7 +4205,7 @@
         <v>50</v>
       </c>
       <c r="F137" s="6" t="n">
-        <v>3850</v>
+        <v>3900</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>2533.8</v>
+        <v>2540</v>
       </c>
       <c r="D138" s="7" t="n">
         <v>375</v>
@@ -4250,7 +4250,7 @@
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>1849.9</v>
+        <v>1852.2</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>350</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>512.7</v>
+        <v>513.2</v>
       </c>
       <c r="D140" s="7" t="n">
         <v>1500</v>
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C141" s="5" t="n">
-        <v>380.35</v>
+        <v>378.7</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>1500</v>
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>652.2</v>
+        <v>643.75</v>
       </c>
       <c r="D142" s="7" t="n">
         <v>1100</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>1670</v>
+        <v>1666.5</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>700</v>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>986.3</v>
+        <v>983.2</v>
       </c>
       <c r="D144" s="7" t="n">
         <v>1100</v>
@@ -4394,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>363.45</v>
+        <v>367.5</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>3375</v>
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>188.02</v>
+        <v>187.97</v>
       </c>
       <c r="D146" s="7" t="n">
         <v>5500</v>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2087</v>
+        <v>2082</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>150</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>1543</v>
+        <v>1548</v>
       </c>
       <c r="D148" s="7" t="n">
         <v>400</v>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>4832.5</v>
+        <v>4884</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>375</v>
@@ -4529,7 +4529,7 @@
         <v>50</v>
       </c>
       <c r="F149" s="6" t="n">
-        <v>4850</v>
+        <v>4900</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>4928.5</v>
+        <v>4988.5</v>
       </c>
       <c r="D150" s="7" t="n">
         <v>500</v>
@@ -4556,7 +4556,7 @@
         <v>50</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>4950</v>
+        <v>5000</v>
       </c>
       <c r="G150" s="7" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1244.2</v>
+        <v>1254.6</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>2700</v>
+        <v>2669.3</v>
       </c>
       <c r="D152" s="7" t="n">
         <v>375</v>
@@ -4610,7 +4610,7 @@
         <v>50</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>2700</v>
+        <v>2650</v>
       </c>
       <c r="G152" s="7" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="C153" s="5" t="n">
-        <v>4091</v>
+        <v>4157.3</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>350</v>
@@ -4637,7 +4637,7 @@
         <v>25</v>
       </c>
       <c r="F153" s="6" t="n">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>1270.2</v>
+        <v>1251.3</v>
       </c>
       <c r="D154" s="7" t="n">
         <v>700</v>
@@ -4664,7 +4664,7 @@
         <v>25</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>1275</v>
+        <v>1250</v>
       </c>
       <c r="G154" s="7" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>11056</v>
+        <v>11155</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>200</v>
@@ -4691,7 +4691,7 @@
         <v>100</v>
       </c>
       <c r="F155" s="6" t="n">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>179.45</v>
+        <v>180.2</v>
       </c>
       <c r="D156" s="7" t="n">
         <v>8400</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>549.6</v>
+        <v>550.05</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>1300</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>267.5</v>
+        <v>266.35</v>
       </c>
       <c r="D158" s="7" t="n">
         <v>2750</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>1113.4</v>
+        <v>1118.2</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>1000</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>163.64</v>
+        <v>164.02</v>
       </c>
       <c r="D160" s="7" t="n">
         <v>1500</v>
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>1180.3</v>
+        <v>1203.9</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>700</v>
@@ -4853,7 +4853,7 @@
         <v>25</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>1175</v>
+        <v>1200</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -42,9 +42,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,10 +51,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -113,11 +118,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -498,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:29-Oct-2026  NM:26-Nov-2026  |  28-Sep-2026 20:03</t>
+          <t>NSE Stock Options  |  CM:29-Oct-2026  NM:26-Nov-2026  |  29-Sep-2026 18:30</t>
         </is>
       </c>
     </row>
@@ -536,6 +565,1005 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>469.9</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND_CM | AARTIIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>6660.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>6650</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ABB_CM | ABB_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>27270</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>27200</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ABBOTINDIA_CM | ABBOTINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>378</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>380</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>ABCAPITAL_CM | ABCAPITAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ABFRL</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>ABFRL_CM | ABFRL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ACC_CM | ACC_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2972.9</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2950</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>ADANIENT_CM | ADANIENT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>ADANIPORTS_CM | ADANIPORTS_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ALKEM</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5250</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ALKEM_CM | ALKEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>370</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>AMBUJACEM_CM | AMBUJACEM_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ANGELONE_CM | ANGELONE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>8659</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP_CM | APOLLOHOSP_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>406.75</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>APOLLOTYRE_CM | APOLLOTYRE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>153.44</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>155</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>ASHOKLEY_CM | ASHOKLEY_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2415</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ASIANPAINT_CM | ASIANPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAL_CM | ASTRAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>600</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>ATGL_CM | ATGL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1697.7</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>AUROPHARMA_CM | AUROPHARMA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1005.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK_CM | AUBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>1212.1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>625</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>AXISBANK_CM | AXISBANK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>10811</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>10800</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO_CM | BAJAJ-AUTO_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1742.4</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV_CM | BAJAJFINSV_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>973.8</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>BAJFINANCE_CM | BAJFINANCE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BALKRISIND</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>2126.2</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>BALKRISIND_CM | BALKRISIND_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>185.31</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK_CM | BANDHANBNK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>227.68</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>230</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>BANKBARODA_CM | BANKBARODA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>3750</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>BEL_CM | BEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>BERGEPAINT_CM | BERGEPAINT_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1771.2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1775</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>BHARTIARTL_CM | BHARTIARTL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>413.35</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>415</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>BHEL_CM | BHEL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>377</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>375</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>BIOCON_CM | BIOCON_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>45700</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>45600</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>BOSCHLTD_CM | BOSCHLTD_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>299.35</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>BPCL_CM | BPCL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>4835</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>4850</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>BRITANNIA_CM | BRITANNIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>4350</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>120</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CANBK_CM | CANBK_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>1627.3</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>CHOLAFIN_CM | CHOLAFIN_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1379.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
         </is>
       </c>
     </row>
@@ -562,151 +1590,151 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Legend &amp; Column Guide</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Sheet Naming</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>SYMBOL_CM = Current Month | SYMBOL_NM = Next Month</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Monthly Expiry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Last Thursday of each month (NSE standard for stock F&amp;O)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ATM Row</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Yellow = At-The-Money strike (nearest to spot price)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>CALL (CE)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Blue — buyer profits when stock RISES above strike</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>PUT (PE)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Red — buyer profits when stock FALLS below strike</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>Last traded price of the option contract</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>Open Interest — total outstanding contracts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>Contracts traded in current session</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>IV (%)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>Implied Volatility (%) from Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Open / Chg OI</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>0 = not available via Yahoo Finance option chain</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Data Source</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Yahoo Finance (yfinance) — NSE option chain</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>GitHub Actions — Every weekday Mon–Fri at 6:30 PM IST</t>
         </is>

--- a/data/stock_options.xlsx
+++ b/data/stock_options.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Stock Options  |  CM:29-Oct-2026  NM:26-Nov-2026  |  29-Sep-2026 18:30</t>
+          <t>NSE Stock Options  |  CM:29-Oct-2026  NM:26-Nov-2026  |  30-Sep-2026 18:19</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C3" s="5" t="n">
-        <v>469.9</v>
+        <v>475.7</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1200</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C4" s="9" t="n">
-        <v>6660.5</v>
+        <v>6776</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>250</v>
@@ -614,7 +614,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>6650</v>
+        <v>6800</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>27270</v>
+        <v>27125</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>40</v>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>378</v>
+        <v>380.6</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3200</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>46.24</v>
+        <v>46.32</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>2800</v>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1202.6</v>
+        <v>1204.1</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>500</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2972.9</v>
+        <v>2903.4</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>875</v>
@@ -749,7 +749,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2950</v>
+        <v>2900</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1822</v>
+        <v>1798.3</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1250</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>1825</v>
+        <v>1800</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5250</v>
+        <v>5163.5</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>200</v>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>365.75</v>
+        <v>374</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>273.5</v>
+        <v>274</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>300</v>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>8659</v>
+        <v>8165.5</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>125</v>
@@ -884,7 +884,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>8700</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>406.75</v>
+        <v>404.7</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>2700</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>153.44</v>
+        <v>154.19</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>5500</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2415</v>
+        <v>2402.6</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>200</v>
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1375</v>
+        <v>1370.4</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>400</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>588.4</v>
+        <v>593.9</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>750</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1697.7</v>
+        <v>1672</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>650</v>
@@ -1046,7 +1046,7 @@
         <v>25</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1700</v>
+        <v>1675</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1005.2</v>
+        <v>1010.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>1000</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>1212.1</v>
+        <v>1226</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>625</v>
@@ -1100,7 +1100,7 @@
         <v>25</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>1200</v>
+        <v>1225</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10811</v>
+        <v>10874</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>250</v>
@@ -1127,7 +1127,7 @@
         <v>100</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1742.4</v>
+        <v>1731</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>500</v>
@@ -1154,7 +1154,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>1750</v>
+        <v>1725</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>973.8</v>
+        <v>959.4</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>125</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>2126.2</v>
+        <v>2117</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>400</v>
@@ -1208,7 +1208,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>185.31</v>
+        <v>178.23</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>3600</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>227.68</v>
+        <v>230.55</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>5850</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>387.75</v>
+        <v>388.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>3750</v>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>448.2</v>
+        <v>455.45</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>1100</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1771.2</v>
+        <v>1757</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>500</v>
@@ -1343,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1775</v>
+        <v>1750</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>413.35</v>
+        <v>415.5</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>10500</v>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>377</v>
+        <v>370.3</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>2900</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>45700</v>
+        <v>47100</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>50</v>
@@ -1424,7 +1424,7 @@
         <v>200</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>45600</v>
+        <v>47200</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>299.35</v>
+        <v>303.2</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1800</v>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C36" s="9" t="n">
-        <v>4835</v>
+        <v>4830</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>200</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>119.51</v>
+        <v>119.44</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>4350</v>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>1627.3</v>
+        <v>1620</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>700</v>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1379.3</v>
+        <v>1346</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>650</v>
@@ -1559,11 +1559,3305 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CIPLA_CM | CIPLA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>425</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>420</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>COALINDIA_CM | COALINDIA_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1749.1</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>COFORGE_CM | COFORGE_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>COLPAL</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>1763.3</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>350</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1775</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>COLPAL_CM | COLPAL_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CONCOR_CM | CONCOR_NM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>208.67</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>3000</v>
+      </c>
